--- a/public/plantillas/analisis-diferencia-novedades.xlsx
+++ b/public/plantillas/analisis-diferencia-novedades.xlsx
@@ -118,7 +118,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -145,6 +145,9 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -656,7 +659,7 @@
         <v/>
       </c>
       <c r="H6" s="9">
-        <f>IF(A6="","",IFERROR(VLOOKUP(A6,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A6="","",IFERROR(IF(VLOOKUP(A6,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A6,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I6" s="10">
@@ -672,7 +675,7 @@
         <v/>
       </c>
       <c r="L6" s="9">
-        <f>IF(AND(A6="",C6=""),"",IF(A6="","Falta el tipo",IF(C6="","Falta el código",IF(ISNA(MATCH(C6,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D6)&gt;0,N(VLOOKUP(C6,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A6,TIPOS!$A:$C,3,FALSE),"")="Sí",B6=""),"Falta el N° de entrega",IF(N(I6)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A6="",C6=""),"",IF(A6="","Falta el tipo",IF(H6="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C6="","Falta el código",IF(ISNA(MATCH(C6,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D6)&gt;0,N(VLOOKUP(C6,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A6,TIPOS!$A:$C,3,FALSE),"")="Sí",B6=""),"Falta el N° de entrega",IF(N(I6)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -688,7 +691,7 @@
         <v/>
       </c>
       <c r="H7" s="9">
-        <f>IF(A7="","",IFERROR(VLOOKUP(A7,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A7="","",IFERROR(IF(VLOOKUP(A7,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A7,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I7" s="10">
@@ -704,7 +707,7 @@
         <v/>
       </c>
       <c r="L7" s="9">
-        <f>IF(AND(A7="",C7=""),"",IF(A7="","Falta el tipo",IF(C7="","Falta el código",IF(ISNA(MATCH(C7,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D7)&gt;0,N(VLOOKUP(C7,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A7,TIPOS!$A:$C,3,FALSE),"")="Sí",B7=""),"Falta el N° de entrega",IF(N(I7)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A7="",C7=""),"",IF(A7="","Falta el tipo",IF(H7="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C7="","Falta el código",IF(ISNA(MATCH(C7,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D7)&gt;0,N(VLOOKUP(C7,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A7,TIPOS!$A:$C,3,FALSE),"")="Sí",B7=""),"Falta el N° de entrega",IF(N(I7)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -720,7 +723,7 @@
         <v/>
       </c>
       <c r="H8" s="9">
-        <f>IF(A8="","",IFERROR(VLOOKUP(A8,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A8="","",IFERROR(IF(VLOOKUP(A8,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A8,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I8" s="10">
@@ -736,7 +739,7 @@
         <v/>
       </c>
       <c r="L8" s="9">
-        <f>IF(AND(A8="",C8=""),"",IF(A8="","Falta el tipo",IF(C8="","Falta el código",IF(ISNA(MATCH(C8,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D8)&gt;0,N(VLOOKUP(C8,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A8,TIPOS!$A:$C,3,FALSE),"")="Sí",B8=""),"Falta el N° de entrega",IF(N(I8)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A8="",C8=""),"",IF(A8="","Falta el tipo",IF(H8="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C8="","Falta el código",IF(ISNA(MATCH(C8,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D8)&gt;0,N(VLOOKUP(C8,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A8,TIPOS!$A:$C,3,FALSE),"")="Sí",B8=""),"Falta el N° de entrega",IF(N(I8)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -752,7 +755,7 @@
         <v/>
       </c>
       <c r="H9" s="9">
-        <f>IF(A9="","",IFERROR(VLOOKUP(A9,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A9="","",IFERROR(IF(VLOOKUP(A9,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A9,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I9" s="10">
@@ -768,7 +771,7 @@
         <v/>
       </c>
       <c r="L9" s="9">
-        <f>IF(AND(A9="",C9=""),"",IF(A9="","Falta el tipo",IF(C9="","Falta el código",IF(ISNA(MATCH(C9,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D9)&gt;0,N(VLOOKUP(C9,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A9,TIPOS!$A:$C,3,FALSE),"")="Sí",B9=""),"Falta el N° de entrega",IF(N(I9)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A9="",C9=""),"",IF(A9="","Falta el tipo",IF(H9="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C9="","Falta el código",IF(ISNA(MATCH(C9,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D9)&gt;0,N(VLOOKUP(C9,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A9,TIPOS!$A:$C,3,FALSE),"")="Sí",B9=""),"Falta el N° de entrega",IF(N(I9)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -784,7 +787,7 @@
         <v/>
       </c>
       <c r="H10" s="9">
-        <f>IF(A10="","",IFERROR(VLOOKUP(A10,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A10="","",IFERROR(IF(VLOOKUP(A10,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A10,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I10" s="10">
@@ -800,7 +803,7 @@
         <v/>
       </c>
       <c r="L10" s="9">
-        <f>IF(AND(A10="",C10=""),"",IF(A10="","Falta el tipo",IF(C10="","Falta el código",IF(ISNA(MATCH(C10,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D10)&gt;0,N(VLOOKUP(C10,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A10,TIPOS!$A:$C,3,FALSE),"")="Sí",B10=""),"Falta el N° de entrega",IF(N(I10)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A10="",C10=""),"",IF(A10="","Falta el tipo",IF(H10="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C10="","Falta el código",IF(ISNA(MATCH(C10,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D10)&gt;0,N(VLOOKUP(C10,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A10,TIPOS!$A:$C,3,FALSE),"")="Sí",B10=""),"Falta el N° de entrega",IF(N(I10)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -816,7 +819,7 @@
         <v/>
       </c>
       <c r="H11" s="9">
-        <f>IF(A11="","",IFERROR(VLOOKUP(A11,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A11="","",IFERROR(IF(VLOOKUP(A11,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A11,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I11" s="10">
@@ -832,7 +835,7 @@
         <v/>
       </c>
       <c r="L11" s="9">
-        <f>IF(AND(A11="",C11=""),"",IF(A11="","Falta el tipo",IF(C11="","Falta el código",IF(ISNA(MATCH(C11,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D11)&gt;0,N(VLOOKUP(C11,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A11,TIPOS!$A:$C,3,FALSE),"")="Sí",B11=""),"Falta el N° de entrega",IF(N(I11)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A11="",C11=""),"",IF(A11="","Falta el tipo",IF(H11="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C11="","Falta el código",IF(ISNA(MATCH(C11,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D11)&gt;0,N(VLOOKUP(C11,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A11,TIPOS!$A:$C,3,FALSE),"")="Sí",B11=""),"Falta el N° de entrega",IF(N(I11)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -848,7 +851,7 @@
         <v/>
       </c>
       <c r="H12" s="9">
-        <f>IF(A12="","",IFERROR(VLOOKUP(A12,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A12="","",IFERROR(IF(VLOOKUP(A12,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A12,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I12" s="10">
@@ -864,7 +867,7 @@
         <v/>
       </c>
       <c r="L12" s="9">
-        <f>IF(AND(A12="",C12=""),"",IF(A12="","Falta el tipo",IF(C12="","Falta el código",IF(ISNA(MATCH(C12,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D12)&gt;0,N(VLOOKUP(C12,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A12,TIPOS!$A:$C,3,FALSE),"")="Sí",B12=""),"Falta el N° de entrega",IF(N(I12)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A12="",C12=""),"",IF(A12="","Falta el tipo",IF(H12="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C12="","Falta el código",IF(ISNA(MATCH(C12,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D12)&gt;0,N(VLOOKUP(C12,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A12,TIPOS!$A:$C,3,FALSE),"")="Sí",B12=""),"Falta el N° de entrega",IF(N(I12)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -880,7 +883,7 @@
         <v/>
       </c>
       <c r="H13" s="9">
-        <f>IF(A13="","",IFERROR(VLOOKUP(A13,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A13="","",IFERROR(IF(VLOOKUP(A13,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A13,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I13" s="10">
@@ -896,7 +899,7 @@
         <v/>
       </c>
       <c r="L13" s="9">
-        <f>IF(AND(A13="",C13=""),"",IF(A13="","Falta el tipo",IF(C13="","Falta el código",IF(ISNA(MATCH(C13,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D13)&gt;0,N(VLOOKUP(C13,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A13,TIPOS!$A:$C,3,FALSE),"")="Sí",B13=""),"Falta el N° de entrega",IF(N(I13)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A13="",C13=""),"",IF(A13="","Falta el tipo",IF(H13="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C13="","Falta el código",IF(ISNA(MATCH(C13,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D13)&gt;0,N(VLOOKUP(C13,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A13,TIPOS!$A:$C,3,FALSE),"")="Sí",B13=""),"Falta el N° de entrega",IF(N(I13)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -912,7 +915,7 @@
         <v/>
       </c>
       <c r="H14" s="9">
-        <f>IF(A14="","",IFERROR(VLOOKUP(A14,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A14="","",IFERROR(IF(VLOOKUP(A14,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A14,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I14" s="10">
@@ -928,7 +931,7 @@
         <v/>
       </c>
       <c r="L14" s="9">
-        <f>IF(AND(A14="",C14=""),"",IF(A14="","Falta el tipo",IF(C14="","Falta el código",IF(ISNA(MATCH(C14,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D14)&gt;0,N(VLOOKUP(C14,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A14,TIPOS!$A:$C,3,FALSE),"")="Sí",B14=""),"Falta el N° de entrega",IF(N(I14)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A14="",C14=""),"",IF(A14="","Falta el tipo",IF(H14="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C14="","Falta el código",IF(ISNA(MATCH(C14,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D14)&gt;0,N(VLOOKUP(C14,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A14,TIPOS!$A:$C,3,FALSE),"")="Sí",B14=""),"Falta el N° de entrega",IF(N(I14)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -944,7 +947,7 @@
         <v/>
       </c>
       <c r="H15" s="9">
-        <f>IF(A15="","",IFERROR(VLOOKUP(A15,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A15="","",IFERROR(IF(VLOOKUP(A15,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A15,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I15" s="10">
@@ -960,7 +963,7 @@
         <v/>
       </c>
       <c r="L15" s="9">
-        <f>IF(AND(A15="",C15=""),"",IF(A15="","Falta el tipo",IF(C15="","Falta el código",IF(ISNA(MATCH(C15,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D15)&gt;0,N(VLOOKUP(C15,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A15,TIPOS!$A:$C,3,FALSE),"")="Sí",B15=""),"Falta el N° de entrega",IF(N(I15)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A15="",C15=""),"",IF(A15="","Falta el tipo",IF(H15="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C15="","Falta el código",IF(ISNA(MATCH(C15,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D15)&gt;0,N(VLOOKUP(C15,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A15,TIPOS!$A:$C,3,FALSE),"")="Sí",B15=""),"Falta el N° de entrega",IF(N(I15)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -976,7 +979,7 @@
         <v/>
       </c>
       <c r="H16" s="9">
-        <f>IF(A16="","",IFERROR(VLOOKUP(A16,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A16="","",IFERROR(IF(VLOOKUP(A16,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A16,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I16" s="10">
@@ -992,7 +995,7 @@
         <v/>
       </c>
       <c r="L16" s="9">
-        <f>IF(AND(A16="",C16=""),"",IF(A16="","Falta el tipo",IF(C16="","Falta el código",IF(ISNA(MATCH(C16,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D16)&gt;0,N(VLOOKUP(C16,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A16,TIPOS!$A:$C,3,FALSE),"")="Sí",B16=""),"Falta el N° de entrega",IF(N(I16)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A16="",C16=""),"",IF(A16="","Falta el tipo",IF(H16="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C16="","Falta el código",IF(ISNA(MATCH(C16,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D16)&gt;0,N(VLOOKUP(C16,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A16,TIPOS!$A:$C,3,FALSE),"")="Sí",B16=""),"Falta el N° de entrega",IF(N(I16)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -1008,7 +1011,7 @@
         <v/>
       </c>
       <c r="H17" s="9">
-        <f>IF(A17="","",IFERROR(VLOOKUP(A17,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A17="","",IFERROR(IF(VLOOKUP(A17,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A17,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I17" s="10">
@@ -1024,7 +1027,7 @@
         <v/>
       </c>
       <c r="L17" s="9">
-        <f>IF(AND(A17="",C17=""),"",IF(A17="","Falta el tipo",IF(C17="","Falta el código",IF(ISNA(MATCH(C17,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D17)&gt;0,N(VLOOKUP(C17,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A17,TIPOS!$A:$C,3,FALSE),"")="Sí",B17=""),"Falta el N° de entrega",IF(N(I17)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A17="",C17=""),"",IF(A17="","Falta el tipo",IF(H17="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C17="","Falta el código",IF(ISNA(MATCH(C17,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D17)&gt;0,N(VLOOKUP(C17,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A17,TIPOS!$A:$C,3,FALSE),"")="Sí",B17=""),"Falta el N° de entrega",IF(N(I17)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -1040,7 +1043,7 @@
         <v/>
       </c>
       <c r="H18" s="9">
-        <f>IF(A18="","",IFERROR(VLOOKUP(A18,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A18="","",IFERROR(IF(VLOOKUP(A18,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A18,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I18" s="10">
@@ -1056,7 +1059,7 @@
         <v/>
       </c>
       <c r="L18" s="9">
-        <f>IF(AND(A18="",C18=""),"",IF(A18="","Falta el tipo",IF(C18="","Falta el código",IF(ISNA(MATCH(C18,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D18)&gt;0,N(VLOOKUP(C18,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A18,TIPOS!$A:$C,3,FALSE),"")="Sí",B18=""),"Falta el N° de entrega",IF(N(I18)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A18="",C18=""),"",IF(A18="","Falta el tipo",IF(H18="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C18="","Falta el código",IF(ISNA(MATCH(C18,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D18)&gt;0,N(VLOOKUP(C18,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A18,TIPOS!$A:$C,3,FALSE),"")="Sí",B18=""),"Falta el N° de entrega",IF(N(I18)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -1072,7 +1075,7 @@
         <v/>
       </c>
       <c r="H19" s="9">
-        <f>IF(A19="","",IFERROR(VLOOKUP(A19,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A19="","",IFERROR(IF(VLOOKUP(A19,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A19,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I19" s="10">
@@ -1088,7 +1091,7 @@
         <v/>
       </c>
       <c r="L19" s="9">
-        <f>IF(AND(A19="",C19=""),"",IF(A19="","Falta el tipo",IF(C19="","Falta el código",IF(ISNA(MATCH(C19,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D19)&gt;0,N(VLOOKUP(C19,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A19,TIPOS!$A:$C,3,FALSE),"")="Sí",B19=""),"Falta el N° de entrega",IF(N(I19)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A19="",C19=""),"",IF(A19="","Falta el tipo",IF(H19="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C19="","Falta el código",IF(ISNA(MATCH(C19,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D19)&gt;0,N(VLOOKUP(C19,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A19,TIPOS!$A:$C,3,FALSE),"")="Sí",B19=""),"Falta el N° de entrega",IF(N(I19)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -1104,7 +1107,7 @@
         <v/>
       </c>
       <c r="H20" s="9">
-        <f>IF(A20="","",IFERROR(VLOOKUP(A20,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A20="","",IFERROR(IF(VLOOKUP(A20,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A20,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I20" s="10">
@@ -1120,7 +1123,7 @@
         <v/>
       </c>
       <c r="L20" s="9">
-        <f>IF(AND(A20="",C20=""),"",IF(A20="","Falta el tipo",IF(C20="","Falta el código",IF(ISNA(MATCH(C20,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D20)&gt;0,N(VLOOKUP(C20,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A20,TIPOS!$A:$C,3,FALSE),"")="Sí",B20=""),"Falta el N° de entrega",IF(N(I20)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A20="",C20=""),"",IF(A20="","Falta el tipo",IF(H20="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C20="","Falta el código",IF(ISNA(MATCH(C20,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D20)&gt;0,N(VLOOKUP(C20,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A20,TIPOS!$A:$C,3,FALSE),"")="Sí",B20=""),"Falta el N° de entrega",IF(N(I20)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -1136,7 +1139,7 @@
         <v/>
       </c>
       <c r="H21" s="9">
-        <f>IF(A21="","",IFERROR(VLOOKUP(A21,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A21="","",IFERROR(IF(VLOOKUP(A21,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A21,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I21" s="10">
@@ -1152,7 +1155,7 @@
         <v/>
       </c>
       <c r="L21" s="9">
-        <f>IF(AND(A21="",C21=""),"",IF(A21="","Falta el tipo",IF(C21="","Falta el código",IF(ISNA(MATCH(C21,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D21)&gt;0,N(VLOOKUP(C21,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A21,TIPOS!$A:$C,3,FALSE),"")="Sí",B21=""),"Falta el N° de entrega",IF(N(I21)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A21="",C21=""),"",IF(A21="","Falta el tipo",IF(H21="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C21="","Falta el código",IF(ISNA(MATCH(C21,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D21)&gt;0,N(VLOOKUP(C21,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A21,TIPOS!$A:$C,3,FALSE),"")="Sí",B21=""),"Falta el N° de entrega",IF(N(I21)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -1168,7 +1171,7 @@
         <v/>
       </c>
       <c r="H22" s="9">
-        <f>IF(A22="","",IFERROR(VLOOKUP(A22,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A22="","",IFERROR(IF(VLOOKUP(A22,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A22,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I22" s="10">
@@ -1184,7 +1187,7 @@
         <v/>
       </c>
       <c r="L22" s="9">
-        <f>IF(AND(A22="",C22=""),"",IF(A22="","Falta el tipo",IF(C22="","Falta el código",IF(ISNA(MATCH(C22,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D22)&gt;0,N(VLOOKUP(C22,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A22,TIPOS!$A:$C,3,FALSE),"")="Sí",B22=""),"Falta el N° de entrega",IF(N(I22)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A22="",C22=""),"",IF(A22="","Falta el tipo",IF(H22="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C22="","Falta el código",IF(ISNA(MATCH(C22,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D22)&gt;0,N(VLOOKUP(C22,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A22,TIPOS!$A:$C,3,FALSE),"")="Sí",B22=""),"Falta el N° de entrega",IF(N(I22)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -1200,7 +1203,7 @@
         <v/>
       </c>
       <c r="H23" s="9">
-        <f>IF(A23="","",IFERROR(VLOOKUP(A23,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A23="","",IFERROR(IF(VLOOKUP(A23,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A23,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I23" s="10">
@@ -1216,7 +1219,7 @@
         <v/>
       </c>
       <c r="L23" s="9">
-        <f>IF(AND(A23="",C23=""),"",IF(A23="","Falta el tipo",IF(C23="","Falta el código",IF(ISNA(MATCH(C23,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D23)&gt;0,N(VLOOKUP(C23,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A23,TIPOS!$A:$C,3,FALSE),"")="Sí",B23=""),"Falta el N° de entrega",IF(N(I23)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A23="",C23=""),"",IF(A23="","Falta el tipo",IF(H23="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C23="","Falta el código",IF(ISNA(MATCH(C23,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D23)&gt;0,N(VLOOKUP(C23,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A23,TIPOS!$A:$C,3,FALSE),"")="Sí",B23=""),"Falta el N° de entrega",IF(N(I23)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -1232,7 +1235,7 @@
         <v/>
       </c>
       <c r="H24" s="9">
-        <f>IF(A24="","",IFERROR(VLOOKUP(A24,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A24="","",IFERROR(IF(VLOOKUP(A24,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A24,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I24" s="10">
@@ -1248,7 +1251,7 @@
         <v/>
       </c>
       <c r="L24" s="9">
-        <f>IF(AND(A24="",C24=""),"",IF(A24="","Falta el tipo",IF(C24="","Falta el código",IF(ISNA(MATCH(C24,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D24)&gt;0,N(VLOOKUP(C24,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A24,TIPOS!$A:$C,3,FALSE),"")="Sí",B24=""),"Falta el N° de entrega",IF(N(I24)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A24="",C24=""),"",IF(A24="","Falta el tipo",IF(H24="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C24="","Falta el código",IF(ISNA(MATCH(C24,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D24)&gt;0,N(VLOOKUP(C24,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A24,TIPOS!$A:$C,3,FALSE),"")="Sí",B24=""),"Falta el N° de entrega",IF(N(I24)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -1264,7 +1267,7 @@
         <v/>
       </c>
       <c r="H25" s="9">
-        <f>IF(A25="","",IFERROR(VLOOKUP(A25,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A25="","",IFERROR(IF(VLOOKUP(A25,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A25,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I25" s="10">
@@ -1280,7 +1283,7 @@
         <v/>
       </c>
       <c r="L25" s="9">
-        <f>IF(AND(A25="",C25=""),"",IF(A25="","Falta el tipo",IF(C25="","Falta el código",IF(ISNA(MATCH(C25,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D25)&gt;0,N(VLOOKUP(C25,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A25,TIPOS!$A:$C,3,FALSE),"")="Sí",B25=""),"Falta el N° de entrega",IF(N(I25)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A25="",C25=""),"",IF(A25="","Falta el tipo",IF(H25="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C25="","Falta el código",IF(ISNA(MATCH(C25,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D25)&gt;0,N(VLOOKUP(C25,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A25,TIPOS!$A:$C,3,FALSE),"")="Sí",B25=""),"Falta el N° de entrega",IF(N(I25)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -1296,7 +1299,7 @@
         <v/>
       </c>
       <c r="H26" s="9">
-        <f>IF(A26="","",IFERROR(VLOOKUP(A26,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A26="","",IFERROR(IF(VLOOKUP(A26,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A26,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I26" s="10">
@@ -1312,7 +1315,7 @@
         <v/>
       </c>
       <c r="L26" s="9">
-        <f>IF(AND(A26="",C26=""),"",IF(A26="","Falta el tipo",IF(C26="","Falta el código",IF(ISNA(MATCH(C26,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D26)&gt;0,N(VLOOKUP(C26,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A26,TIPOS!$A:$C,3,FALSE),"")="Sí",B26=""),"Falta el N° de entrega",IF(N(I26)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A26="",C26=""),"",IF(A26="","Falta el tipo",IF(H26="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C26="","Falta el código",IF(ISNA(MATCH(C26,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D26)&gt;0,N(VLOOKUP(C26,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A26,TIPOS!$A:$C,3,FALSE),"")="Sí",B26=""),"Falta el N° de entrega",IF(N(I26)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -1328,7 +1331,7 @@
         <v/>
       </c>
       <c r="H27" s="9">
-        <f>IF(A27="","",IFERROR(VLOOKUP(A27,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A27="","",IFERROR(IF(VLOOKUP(A27,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A27,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I27" s="10">
@@ -1344,7 +1347,7 @@
         <v/>
       </c>
       <c r="L27" s="9">
-        <f>IF(AND(A27="",C27=""),"",IF(A27="","Falta el tipo",IF(C27="","Falta el código",IF(ISNA(MATCH(C27,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D27)&gt;0,N(VLOOKUP(C27,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A27,TIPOS!$A:$C,3,FALSE),"")="Sí",B27=""),"Falta el N° de entrega",IF(N(I27)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A27="",C27=""),"",IF(A27="","Falta el tipo",IF(H27="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C27="","Falta el código",IF(ISNA(MATCH(C27,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D27)&gt;0,N(VLOOKUP(C27,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A27,TIPOS!$A:$C,3,FALSE),"")="Sí",B27=""),"Falta el N° de entrega",IF(N(I27)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -1360,7 +1363,7 @@
         <v/>
       </c>
       <c r="H28" s="9">
-        <f>IF(A28="","",IFERROR(VLOOKUP(A28,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A28="","",IFERROR(IF(VLOOKUP(A28,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A28,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I28" s="10">
@@ -1376,7 +1379,7 @@
         <v/>
       </c>
       <c r="L28" s="9">
-        <f>IF(AND(A28="",C28=""),"",IF(A28="","Falta el tipo",IF(C28="","Falta el código",IF(ISNA(MATCH(C28,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D28)&gt;0,N(VLOOKUP(C28,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A28,TIPOS!$A:$C,3,FALSE),"")="Sí",B28=""),"Falta el N° de entrega",IF(N(I28)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A28="",C28=""),"",IF(A28="","Falta el tipo",IF(H28="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C28="","Falta el código",IF(ISNA(MATCH(C28,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D28)&gt;0,N(VLOOKUP(C28,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A28,TIPOS!$A:$C,3,FALSE),"")="Sí",B28=""),"Falta el N° de entrega",IF(N(I28)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -1392,7 +1395,7 @@
         <v/>
       </c>
       <c r="H29" s="9">
-        <f>IF(A29="","",IFERROR(VLOOKUP(A29,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A29="","",IFERROR(IF(VLOOKUP(A29,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A29,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I29" s="10">
@@ -1408,7 +1411,7 @@
         <v/>
       </c>
       <c r="L29" s="9">
-        <f>IF(AND(A29="",C29=""),"",IF(A29="","Falta el tipo",IF(C29="","Falta el código",IF(ISNA(MATCH(C29,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D29)&gt;0,N(VLOOKUP(C29,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A29,TIPOS!$A:$C,3,FALSE),"")="Sí",B29=""),"Falta el N° de entrega",IF(N(I29)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A29="",C29=""),"",IF(A29="","Falta el tipo",IF(H29="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C29="","Falta el código",IF(ISNA(MATCH(C29,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D29)&gt;0,N(VLOOKUP(C29,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A29,TIPOS!$A:$C,3,FALSE),"")="Sí",B29=""),"Falta el N° de entrega",IF(N(I29)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -1424,7 +1427,7 @@
         <v/>
       </c>
       <c r="H30" s="9">
-        <f>IF(A30="","",IFERROR(VLOOKUP(A30,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A30="","",IFERROR(IF(VLOOKUP(A30,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A30,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I30" s="10">
@@ -1440,7 +1443,7 @@
         <v/>
       </c>
       <c r="L30" s="9">
-        <f>IF(AND(A30="",C30=""),"",IF(A30="","Falta el tipo",IF(C30="","Falta el código",IF(ISNA(MATCH(C30,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D30)&gt;0,N(VLOOKUP(C30,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A30,TIPOS!$A:$C,3,FALSE),"")="Sí",B30=""),"Falta el N° de entrega",IF(N(I30)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A30="",C30=""),"",IF(A30="","Falta el tipo",IF(H30="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C30="","Falta el código",IF(ISNA(MATCH(C30,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D30)&gt;0,N(VLOOKUP(C30,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A30,TIPOS!$A:$C,3,FALSE),"")="Sí",B30=""),"Falta el N° de entrega",IF(N(I30)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -1456,7 +1459,7 @@
         <v/>
       </c>
       <c r="H31" s="9">
-        <f>IF(A31="","",IFERROR(VLOOKUP(A31,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A31="","",IFERROR(IF(VLOOKUP(A31,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A31,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I31" s="10">
@@ -1472,7 +1475,7 @@
         <v/>
       </c>
       <c r="L31" s="9">
-        <f>IF(AND(A31="",C31=""),"",IF(A31="","Falta el tipo",IF(C31="","Falta el código",IF(ISNA(MATCH(C31,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D31)&gt;0,N(VLOOKUP(C31,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A31,TIPOS!$A:$C,3,FALSE),"")="Sí",B31=""),"Falta el N° de entrega",IF(N(I31)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A31="",C31=""),"",IF(A31="","Falta el tipo",IF(H31="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C31="","Falta el código",IF(ISNA(MATCH(C31,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D31)&gt;0,N(VLOOKUP(C31,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A31,TIPOS!$A:$C,3,FALSE),"")="Sí",B31=""),"Falta el N° de entrega",IF(N(I31)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -1488,7 +1491,7 @@
         <v/>
       </c>
       <c r="H32" s="9">
-        <f>IF(A32="","",IFERROR(VLOOKUP(A32,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A32="","",IFERROR(IF(VLOOKUP(A32,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A32,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I32" s="10">
@@ -1504,7 +1507,7 @@
         <v/>
       </c>
       <c r="L32" s="9">
-        <f>IF(AND(A32="",C32=""),"",IF(A32="","Falta el tipo",IF(C32="","Falta el código",IF(ISNA(MATCH(C32,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D32)&gt;0,N(VLOOKUP(C32,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A32,TIPOS!$A:$C,3,FALSE),"")="Sí",B32=""),"Falta el N° de entrega",IF(N(I32)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A32="",C32=""),"",IF(A32="","Falta el tipo",IF(H32="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C32="","Falta el código",IF(ISNA(MATCH(C32,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D32)&gt;0,N(VLOOKUP(C32,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A32,TIPOS!$A:$C,3,FALSE),"")="Sí",B32=""),"Falta el N° de entrega",IF(N(I32)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -1520,7 +1523,7 @@
         <v/>
       </c>
       <c r="H33" s="9">
-        <f>IF(A33="","",IFERROR(VLOOKUP(A33,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A33="","",IFERROR(IF(VLOOKUP(A33,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A33,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I33" s="10">
@@ -1536,7 +1539,7 @@
         <v/>
       </c>
       <c r="L33" s="9">
-        <f>IF(AND(A33="",C33=""),"",IF(A33="","Falta el tipo",IF(C33="","Falta el código",IF(ISNA(MATCH(C33,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D33)&gt;0,N(VLOOKUP(C33,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A33,TIPOS!$A:$C,3,FALSE),"")="Sí",B33=""),"Falta el N° de entrega",IF(N(I33)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A33="",C33=""),"",IF(A33="","Falta el tipo",IF(H33="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C33="","Falta el código",IF(ISNA(MATCH(C33,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D33)&gt;0,N(VLOOKUP(C33,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A33,TIPOS!$A:$C,3,FALSE),"")="Sí",B33=""),"Falta el N° de entrega",IF(N(I33)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -1552,7 +1555,7 @@
         <v/>
       </c>
       <c r="H34" s="9">
-        <f>IF(A34="","",IFERROR(VLOOKUP(A34,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A34="","",IFERROR(IF(VLOOKUP(A34,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A34,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I34" s="10">
@@ -1568,7 +1571,7 @@
         <v/>
       </c>
       <c r="L34" s="9">
-        <f>IF(AND(A34="",C34=""),"",IF(A34="","Falta el tipo",IF(C34="","Falta el código",IF(ISNA(MATCH(C34,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D34)&gt;0,N(VLOOKUP(C34,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A34,TIPOS!$A:$C,3,FALSE),"")="Sí",B34=""),"Falta el N° de entrega",IF(N(I34)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A34="",C34=""),"",IF(A34="","Falta el tipo",IF(H34="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C34="","Falta el código",IF(ISNA(MATCH(C34,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D34)&gt;0,N(VLOOKUP(C34,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A34,TIPOS!$A:$C,3,FALSE),"")="Sí",B34=""),"Falta el N° de entrega",IF(N(I34)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -1584,7 +1587,7 @@
         <v/>
       </c>
       <c r="H35" s="9">
-        <f>IF(A35="","",IFERROR(VLOOKUP(A35,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A35="","",IFERROR(IF(VLOOKUP(A35,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A35,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I35" s="10">
@@ -1600,7 +1603,7 @@
         <v/>
       </c>
       <c r="L35" s="9">
-        <f>IF(AND(A35="",C35=""),"",IF(A35="","Falta el tipo",IF(C35="","Falta el código",IF(ISNA(MATCH(C35,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D35)&gt;0,N(VLOOKUP(C35,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A35,TIPOS!$A:$C,3,FALSE),"")="Sí",B35=""),"Falta el N° de entrega",IF(N(I35)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A35="",C35=""),"",IF(A35="","Falta el tipo",IF(H35="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C35="","Falta el código",IF(ISNA(MATCH(C35,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D35)&gt;0,N(VLOOKUP(C35,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A35,TIPOS!$A:$C,3,FALSE),"")="Sí",B35=""),"Falta el N° de entrega",IF(N(I35)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -1616,7 +1619,7 @@
         <v/>
       </c>
       <c r="H36" s="9">
-        <f>IF(A36="","",IFERROR(VLOOKUP(A36,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A36="","",IFERROR(IF(VLOOKUP(A36,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A36,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I36" s="10">
@@ -1632,7 +1635,7 @@
         <v/>
       </c>
       <c r="L36" s="9">
-        <f>IF(AND(A36="",C36=""),"",IF(A36="","Falta el tipo",IF(C36="","Falta el código",IF(ISNA(MATCH(C36,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D36)&gt;0,N(VLOOKUP(C36,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A36,TIPOS!$A:$C,3,FALSE),"")="Sí",B36=""),"Falta el N° de entrega",IF(N(I36)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A36="",C36=""),"",IF(A36="","Falta el tipo",IF(H36="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C36="","Falta el código",IF(ISNA(MATCH(C36,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D36)&gt;0,N(VLOOKUP(C36,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A36,TIPOS!$A:$C,3,FALSE),"")="Sí",B36=""),"Falta el N° de entrega",IF(N(I36)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -1648,7 +1651,7 @@
         <v/>
       </c>
       <c r="H37" s="9">
-        <f>IF(A37="","",IFERROR(VLOOKUP(A37,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A37="","",IFERROR(IF(VLOOKUP(A37,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A37,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I37" s="10">
@@ -1664,7 +1667,7 @@
         <v/>
       </c>
       <c r="L37" s="9">
-        <f>IF(AND(A37="",C37=""),"",IF(A37="","Falta el tipo",IF(C37="","Falta el código",IF(ISNA(MATCH(C37,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D37)&gt;0,N(VLOOKUP(C37,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A37,TIPOS!$A:$C,3,FALSE),"")="Sí",B37=""),"Falta el N° de entrega",IF(N(I37)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A37="",C37=""),"",IF(A37="","Falta el tipo",IF(H37="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C37="","Falta el código",IF(ISNA(MATCH(C37,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D37)&gt;0,N(VLOOKUP(C37,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A37,TIPOS!$A:$C,3,FALSE),"")="Sí",B37=""),"Falta el N° de entrega",IF(N(I37)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -1680,7 +1683,7 @@
         <v/>
       </c>
       <c r="H38" s="9">
-        <f>IF(A38="","",IFERROR(VLOOKUP(A38,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A38="","",IFERROR(IF(VLOOKUP(A38,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A38,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I38" s="10">
@@ -1696,7 +1699,7 @@
         <v/>
       </c>
       <c r="L38" s="9">
-        <f>IF(AND(A38="",C38=""),"",IF(A38="","Falta el tipo",IF(C38="","Falta el código",IF(ISNA(MATCH(C38,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D38)&gt;0,N(VLOOKUP(C38,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A38,TIPOS!$A:$C,3,FALSE),"")="Sí",B38=""),"Falta el N° de entrega",IF(N(I38)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A38="",C38=""),"",IF(A38="","Falta el tipo",IF(H38="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C38="","Falta el código",IF(ISNA(MATCH(C38,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D38)&gt;0,N(VLOOKUP(C38,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A38,TIPOS!$A:$C,3,FALSE),"")="Sí",B38=""),"Falta el N° de entrega",IF(N(I38)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -1712,7 +1715,7 @@
         <v/>
       </c>
       <c r="H39" s="9">
-        <f>IF(A39="","",IFERROR(VLOOKUP(A39,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A39="","",IFERROR(IF(VLOOKUP(A39,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A39,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I39" s="10">
@@ -1728,7 +1731,7 @@
         <v/>
       </c>
       <c r="L39" s="9">
-        <f>IF(AND(A39="",C39=""),"",IF(A39="","Falta el tipo",IF(C39="","Falta el código",IF(ISNA(MATCH(C39,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D39)&gt;0,N(VLOOKUP(C39,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A39,TIPOS!$A:$C,3,FALSE),"")="Sí",B39=""),"Falta el N° de entrega",IF(N(I39)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A39="",C39=""),"",IF(A39="","Falta el tipo",IF(H39="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C39="","Falta el código",IF(ISNA(MATCH(C39,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D39)&gt;0,N(VLOOKUP(C39,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A39,TIPOS!$A:$C,3,FALSE),"")="Sí",B39=""),"Falta el N° de entrega",IF(N(I39)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -1744,7 +1747,7 @@
         <v/>
       </c>
       <c r="H40" s="9">
-        <f>IF(A40="","",IFERROR(VLOOKUP(A40,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A40="","",IFERROR(IF(VLOOKUP(A40,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A40,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I40" s="10">
@@ -1760,7 +1763,7 @@
         <v/>
       </c>
       <c r="L40" s="9">
-        <f>IF(AND(A40="",C40=""),"",IF(A40="","Falta el tipo",IF(C40="","Falta el código",IF(ISNA(MATCH(C40,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D40)&gt;0,N(VLOOKUP(C40,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A40,TIPOS!$A:$C,3,FALSE),"")="Sí",B40=""),"Falta el N° de entrega",IF(N(I40)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A40="",C40=""),"",IF(A40="","Falta el tipo",IF(H40="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C40="","Falta el código",IF(ISNA(MATCH(C40,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D40)&gt;0,N(VLOOKUP(C40,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A40,TIPOS!$A:$C,3,FALSE),"")="Sí",B40=""),"Falta el N° de entrega",IF(N(I40)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -1776,7 +1779,7 @@
         <v/>
       </c>
       <c r="H41" s="9">
-        <f>IF(A41="","",IFERROR(VLOOKUP(A41,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A41="","",IFERROR(IF(VLOOKUP(A41,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A41,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I41" s="10">
@@ -1792,7 +1795,7 @@
         <v/>
       </c>
       <c r="L41" s="9">
-        <f>IF(AND(A41="",C41=""),"",IF(A41="","Falta el tipo",IF(C41="","Falta el código",IF(ISNA(MATCH(C41,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D41)&gt;0,N(VLOOKUP(C41,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A41,TIPOS!$A:$C,3,FALSE),"")="Sí",B41=""),"Falta el N° de entrega",IF(N(I41)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A41="",C41=""),"",IF(A41="","Falta el tipo",IF(H41="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C41="","Falta el código",IF(ISNA(MATCH(C41,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D41)&gt;0,N(VLOOKUP(C41,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A41,TIPOS!$A:$C,3,FALSE),"")="Sí",B41=""),"Falta el N° de entrega",IF(N(I41)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -1808,7 +1811,7 @@
         <v/>
       </c>
       <c r="H42" s="9">
-        <f>IF(A42="","",IFERROR(VLOOKUP(A42,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A42="","",IFERROR(IF(VLOOKUP(A42,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A42,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I42" s="10">
@@ -1824,7 +1827,7 @@
         <v/>
       </c>
       <c r="L42" s="9">
-        <f>IF(AND(A42="",C42=""),"",IF(A42="","Falta el tipo",IF(C42="","Falta el código",IF(ISNA(MATCH(C42,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D42)&gt;0,N(VLOOKUP(C42,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A42,TIPOS!$A:$C,3,FALSE),"")="Sí",B42=""),"Falta el N° de entrega",IF(N(I42)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A42="",C42=""),"",IF(A42="","Falta el tipo",IF(H42="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C42="","Falta el código",IF(ISNA(MATCH(C42,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D42)&gt;0,N(VLOOKUP(C42,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A42,TIPOS!$A:$C,3,FALSE),"")="Sí",B42=""),"Falta el N° de entrega",IF(N(I42)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -1840,7 +1843,7 @@
         <v/>
       </c>
       <c r="H43" s="9">
-        <f>IF(A43="","",IFERROR(VLOOKUP(A43,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A43="","",IFERROR(IF(VLOOKUP(A43,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A43,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I43" s="10">
@@ -1856,7 +1859,7 @@
         <v/>
       </c>
       <c r="L43" s="9">
-        <f>IF(AND(A43="",C43=""),"",IF(A43="","Falta el tipo",IF(C43="","Falta el código",IF(ISNA(MATCH(C43,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D43)&gt;0,N(VLOOKUP(C43,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A43,TIPOS!$A:$C,3,FALSE),"")="Sí",B43=""),"Falta el N° de entrega",IF(N(I43)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A43="",C43=""),"",IF(A43="","Falta el tipo",IF(H43="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C43="","Falta el código",IF(ISNA(MATCH(C43,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D43)&gt;0,N(VLOOKUP(C43,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A43,TIPOS!$A:$C,3,FALSE),"")="Sí",B43=""),"Falta el N° de entrega",IF(N(I43)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -1872,7 +1875,7 @@
         <v/>
       </c>
       <c r="H44" s="9">
-        <f>IF(A44="","",IFERROR(VLOOKUP(A44,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A44="","",IFERROR(IF(VLOOKUP(A44,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A44,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I44" s="10">
@@ -1888,7 +1891,7 @@
         <v/>
       </c>
       <c r="L44" s="9">
-        <f>IF(AND(A44="",C44=""),"",IF(A44="","Falta el tipo",IF(C44="","Falta el código",IF(ISNA(MATCH(C44,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D44)&gt;0,N(VLOOKUP(C44,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A44,TIPOS!$A:$C,3,FALSE),"")="Sí",B44=""),"Falta el N° de entrega",IF(N(I44)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A44="",C44=""),"",IF(A44="","Falta el tipo",IF(H44="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C44="","Falta el código",IF(ISNA(MATCH(C44,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D44)&gt;0,N(VLOOKUP(C44,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A44,TIPOS!$A:$C,3,FALSE),"")="Sí",B44=""),"Falta el N° de entrega",IF(N(I44)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -1904,7 +1907,7 @@
         <v/>
       </c>
       <c r="H45" s="9">
-        <f>IF(A45="","",IFERROR(VLOOKUP(A45,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A45="","",IFERROR(IF(VLOOKUP(A45,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A45,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I45" s="10">
@@ -1920,7 +1923,7 @@
         <v/>
       </c>
       <c r="L45" s="9">
-        <f>IF(AND(A45="",C45=""),"",IF(A45="","Falta el tipo",IF(C45="","Falta el código",IF(ISNA(MATCH(C45,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D45)&gt;0,N(VLOOKUP(C45,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A45,TIPOS!$A:$C,3,FALSE),"")="Sí",B45=""),"Falta el N° de entrega",IF(N(I45)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A45="",C45=""),"",IF(A45="","Falta el tipo",IF(H45="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C45="","Falta el código",IF(ISNA(MATCH(C45,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D45)&gt;0,N(VLOOKUP(C45,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A45,TIPOS!$A:$C,3,FALSE),"")="Sí",B45=""),"Falta el N° de entrega",IF(N(I45)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -1936,7 +1939,7 @@
         <v/>
       </c>
       <c r="H46" s="9">
-        <f>IF(A46="","",IFERROR(VLOOKUP(A46,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A46="","",IFERROR(IF(VLOOKUP(A46,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A46,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I46" s="10">
@@ -1952,7 +1955,7 @@
         <v/>
       </c>
       <c r="L46" s="9">
-        <f>IF(AND(A46="",C46=""),"",IF(A46="","Falta el tipo",IF(C46="","Falta el código",IF(ISNA(MATCH(C46,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D46)&gt;0,N(VLOOKUP(C46,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A46,TIPOS!$A:$C,3,FALSE),"")="Sí",B46=""),"Falta el N° de entrega",IF(N(I46)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A46="",C46=""),"",IF(A46="","Falta el tipo",IF(H46="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C46="","Falta el código",IF(ISNA(MATCH(C46,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D46)&gt;0,N(VLOOKUP(C46,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A46,TIPOS!$A:$C,3,FALSE),"")="Sí",B46=""),"Falta el N° de entrega",IF(N(I46)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -1968,7 +1971,7 @@
         <v/>
       </c>
       <c r="H47" s="9">
-        <f>IF(A47="","",IFERROR(VLOOKUP(A47,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A47="","",IFERROR(IF(VLOOKUP(A47,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A47,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I47" s="10">
@@ -1984,7 +1987,7 @@
         <v/>
       </c>
       <c r="L47" s="9">
-        <f>IF(AND(A47="",C47=""),"",IF(A47="","Falta el tipo",IF(C47="","Falta el código",IF(ISNA(MATCH(C47,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D47)&gt;0,N(VLOOKUP(C47,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A47,TIPOS!$A:$C,3,FALSE),"")="Sí",B47=""),"Falta el N° de entrega",IF(N(I47)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A47="",C47=""),"",IF(A47="","Falta el tipo",IF(H47="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C47="","Falta el código",IF(ISNA(MATCH(C47,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D47)&gt;0,N(VLOOKUP(C47,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A47,TIPOS!$A:$C,3,FALSE),"")="Sí",B47=""),"Falta el N° de entrega",IF(N(I47)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -2000,7 +2003,7 @@
         <v/>
       </c>
       <c r="H48" s="9">
-        <f>IF(A48="","",IFERROR(VLOOKUP(A48,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A48="","",IFERROR(IF(VLOOKUP(A48,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A48,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I48" s="10">
@@ -2016,7 +2019,7 @@
         <v/>
       </c>
       <c r="L48" s="9">
-        <f>IF(AND(A48="",C48=""),"",IF(A48="","Falta el tipo",IF(C48="","Falta el código",IF(ISNA(MATCH(C48,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D48)&gt;0,N(VLOOKUP(C48,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A48,TIPOS!$A:$C,3,FALSE),"")="Sí",B48=""),"Falta el N° de entrega",IF(N(I48)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A48="",C48=""),"",IF(A48="","Falta el tipo",IF(H48="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C48="","Falta el código",IF(ISNA(MATCH(C48,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D48)&gt;0,N(VLOOKUP(C48,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A48,TIPOS!$A:$C,3,FALSE),"")="Sí",B48=""),"Falta el N° de entrega",IF(N(I48)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -2032,7 +2035,7 @@
         <v/>
       </c>
       <c r="H49" s="9">
-        <f>IF(A49="","",IFERROR(VLOOKUP(A49,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A49="","",IFERROR(IF(VLOOKUP(A49,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A49,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I49" s="10">
@@ -2048,7 +2051,7 @@
         <v/>
       </c>
       <c r="L49" s="9">
-        <f>IF(AND(A49="",C49=""),"",IF(A49="","Falta el tipo",IF(C49="","Falta el código",IF(ISNA(MATCH(C49,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D49)&gt;0,N(VLOOKUP(C49,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A49,TIPOS!$A:$C,3,FALSE),"")="Sí",B49=""),"Falta el N° de entrega",IF(N(I49)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A49="",C49=""),"",IF(A49="","Falta el tipo",IF(H49="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C49="","Falta el código",IF(ISNA(MATCH(C49,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D49)&gt;0,N(VLOOKUP(C49,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A49,TIPOS!$A:$C,3,FALSE),"")="Sí",B49=""),"Falta el N° de entrega",IF(N(I49)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -2064,7 +2067,7 @@
         <v/>
       </c>
       <c r="H50" s="9">
-        <f>IF(A50="","",IFERROR(VLOOKUP(A50,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A50="","",IFERROR(IF(VLOOKUP(A50,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A50,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I50" s="10">
@@ -2080,7 +2083,7 @@
         <v/>
       </c>
       <c r="L50" s="9">
-        <f>IF(AND(A50="",C50=""),"",IF(A50="","Falta el tipo",IF(C50="","Falta el código",IF(ISNA(MATCH(C50,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D50)&gt;0,N(VLOOKUP(C50,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A50,TIPOS!$A:$C,3,FALSE),"")="Sí",B50=""),"Falta el N° de entrega",IF(N(I50)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A50="",C50=""),"",IF(A50="","Falta el tipo",IF(H50="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C50="","Falta el código",IF(ISNA(MATCH(C50,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D50)&gt;0,N(VLOOKUP(C50,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A50,TIPOS!$A:$C,3,FALSE),"")="Sí",B50=""),"Falta el N° de entrega",IF(N(I50)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -2096,7 +2099,7 @@
         <v/>
       </c>
       <c r="H51" s="9">
-        <f>IF(A51="","",IFERROR(VLOOKUP(A51,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A51="","",IFERROR(IF(VLOOKUP(A51,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A51,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I51" s="10">
@@ -2112,7 +2115,7 @@
         <v/>
       </c>
       <c r="L51" s="9">
-        <f>IF(AND(A51="",C51=""),"",IF(A51="","Falta el tipo",IF(C51="","Falta el código",IF(ISNA(MATCH(C51,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D51)&gt;0,N(VLOOKUP(C51,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A51,TIPOS!$A:$C,3,FALSE),"")="Sí",B51=""),"Falta el N° de entrega",IF(N(I51)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A51="",C51=""),"",IF(A51="","Falta el tipo",IF(H51="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C51="","Falta el código",IF(ISNA(MATCH(C51,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D51)&gt;0,N(VLOOKUP(C51,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A51,TIPOS!$A:$C,3,FALSE),"")="Sí",B51=""),"Falta el N° de entrega",IF(N(I51)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -2128,7 +2131,7 @@
         <v/>
       </c>
       <c r="H52" s="9">
-        <f>IF(A52="","",IFERROR(VLOOKUP(A52,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A52="","",IFERROR(IF(VLOOKUP(A52,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A52,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I52" s="10">
@@ -2144,7 +2147,7 @@
         <v/>
       </c>
       <c r="L52" s="9">
-        <f>IF(AND(A52="",C52=""),"",IF(A52="","Falta el tipo",IF(C52="","Falta el código",IF(ISNA(MATCH(C52,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D52)&gt;0,N(VLOOKUP(C52,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A52,TIPOS!$A:$C,3,FALSE),"")="Sí",B52=""),"Falta el N° de entrega",IF(N(I52)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A52="",C52=""),"",IF(A52="","Falta el tipo",IF(H52="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C52="","Falta el código",IF(ISNA(MATCH(C52,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D52)&gt;0,N(VLOOKUP(C52,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A52,TIPOS!$A:$C,3,FALSE),"")="Sí",B52=""),"Falta el N° de entrega",IF(N(I52)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -2160,7 +2163,7 @@
         <v/>
       </c>
       <c r="H53" s="9">
-        <f>IF(A53="","",IFERROR(VLOOKUP(A53,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A53="","",IFERROR(IF(VLOOKUP(A53,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A53,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I53" s="10">
@@ -2176,7 +2179,7 @@
         <v/>
       </c>
       <c r="L53" s="9">
-        <f>IF(AND(A53="",C53=""),"",IF(A53="","Falta el tipo",IF(C53="","Falta el código",IF(ISNA(MATCH(C53,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D53)&gt;0,N(VLOOKUP(C53,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A53,TIPOS!$A:$C,3,FALSE),"")="Sí",B53=""),"Falta el N° de entrega",IF(N(I53)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A53="",C53=""),"",IF(A53="","Falta el tipo",IF(H53="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C53="","Falta el código",IF(ISNA(MATCH(C53,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D53)&gt;0,N(VLOOKUP(C53,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A53,TIPOS!$A:$C,3,FALSE),"")="Sí",B53=""),"Falta el N° de entrega",IF(N(I53)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -2192,7 +2195,7 @@
         <v/>
       </c>
       <c r="H54" s="9">
-        <f>IF(A54="","",IFERROR(VLOOKUP(A54,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A54="","",IFERROR(IF(VLOOKUP(A54,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A54,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I54" s="10">
@@ -2208,7 +2211,7 @@
         <v/>
       </c>
       <c r="L54" s="9">
-        <f>IF(AND(A54="",C54=""),"",IF(A54="","Falta el tipo",IF(C54="","Falta el código",IF(ISNA(MATCH(C54,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D54)&gt;0,N(VLOOKUP(C54,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A54,TIPOS!$A:$C,3,FALSE),"")="Sí",B54=""),"Falta el N° de entrega",IF(N(I54)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A54="",C54=""),"",IF(A54="","Falta el tipo",IF(H54="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C54="","Falta el código",IF(ISNA(MATCH(C54,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D54)&gt;0,N(VLOOKUP(C54,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A54,TIPOS!$A:$C,3,FALSE),"")="Sí",B54=""),"Falta el N° de entrega",IF(N(I54)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -2224,7 +2227,7 @@
         <v/>
       </c>
       <c r="H55" s="9">
-        <f>IF(A55="","",IFERROR(VLOOKUP(A55,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A55="","",IFERROR(IF(VLOOKUP(A55,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A55,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I55" s="10">
@@ -2240,7 +2243,7 @@
         <v/>
       </c>
       <c r="L55" s="9">
-        <f>IF(AND(A55="",C55=""),"",IF(A55="","Falta el tipo",IF(C55="","Falta el código",IF(ISNA(MATCH(C55,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D55)&gt;0,N(VLOOKUP(C55,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A55,TIPOS!$A:$C,3,FALSE),"")="Sí",B55=""),"Falta el N° de entrega",IF(N(I55)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A55="",C55=""),"",IF(A55="","Falta el tipo",IF(H55="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C55="","Falta el código",IF(ISNA(MATCH(C55,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D55)&gt;0,N(VLOOKUP(C55,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A55,TIPOS!$A:$C,3,FALSE),"")="Sí",B55=""),"Falta el N° de entrega",IF(N(I55)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -2256,7 +2259,7 @@
         <v/>
       </c>
       <c r="H56" s="9">
-        <f>IF(A56="","",IFERROR(VLOOKUP(A56,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A56="","",IFERROR(IF(VLOOKUP(A56,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A56,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I56" s="10">
@@ -2272,7 +2275,7 @@
         <v/>
       </c>
       <c r="L56" s="9">
-        <f>IF(AND(A56="",C56=""),"",IF(A56="","Falta el tipo",IF(C56="","Falta el código",IF(ISNA(MATCH(C56,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D56)&gt;0,N(VLOOKUP(C56,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A56,TIPOS!$A:$C,3,FALSE),"")="Sí",B56=""),"Falta el N° de entrega",IF(N(I56)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A56="",C56=""),"",IF(A56="","Falta el tipo",IF(H56="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C56="","Falta el código",IF(ISNA(MATCH(C56,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D56)&gt;0,N(VLOOKUP(C56,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A56,TIPOS!$A:$C,3,FALSE),"")="Sí",B56=""),"Falta el N° de entrega",IF(N(I56)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -2288,7 +2291,7 @@
         <v/>
       </c>
       <c r="H57" s="9">
-        <f>IF(A57="","",IFERROR(VLOOKUP(A57,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A57="","",IFERROR(IF(VLOOKUP(A57,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A57,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I57" s="10">
@@ -2304,7 +2307,7 @@
         <v/>
       </c>
       <c r="L57" s="9">
-        <f>IF(AND(A57="",C57=""),"",IF(A57="","Falta el tipo",IF(C57="","Falta el código",IF(ISNA(MATCH(C57,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D57)&gt;0,N(VLOOKUP(C57,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A57,TIPOS!$A:$C,3,FALSE),"")="Sí",B57=""),"Falta el N° de entrega",IF(N(I57)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A57="",C57=""),"",IF(A57="","Falta el tipo",IF(H57="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C57="","Falta el código",IF(ISNA(MATCH(C57,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D57)&gt;0,N(VLOOKUP(C57,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A57,TIPOS!$A:$C,3,FALSE),"")="Sí",B57=""),"Falta el N° de entrega",IF(N(I57)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -2320,7 +2323,7 @@
         <v/>
       </c>
       <c r="H58" s="9">
-        <f>IF(A58="","",IFERROR(VLOOKUP(A58,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A58="","",IFERROR(IF(VLOOKUP(A58,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A58,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I58" s="10">
@@ -2336,7 +2339,7 @@
         <v/>
       </c>
       <c r="L58" s="9">
-        <f>IF(AND(A58="",C58=""),"",IF(A58="","Falta el tipo",IF(C58="","Falta el código",IF(ISNA(MATCH(C58,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D58)&gt;0,N(VLOOKUP(C58,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A58,TIPOS!$A:$C,3,FALSE),"")="Sí",B58=""),"Falta el N° de entrega",IF(N(I58)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A58="",C58=""),"",IF(A58="","Falta el tipo",IF(H58="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C58="","Falta el código",IF(ISNA(MATCH(C58,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D58)&gt;0,N(VLOOKUP(C58,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A58,TIPOS!$A:$C,3,FALSE),"")="Sí",B58=""),"Falta el N° de entrega",IF(N(I58)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -2352,7 +2355,7 @@
         <v/>
       </c>
       <c r="H59" s="9">
-        <f>IF(A59="","",IFERROR(VLOOKUP(A59,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A59="","",IFERROR(IF(VLOOKUP(A59,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A59,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I59" s="10">
@@ -2368,7 +2371,7 @@
         <v/>
       </c>
       <c r="L59" s="9">
-        <f>IF(AND(A59="",C59=""),"",IF(A59="","Falta el tipo",IF(C59="","Falta el código",IF(ISNA(MATCH(C59,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D59)&gt;0,N(VLOOKUP(C59,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A59,TIPOS!$A:$C,3,FALSE),"")="Sí",B59=""),"Falta el N° de entrega",IF(N(I59)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A59="",C59=""),"",IF(A59="","Falta el tipo",IF(H59="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C59="","Falta el código",IF(ISNA(MATCH(C59,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D59)&gt;0,N(VLOOKUP(C59,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A59,TIPOS!$A:$C,3,FALSE),"")="Sí",B59=""),"Falta el N° de entrega",IF(N(I59)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -2384,7 +2387,7 @@
         <v/>
       </c>
       <c r="H60" s="9">
-        <f>IF(A60="","",IFERROR(VLOOKUP(A60,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A60="","",IFERROR(IF(VLOOKUP(A60,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A60,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I60" s="10">
@@ -2400,7 +2403,7 @@
         <v/>
       </c>
       <c r="L60" s="9">
-        <f>IF(AND(A60="",C60=""),"",IF(A60="","Falta el tipo",IF(C60="","Falta el código",IF(ISNA(MATCH(C60,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D60)&gt;0,N(VLOOKUP(C60,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A60,TIPOS!$A:$C,3,FALSE),"")="Sí",B60=""),"Falta el N° de entrega",IF(N(I60)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A60="",C60=""),"",IF(A60="","Falta el tipo",IF(H60="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C60="","Falta el código",IF(ISNA(MATCH(C60,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D60)&gt;0,N(VLOOKUP(C60,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A60,TIPOS!$A:$C,3,FALSE),"")="Sí",B60=""),"Falta el N° de entrega",IF(N(I60)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -2416,7 +2419,7 @@
         <v/>
       </c>
       <c r="H61" s="9">
-        <f>IF(A61="","",IFERROR(VLOOKUP(A61,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A61="","",IFERROR(IF(VLOOKUP(A61,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A61,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I61" s="10">
@@ -2432,7 +2435,7 @@
         <v/>
       </c>
       <c r="L61" s="9">
-        <f>IF(AND(A61="",C61=""),"",IF(A61="","Falta el tipo",IF(C61="","Falta el código",IF(ISNA(MATCH(C61,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D61)&gt;0,N(VLOOKUP(C61,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A61,TIPOS!$A:$C,3,FALSE),"")="Sí",B61=""),"Falta el N° de entrega",IF(N(I61)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A61="",C61=""),"",IF(A61="","Falta el tipo",IF(H61="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C61="","Falta el código",IF(ISNA(MATCH(C61,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D61)&gt;0,N(VLOOKUP(C61,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A61,TIPOS!$A:$C,3,FALSE),"")="Sí",B61=""),"Falta el N° de entrega",IF(N(I61)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -2448,7 +2451,7 @@
         <v/>
       </c>
       <c r="H62" s="9">
-        <f>IF(A62="","",IFERROR(VLOOKUP(A62,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A62="","",IFERROR(IF(VLOOKUP(A62,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A62,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I62" s="10">
@@ -2464,7 +2467,7 @@
         <v/>
       </c>
       <c r="L62" s="9">
-        <f>IF(AND(A62="",C62=""),"",IF(A62="","Falta el tipo",IF(C62="","Falta el código",IF(ISNA(MATCH(C62,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D62)&gt;0,N(VLOOKUP(C62,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A62,TIPOS!$A:$C,3,FALSE),"")="Sí",B62=""),"Falta el N° de entrega",IF(N(I62)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A62="",C62=""),"",IF(A62="","Falta el tipo",IF(H62="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C62="","Falta el código",IF(ISNA(MATCH(C62,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D62)&gt;0,N(VLOOKUP(C62,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A62,TIPOS!$A:$C,3,FALSE),"")="Sí",B62=""),"Falta el N° de entrega",IF(N(I62)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -2480,7 +2483,7 @@
         <v/>
       </c>
       <c r="H63" s="9">
-        <f>IF(A63="","",IFERROR(VLOOKUP(A63,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A63="","",IFERROR(IF(VLOOKUP(A63,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A63,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I63" s="10">
@@ -2496,7 +2499,7 @@
         <v/>
       </c>
       <c r="L63" s="9">
-        <f>IF(AND(A63="",C63=""),"",IF(A63="","Falta el tipo",IF(C63="","Falta el código",IF(ISNA(MATCH(C63,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D63)&gt;0,N(VLOOKUP(C63,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A63,TIPOS!$A:$C,3,FALSE),"")="Sí",B63=""),"Falta el N° de entrega",IF(N(I63)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A63="",C63=""),"",IF(A63="","Falta el tipo",IF(H63="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C63="","Falta el código",IF(ISNA(MATCH(C63,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D63)&gt;0,N(VLOOKUP(C63,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A63,TIPOS!$A:$C,3,FALSE),"")="Sí",B63=""),"Falta el N° de entrega",IF(N(I63)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -2512,7 +2515,7 @@
         <v/>
       </c>
       <c r="H64" s="9">
-        <f>IF(A64="","",IFERROR(VLOOKUP(A64,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A64="","",IFERROR(IF(VLOOKUP(A64,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A64,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I64" s="10">
@@ -2528,7 +2531,7 @@
         <v/>
       </c>
       <c r="L64" s="9">
-        <f>IF(AND(A64="",C64=""),"",IF(A64="","Falta el tipo",IF(C64="","Falta el código",IF(ISNA(MATCH(C64,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D64)&gt;0,N(VLOOKUP(C64,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A64,TIPOS!$A:$C,3,FALSE),"")="Sí",B64=""),"Falta el N° de entrega",IF(N(I64)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A64="",C64=""),"",IF(A64="","Falta el tipo",IF(H64="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C64="","Falta el código",IF(ISNA(MATCH(C64,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D64)&gt;0,N(VLOOKUP(C64,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A64,TIPOS!$A:$C,3,FALSE),"")="Sí",B64=""),"Falta el N° de entrega",IF(N(I64)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -2544,7 +2547,7 @@
         <v/>
       </c>
       <c r="H65" s="9">
-        <f>IF(A65="","",IFERROR(VLOOKUP(A65,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A65="","",IFERROR(IF(VLOOKUP(A65,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A65,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I65" s="10">
@@ -2560,7 +2563,7 @@
         <v/>
       </c>
       <c r="L65" s="9">
-        <f>IF(AND(A65="",C65=""),"",IF(A65="","Falta el tipo",IF(C65="","Falta el código",IF(ISNA(MATCH(C65,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D65)&gt;0,N(VLOOKUP(C65,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A65,TIPOS!$A:$C,3,FALSE),"")="Sí",B65=""),"Falta el N° de entrega",IF(N(I65)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A65="",C65=""),"",IF(A65="","Falta el tipo",IF(H65="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C65="","Falta el código",IF(ISNA(MATCH(C65,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D65)&gt;0,N(VLOOKUP(C65,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A65,TIPOS!$A:$C,3,FALSE),"")="Sí",B65=""),"Falta el N° de entrega",IF(N(I65)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -2576,7 +2579,7 @@
         <v/>
       </c>
       <c r="H66" s="9">
-        <f>IF(A66="","",IFERROR(VLOOKUP(A66,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A66="","",IFERROR(IF(VLOOKUP(A66,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A66,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I66" s="10">
@@ -2592,7 +2595,7 @@
         <v/>
       </c>
       <c r="L66" s="9">
-        <f>IF(AND(A66="",C66=""),"",IF(A66="","Falta el tipo",IF(C66="","Falta el código",IF(ISNA(MATCH(C66,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D66)&gt;0,N(VLOOKUP(C66,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A66,TIPOS!$A:$C,3,FALSE),"")="Sí",B66=""),"Falta el N° de entrega",IF(N(I66)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A66="",C66=""),"",IF(A66="","Falta el tipo",IF(H66="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C66="","Falta el código",IF(ISNA(MATCH(C66,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D66)&gt;0,N(VLOOKUP(C66,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A66,TIPOS!$A:$C,3,FALSE),"")="Sí",B66=""),"Falta el N° de entrega",IF(N(I66)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -2608,7 +2611,7 @@
         <v/>
       </c>
       <c r="H67" s="9">
-        <f>IF(A67="","",IFERROR(VLOOKUP(A67,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A67="","",IFERROR(IF(VLOOKUP(A67,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A67,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I67" s="10">
@@ -2624,7 +2627,7 @@
         <v/>
       </c>
       <c r="L67" s="9">
-        <f>IF(AND(A67="",C67=""),"",IF(A67="","Falta el tipo",IF(C67="","Falta el código",IF(ISNA(MATCH(C67,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D67)&gt;0,N(VLOOKUP(C67,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A67,TIPOS!$A:$C,3,FALSE),"")="Sí",B67=""),"Falta el N° de entrega",IF(N(I67)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A67="",C67=""),"",IF(A67="","Falta el tipo",IF(H67="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C67="","Falta el código",IF(ISNA(MATCH(C67,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D67)&gt;0,N(VLOOKUP(C67,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A67,TIPOS!$A:$C,3,FALSE),"")="Sí",B67=""),"Falta el N° de entrega",IF(N(I67)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -2640,7 +2643,7 @@
         <v/>
       </c>
       <c r="H68" s="9">
-        <f>IF(A68="","",IFERROR(VLOOKUP(A68,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A68="","",IFERROR(IF(VLOOKUP(A68,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A68,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I68" s="10">
@@ -2656,7 +2659,7 @@
         <v/>
       </c>
       <c r="L68" s="9">
-        <f>IF(AND(A68="",C68=""),"",IF(A68="","Falta el tipo",IF(C68="","Falta el código",IF(ISNA(MATCH(C68,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D68)&gt;0,N(VLOOKUP(C68,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A68,TIPOS!$A:$C,3,FALSE),"")="Sí",B68=""),"Falta el N° de entrega",IF(N(I68)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A68="",C68=""),"",IF(A68="","Falta el tipo",IF(H68="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C68="","Falta el código",IF(ISNA(MATCH(C68,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D68)&gt;0,N(VLOOKUP(C68,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A68,TIPOS!$A:$C,3,FALSE),"")="Sí",B68=""),"Falta el N° de entrega",IF(N(I68)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -2672,7 +2675,7 @@
         <v/>
       </c>
       <c r="H69" s="9">
-        <f>IF(A69="","",IFERROR(VLOOKUP(A69,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A69="","",IFERROR(IF(VLOOKUP(A69,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A69,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I69" s="10">
@@ -2688,7 +2691,7 @@
         <v/>
       </c>
       <c r="L69" s="9">
-        <f>IF(AND(A69="",C69=""),"",IF(A69="","Falta el tipo",IF(C69="","Falta el código",IF(ISNA(MATCH(C69,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D69)&gt;0,N(VLOOKUP(C69,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A69,TIPOS!$A:$C,3,FALSE),"")="Sí",B69=""),"Falta el N° de entrega",IF(N(I69)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A69="",C69=""),"",IF(A69="","Falta el tipo",IF(H69="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C69="","Falta el código",IF(ISNA(MATCH(C69,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D69)&gt;0,N(VLOOKUP(C69,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A69,TIPOS!$A:$C,3,FALSE),"")="Sí",B69=""),"Falta el N° de entrega",IF(N(I69)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -2704,7 +2707,7 @@
         <v/>
       </c>
       <c r="H70" s="9">
-        <f>IF(A70="","",IFERROR(VLOOKUP(A70,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A70="","",IFERROR(IF(VLOOKUP(A70,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A70,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I70" s="10">
@@ -2720,7 +2723,7 @@
         <v/>
       </c>
       <c r="L70" s="9">
-        <f>IF(AND(A70="",C70=""),"",IF(A70="","Falta el tipo",IF(C70="","Falta el código",IF(ISNA(MATCH(C70,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D70)&gt;0,N(VLOOKUP(C70,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A70,TIPOS!$A:$C,3,FALSE),"")="Sí",B70=""),"Falta el N° de entrega",IF(N(I70)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A70="",C70=""),"",IF(A70="","Falta el tipo",IF(H70="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C70="","Falta el código",IF(ISNA(MATCH(C70,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D70)&gt;0,N(VLOOKUP(C70,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A70,TIPOS!$A:$C,3,FALSE),"")="Sí",B70=""),"Falta el N° de entrega",IF(N(I70)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -2736,7 +2739,7 @@
         <v/>
       </c>
       <c r="H71" s="9">
-        <f>IF(A71="","",IFERROR(VLOOKUP(A71,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A71="","",IFERROR(IF(VLOOKUP(A71,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A71,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I71" s="10">
@@ -2752,7 +2755,7 @@
         <v/>
       </c>
       <c r="L71" s="9">
-        <f>IF(AND(A71="",C71=""),"",IF(A71="","Falta el tipo",IF(C71="","Falta el código",IF(ISNA(MATCH(C71,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D71)&gt;0,N(VLOOKUP(C71,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A71,TIPOS!$A:$C,3,FALSE),"")="Sí",B71=""),"Falta el N° de entrega",IF(N(I71)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A71="",C71=""),"",IF(A71="","Falta el tipo",IF(H71="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C71="","Falta el código",IF(ISNA(MATCH(C71,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D71)&gt;0,N(VLOOKUP(C71,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A71,TIPOS!$A:$C,3,FALSE),"")="Sí",B71=""),"Falta el N° de entrega",IF(N(I71)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -2768,7 +2771,7 @@
         <v/>
       </c>
       <c r="H72" s="9">
-        <f>IF(A72="","",IFERROR(VLOOKUP(A72,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A72="","",IFERROR(IF(VLOOKUP(A72,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A72,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I72" s="10">
@@ -2784,7 +2787,7 @@
         <v/>
       </c>
       <c r="L72" s="9">
-        <f>IF(AND(A72="",C72=""),"",IF(A72="","Falta el tipo",IF(C72="","Falta el código",IF(ISNA(MATCH(C72,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D72)&gt;0,N(VLOOKUP(C72,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A72,TIPOS!$A:$C,3,FALSE),"")="Sí",B72=""),"Falta el N° de entrega",IF(N(I72)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A72="",C72=""),"",IF(A72="","Falta el tipo",IF(H72="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C72="","Falta el código",IF(ISNA(MATCH(C72,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D72)&gt;0,N(VLOOKUP(C72,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A72,TIPOS!$A:$C,3,FALSE),"")="Sí",B72=""),"Falta el N° de entrega",IF(N(I72)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -2800,7 +2803,7 @@
         <v/>
       </c>
       <c r="H73" s="9">
-        <f>IF(A73="","",IFERROR(VLOOKUP(A73,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A73="","",IFERROR(IF(VLOOKUP(A73,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A73,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I73" s="10">
@@ -2816,7 +2819,7 @@
         <v/>
       </c>
       <c r="L73" s="9">
-        <f>IF(AND(A73="",C73=""),"",IF(A73="","Falta el tipo",IF(C73="","Falta el código",IF(ISNA(MATCH(C73,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D73)&gt;0,N(VLOOKUP(C73,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A73,TIPOS!$A:$C,3,FALSE),"")="Sí",B73=""),"Falta el N° de entrega",IF(N(I73)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A73="",C73=""),"",IF(A73="","Falta el tipo",IF(H73="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C73="","Falta el código",IF(ISNA(MATCH(C73,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D73)&gt;0,N(VLOOKUP(C73,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A73,TIPOS!$A:$C,3,FALSE),"")="Sí",B73=""),"Falta el N° de entrega",IF(N(I73)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -2832,7 +2835,7 @@
         <v/>
       </c>
       <c r="H74" s="9">
-        <f>IF(A74="","",IFERROR(VLOOKUP(A74,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A74="","",IFERROR(IF(VLOOKUP(A74,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A74,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I74" s="10">
@@ -2848,7 +2851,7 @@
         <v/>
       </c>
       <c r="L74" s="9">
-        <f>IF(AND(A74="",C74=""),"",IF(A74="","Falta el tipo",IF(C74="","Falta el código",IF(ISNA(MATCH(C74,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D74)&gt;0,N(VLOOKUP(C74,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A74,TIPOS!$A:$C,3,FALSE),"")="Sí",B74=""),"Falta el N° de entrega",IF(N(I74)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A74="",C74=""),"",IF(A74="","Falta el tipo",IF(H74="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C74="","Falta el código",IF(ISNA(MATCH(C74,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D74)&gt;0,N(VLOOKUP(C74,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A74,TIPOS!$A:$C,3,FALSE),"")="Sí",B74=""),"Falta el N° de entrega",IF(N(I74)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -2864,7 +2867,7 @@
         <v/>
       </c>
       <c r="H75" s="9">
-        <f>IF(A75="","",IFERROR(VLOOKUP(A75,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A75="","",IFERROR(IF(VLOOKUP(A75,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A75,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I75" s="10">
@@ -2880,7 +2883,7 @@
         <v/>
       </c>
       <c r="L75" s="9">
-        <f>IF(AND(A75="",C75=""),"",IF(A75="","Falta el tipo",IF(C75="","Falta el código",IF(ISNA(MATCH(C75,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D75)&gt;0,N(VLOOKUP(C75,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A75,TIPOS!$A:$C,3,FALSE),"")="Sí",B75=""),"Falta el N° de entrega",IF(N(I75)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A75="",C75=""),"",IF(A75="","Falta el tipo",IF(H75="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C75="","Falta el código",IF(ISNA(MATCH(C75,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D75)&gt;0,N(VLOOKUP(C75,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A75,TIPOS!$A:$C,3,FALSE),"")="Sí",B75=""),"Falta el N° de entrega",IF(N(I75)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -2896,7 +2899,7 @@
         <v/>
       </c>
       <c r="H76" s="9">
-        <f>IF(A76="","",IFERROR(VLOOKUP(A76,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A76="","",IFERROR(IF(VLOOKUP(A76,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A76,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I76" s="10">
@@ -2912,7 +2915,7 @@
         <v/>
       </c>
       <c r="L76" s="9">
-        <f>IF(AND(A76="",C76=""),"",IF(A76="","Falta el tipo",IF(C76="","Falta el código",IF(ISNA(MATCH(C76,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D76)&gt;0,N(VLOOKUP(C76,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A76,TIPOS!$A:$C,3,FALSE),"")="Sí",B76=""),"Falta el N° de entrega",IF(N(I76)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A76="",C76=""),"",IF(A76="","Falta el tipo",IF(H76="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C76="","Falta el código",IF(ISNA(MATCH(C76,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D76)&gt;0,N(VLOOKUP(C76,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A76,TIPOS!$A:$C,3,FALSE),"")="Sí",B76=""),"Falta el N° de entrega",IF(N(I76)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -2928,7 +2931,7 @@
         <v/>
       </c>
       <c r="H77" s="9">
-        <f>IF(A77="","",IFERROR(VLOOKUP(A77,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A77="","",IFERROR(IF(VLOOKUP(A77,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A77,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I77" s="10">
@@ -2944,7 +2947,7 @@
         <v/>
       </c>
       <c r="L77" s="9">
-        <f>IF(AND(A77="",C77=""),"",IF(A77="","Falta el tipo",IF(C77="","Falta el código",IF(ISNA(MATCH(C77,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D77)&gt;0,N(VLOOKUP(C77,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A77,TIPOS!$A:$C,3,FALSE),"")="Sí",B77=""),"Falta el N° de entrega",IF(N(I77)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A77="",C77=""),"",IF(A77="","Falta el tipo",IF(H77="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C77="","Falta el código",IF(ISNA(MATCH(C77,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D77)&gt;0,N(VLOOKUP(C77,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A77,TIPOS!$A:$C,3,FALSE),"")="Sí",B77=""),"Falta el N° de entrega",IF(N(I77)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -2960,7 +2963,7 @@
         <v/>
       </c>
       <c r="H78" s="9">
-        <f>IF(A78="","",IFERROR(VLOOKUP(A78,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A78="","",IFERROR(IF(VLOOKUP(A78,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A78,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I78" s="10">
@@ -2976,7 +2979,7 @@
         <v/>
       </c>
       <c r="L78" s="9">
-        <f>IF(AND(A78="",C78=""),"",IF(A78="","Falta el tipo",IF(C78="","Falta el código",IF(ISNA(MATCH(C78,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D78)&gt;0,N(VLOOKUP(C78,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A78,TIPOS!$A:$C,3,FALSE),"")="Sí",B78=""),"Falta el N° de entrega",IF(N(I78)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A78="",C78=""),"",IF(A78="","Falta el tipo",IF(H78="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C78="","Falta el código",IF(ISNA(MATCH(C78,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D78)&gt;0,N(VLOOKUP(C78,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A78,TIPOS!$A:$C,3,FALSE),"")="Sí",B78=""),"Falta el N° de entrega",IF(N(I78)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -2992,7 +2995,7 @@
         <v/>
       </c>
       <c r="H79" s="9">
-        <f>IF(A79="","",IFERROR(VLOOKUP(A79,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A79="","",IFERROR(IF(VLOOKUP(A79,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A79,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I79" s="10">
@@ -3008,7 +3011,7 @@
         <v/>
       </c>
       <c r="L79" s="9">
-        <f>IF(AND(A79="",C79=""),"",IF(A79="","Falta el tipo",IF(C79="","Falta el código",IF(ISNA(MATCH(C79,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D79)&gt;0,N(VLOOKUP(C79,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A79,TIPOS!$A:$C,3,FALSE),"")="Sí",B79=""),"Falta el N° de entrega",IF(N(I79)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A79="",C79=""),"",IF(A79="","Falta el tipo",IF(H79="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C79="","Falta el código",IF(ISNA(MATCH(C79,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D79)&gt;0,N(VLOOKUP(C79,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A79,TIPOS!$A:$C,3,FALSE),"")="Sí",B79=""),"Falta el N° de entrega",IF(N(I79)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -3024,7 +3027,7 @@
         <v/>
       </c>
       <c r="H80" s="9">
-        <f>IF(A80="","",IFERROR(VLOOKUP(A80,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A80="","",IFERROR(IF(VLOOKUP(A80,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A80,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I80" s="10">
@@ -3040,7 +3043,7 @@
         <v/>
       </c>
       <c r="L80" s="9">
-        <f>IF(AND(A80="",C80=""),"",IF(A80="","Falta el tipo",IF(C80="","Falta el código",IF(ISNA(MATCH(C80,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D80)&gt;0,N(VLOOKUP(C80,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A80,TIPOS!$A:$C,3,FALSE),"")="Sí",B80=""),"Falta el N° de entrega",IF(N(I80)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A80="",C80=""),"",IF(A80="","Falta el tipo",IF(H80="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C80="","Falta el código",IF(ISNA(MATCH(C80,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D80)&gt;0,N(VLOOKUP(C80,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A80,TIPOS!$A:$C,3,FALSE),"")="Sí",B80=""),"Falta el N° de entrega",IF(N(I80)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -3056,7 +3059,7 @@
         <v/>
       </c>
       <c r="H81" s="9">
-        <f>IF(A81="","",IFERROR(VLOOKUP(A81,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A81="","",IFERROR(IF(VLOOKUP(A81,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A81,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I81" s="10">
@@ -3072,7 +3075,7 @@
         <v/>
       </c>
       <c r="L81" s="9">
-        <f>IF(AND(A81="",C81=""),"",IF(A81="","Falta el tipo",IF(C81="","Falta el código",IF(ISNA(MATCH(C81,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D81)&gt;0,N(VLOOKUP(C81,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A81,TIPOS!$A:$C,3,FALSE),"")="Sí",B81=""),"Falta el N° de entrega",IF(N(I81)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A81="",C81=""),"",IF(A81="","Falta el tipo",IF(H81="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C81="","Falta el código",IF(ISNA(MATCH(C81,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D81)&gt;0,N(VLOOKUP(C81,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A81,TIPOS!$A:$C,3,FALSE),"")="Sí",B81=""),"Falta el N° de entrega",IF(N(I81)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -3088,7 +3091,7 @@
         <v/>
       </c>
       <c r="H82" s="9">
-        <f>IF(A82="","",IFERROR(VLOOKUP(A82,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A82="","",IFERROR(IF(VLOOKUP(A82,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A82,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I82" s="10">
@@ -3104,7 +3107,7 @@
         <v/>
       </c>
       <c r="L82" s="9">
-        <f>IF(AND(A82="",C82=""),"",IF(A82="","Falta el tipo",IF(C82="","Falta el código",IF(ISNA(MATCH(C82,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D82)&gt;0,N(VLOOKUP(C82,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A82,TIPOS!$A:$C,3,FALSE),"")="Sí",B82=""),"Falta el N° de entrega",IF(N(I82)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A82="",C82=""),"",IF(A82="","Falta el tipo",IF(H82="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C82="","Falta el código",IF(ISNA(MATCH(C82,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D82)&gt;0,N(VLOOKUP(C82,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A82,TIPOS!$A:$C,3,FALSE),"")="Sí",B82=""),"Falta el N° de entrega",IF(N(I82)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -3120,7 +3123,7 @@
         <v/>
       </c>
       <c r="H83" s="9">
-        <f>IF(A83="","",IFERROR(VLOOKUP(A83,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A83="","",IFERROR(IF(VLOOKUP(A83,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A83,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I83" s="10">
@@ -3136,7 +3139,7 @@
         <v/>
       </c>
       <c r="L83" s="9">
-        <f>IF(AND(A83="",C83=""),"",IF(A83="","Falta el tipo",IF(C83="","Falta el código",IF(ISNA(MATCH(C83,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D83)&gt;0,N(VLOOKUP(C83,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A83,TIPOS!$A:$C,3,FALSE),"")="Sí",B83=""),"Falta el N° de entrega",IF(N(I83)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A83="",C83=""),"",IF(A83="","Falta el tipo",IF(H83="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C83="","Falta el código",IF(ISNA(MATCH(C83,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D83)&gt;0,N(VLOOKUP(C83,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A83,TIPOS!$A:$C,3,FALSE),"")="Sí",B83=""),"Falta el N° de entrega",IF(N(I83)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -3152,7 +3155,7 @@
         <v/>
       </c>
       <c r="H84" s="9">
-        <f>IF(A84="","",IFERROR(VLOOKUP(A84,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A84="","",IFERROR(IF(VLOOKUP(A84,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A84,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I84" s="10">
@@ -3168,7 +3171,7 @@
         <v/>
       </c>
       <c r="L84" s="9">
-        <f>IF(AND(A84="",C84=""),"",IF(A84="","Falta el tipo",IF(C84="","Falta el código",IF(ISNA(MATCH(C84,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D84)&gt;0,N(VLOOKUP(C84,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A84,TIPOS!$A:$C,3,FALSE),"")="Sí",B84=""),"Falta el N° de entrega",IF(N(I84)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A84="",C84=""),"",IF(A84="","Falta el tipo",IF(H84="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C84="","Falta el código",IF(ISNA(MATCH(C84,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D84)&gt;0,N(VLOOKUP(C84,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A84,TIPOS!$A:$C,3,FALSE),"")="Sí",B84=""),"Falta el N° de entrega",IF(N(I84)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -3184,7 +3187,7 @@
         <v/>
       </c>
       <c r="H85" s="9">
-        <f>IF(A85="","",IFERROR(VLOOKUP(A85,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A85="","",IFERROR(IF(VLOOKUP(A85,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A85,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I85" s="10">
@@ -3200,7 +3203,7 @@
         <v/>
       </c>
       <c r="L85" s="9">
-        <f>IF(AND(A85="",C85=""),"",IF(A85="","Falta el tipo",IF(C85="","Falta el código",IF(ISNA(MATCH(C85,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D85)&gt;0,N(VLOOKUP(C85,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A85,TIPOS!$A:$C,3,FALSE),"")="Sí",B85=""),"Falta el N° de entrega",IF(N(I85)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A85="",C85=""),"",IF(A85="","Falta el tipo",IF(H85="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C85="","Falta el código",IF(ISNA(MATCH(C85,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D85)&gt;0,N(VLOOKUP(C85,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A85,TIPOS!$A:$C,3,FALSE),"")="Sí",B85=""),"Falta el N° de entrega",IF(N(I85)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -3216,7 +3219,7 @@
         <v/>
       </c>
       <c r="H86" s="9">
-        <f>IF(A86="","",IFERROR(VLOOKUP(A86,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A86="","",IFERROR(IF(VLOOKUP(A86,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A86,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I86" s="10">
@@ -3232,7 +3235,7 @@
         <v/>
       </c>
       <c r="L86" s="9">
-        <f>IF(AND(A86="",C86=""),"",IF(A86="","Falta el tipo",IF(C86="","Falta el código",IF(ISNA(MATCH(C86,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D86)&gt;0,N(VLOOKUP(C86,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A86,TIPOS!$A:$C,3,FALSE),"")="Sí",B86=""),"Falta el N° de entrega",IF(N(I86)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A86="",C86=""),"",IF(A86="","Falta el tipo",IF(H86="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C86="","Falta el código",IF(ISNA(MATCH(C86,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D86)&gt;0,N(VLOOKUP(C86,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A86,TIPOS!$A:$C,3,FALSE),"")="Sí",B86=""),"Falta el N° de entrega",IF(N(I86)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -3248,7 +3251,7 @@
         <v/>
       </c>
       <c r="H87" s="9">
-        <f>IF(A87="","",IFERROR(VLOOKUP(A87,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A87="","",IFERROR(IF(VLOOKUP(A87,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A87,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I87" s="10">
@@ -3264,7 +3267,7 @@
         <v/>
       </c>
       <c r="L87" s="9">
-        <f>IF(AND(A87="",C87=""),"",IF(A87="","Falta el tipo",IF(C87="","Falta el código",IF(ISNA(MATCH(C87,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D87)&gt;0,N(VLOOKUP(C87,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A87,TIPOS!$A:$C,3,FALSE),"")="Sí",B87=""),"Falta el N° de entrega",IF(N(I87)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A87="",C87=""),"",IF(A87="","Falta el tipo",IF(H87="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C87="","Falta el código",IF(ISNA(MATCH(C87,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D87)&gt;0,N(VLOOKUP(C87,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A87,TIPOS!$A:$C,3,FALSE),"")="Sí",B87=""),"Falta el N° de entrega",IF(N(I87)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -3280,7 +3283,7 @@
         <v/>
       </c>
       <c r="H88" s="9">
-        <f>IF(A88="","",IFERROR(VLOOKUP(A88,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A88="","",IFERROR(IF(VLOOKUP(A88,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A88,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I88" s="10">
@@ -3296,7 +3299,7 @@
         <v/>
       </c>
       <c r="L88" s="9">
-        <f>IF(AND(A88="",C88=""),"",IF(A88="","Falta el tipo",IF(C88="","Falta el código",IF(ISNA(MATCH(C88,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D88)&gt;0,N(VLOOKUP(C88,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A88,TIPOS!$A:$C,3,FALSE),"")="Sí",B88=""),"Falta el N° de entrega",IF(N(I88)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A88="",C88=""),"",IF(A88="","Falta el tipo",IF(H88="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C88="","Falta el código",IF(ISNA(MATCH(C88,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D88)&gt;0,N(VLOOKUP(C88,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A88,TIPOS!$A:$C,3,FALSE),"")="Sí",B88=""),"Falta el N° de entrega",IF(N(I88)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -3312,7 +3315,7 @@
         <v/>
       </c>
       <c r="H89" s="9">
-        <f>IF(A89="","",IFERROR(VLOOKUP(A89,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A89="","",IFERROR(IF(VLOOKUP(A89,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A89,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I89" s="10">
@@ -3328,7 +3331,7 @@
         <v/>
       </c>
       <c r="L89" s="9">
-        <f>IF(AND(A89="",C89=""),"",IF(A89="","Falta el tipo",IF(C89="","Falta el código",IF(ISNA(MATCH(C89,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D89)&gt;0,N(VLOOKUP(C89,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A89,TIPOS!$A:$C,3,FALSE),"")="Sí",B89=""),"Falta el N° de entrega",IF(N(I89)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A89="",C89=""),"",IF(A89="","Falta el tipo",IF(H89="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C89="","Falta el código",IF(ISNA(MATCH(C89,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D89)&gt;0,N(VLOOKUP(C89,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A89,TIPOS!$A:$C,3,FALSE),"")="Sí",B89=""),"Falta el N° de entrega",IF(N(I89)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -3344,7 +3347,7 @@
         <v/>
       </c>
       <c r="H90" s="9">
-        <f>IF(A90="","",IFERROR(VLOOKUP(A90,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A90="","",IFERROR(IF(VLOOKUP(A90,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A90,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I90" s="10">
@@ -3360,7 +3363,7 @@
         <v/>
       </c>
       <c r="L90" s="9">
-        <f>IF(AND(A90="",C90=""),"",IF(A90="","Falta el tipo",IF(C90="","Falta el código",IF(ISNA(MATCH(C90,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D90)&gt;0,N(VLOOKUP(C90,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A90,TIPOS!$A:$C,3,FALSE),"")="Sí",B90=""),"Falta el N° de entrega",IF(N(I90)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A90="",C90=""),"",IF(A90="","Falta el tipo",IF(H90="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C90="","Falta el código",IF(ISNA(MATCH(C90,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D90)&gt;0,N(VLOOKUP(C90,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A90,TIPOS!$A:$C,3,FALSE),"")="Sí",B90=""),"Falta el N° de entrega",IF(N(I90)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -3376,7 +3379,7 @@
         <v/>
       </c>
       <c r="H91" s="9">
-        <f>IF(A91="","",IFERROR(VLOOKUP(A91,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A91="","",IFERROR(IF(VLOOKUP(A91,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A91,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I91" s="10">
@@ -3392,7 +3395,7 @@
         <v/>
       </c>
       <c r="L91" s="9">
-        <f>IF(AND(A91="",C91=""),"",IF(A91="","Falta el tipo",IF(C91="","Falta el código",IF(ISNA(MATCH(C91,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D91)&gt;0,N(VLOOKUP(C91,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A91,TIPOS!$A:$C,3,FALSE),"")="Sí",B91=""),"Falta el N° de entrega",IF(N(I91)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A91="",C91=""),"",IF(A91="","Falta el tipo",IF(H91="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C91="","Falta el código",IF(ISNA(MATCH(C91,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D91)&gt;0,N(VLOOKUP(C91,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A91,TIPOS!$A:$C,3,FALSE),"")="Sí",B91=""),"Falta el N° de entrega",IF(N(I91)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -3408,7 +3411,7 @@
         <v/>
       </c>
       <c r="H92" s="9">
-        <f>IF(A92="","",IFERROR(VLOOKUP(A92,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A92="","",IFERROR(IF(VLOOKUP(A92,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A92,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I92" s="10">
@@ -3424,7 +3427,7 @@
         <v/>
       </c>
       <c r="L92" s="9">
-        <f>IF(AND(A92="",C92=""),"",IF(A92="","Falta el tipo",IF(C92="","Falta el código",IF(ISNA(MATCH(C92,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D92)&gt;0,N(VLOOKUP(C92,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A92,TIPOS!$A:$C,3,FALSE),"")="Sí",B92=""),"Falta el N° de entrega",IF(N(I92)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A92="",C92=""),"",IF(A92="","Falta el tipo",IF(H92="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C92="","Falta el código",IF(ISNA(MATCH(C92,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D92)&gt;0,N(VLOOKUP(C92,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A92,TIPOS!$A:$C,3,FALSE),"")="Sí",B92=""),"Falta el N° de entrega",IF(N(I92)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -3440,7 +3443,7 @@
         <v/>
       </c>
       <c r="H93" s="9">
-        <f>IF(A93="","",IFERROR(VLOOKUP(A93,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A93="","",IFERROR(IF(VLOOKUP(A93,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A93,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I93" s="10">
@@ -3456,7 +3459,7 @@
         <v/>
       </c>
       <c r="L93" s="9">
-        <f>IF(AND(A93="",C93=""),"",IF(A93="","Falta el tipo",IF(C93="","Falta el código",IF(ISNA(MATCH(C93,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D93)&gt;0,N(VLOOKUP(C93,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A93,TIPOS!$A:$C,3,FALSE),"")="Sí",B93=""),"Falta el N° de entrega",IF(N(I93)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A93="",C93=""),"",IF(A93="","Falta el tipo",IF(H93="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C93="","Falta el código",IF(ISNA(MATCH(C93,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D93)&gt;0,N(VLOOKUP(C93,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A93,TIPOS!$A:$C,3,FALSE),"")="Sí",B93=""),"Falta el N° de entrega",IF(N(I93)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -3472,7 +3475,7 @@
         <v/>
       </c>
       <c r="H94" s="9">
-        <f>IF(A94="","",IFERROR(VLOOKUP(A94,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A94="","",IFERROR(IF(VLOOKUP(A94,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A94,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I94" s="10">
@@ -3488,7 +3491,7 @@
         <v/>
       </c>
       <c r="L94" s="9">
-        <f>IF(AND(A94="",C94=""),"",IF(A94="","Falta el tipo",IF(C94="","Falta el código",IF(ISNA(MATCH(C94,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D94)&gt;0,N(VLOOKUP(C94,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A94,TIPOS!$A:$C,3,FALSE),"")="Sí",B94=""),"Falta el N° de entrega",IF(N(I94)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A94="",C94=""),"",IF(A94="","Falta el tipo",IF(H94="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C94="","Falta el código",IF(ISNA(MATCH(C94,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D94)&gt;0,N(VLOOKUP(C94,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A94,TIPOS!$A:$C,3,FALSE),"")="Sí",B94=""),"Falta el N° de entrega",IF(N(I94)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -3504,7 +3507,7 @@
         <v/>
       </c>
       <c r="H95" s="9">
-        <f>IF(A95="","",IFERROR(VLOOKUP(A95,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A95="","",IFERROR(IF(VLOOKUP(A95,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A95,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I95" s="10">
@@ -3520,7 +3523,7 @@
         <v/>
       </c>
       <c r="L95" s="9">
-        <f>IF(AND(A95="",C95=""),"",IF(A95="","Falta el tipo",IF(C95="","Falta el código",IF(ISNA(MATCH(C95,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D95)&gt;0,N(VLOOKUP(C95,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A95,TIPOS!$A:$C,3,FALSE),"")="Sí",B95=""),"Falta el N° de entrega",IF(N(I95)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A95="",C95=""),"",IF(A95="","Falta el tipo",IF(H95="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C95="","Falta el código",IF(ISNA(MATCH(C95,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D95)&gt;0,N(VLOOKUP(C95,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A95,TIPOS!$A:$C,3,FALSE),"")="Sí",B95=""),"Falta el N° de entrega",IF(N(I95)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -3536,7 +3539,7 @@
         <v/>
       </c>
       <c r="H96" s="9">
-        <f>IF(A96="","",IFERROR(VLOOKUP(A96,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A96="","",IFERROR(IF(VLOOKUP(A96,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A96,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I96" s="10">
@@ -3552,7 +3555,7 @@
         <v/>
       </c>
       <c r="L96" s="9">
-        <f>IF(AND(A96="",C96=""),"",IF(A96="","Falta el tipo",IF(C96="","Falta el código",IF(ISNA(MATCH(C96,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D96)&gt;0,N(VLOOKUP(C96,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A96,TIPOS!$A:$C,3,FALSE),"")="Sí",B96=""),"Falta el N° de entrega",IF(N(I96)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A96="",C96=""),"",IF(A96="","Falta el tipo",IF(H96="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C96="","Falta el código",IF(ISNA(MATCH(C96,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D96)&gt;0,N(VLOOKUP(C96,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A96,TIPOS!$A:$C,3,FALSE),"")="Sí",B96=""),"Falta el N° de entrega",IF(N(I96)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -3568,7 +3571,7 @@
         <v/>
       </c>
       <c r="H97" s="9">
-        <f>IF(A97="","",IFERROR(VLOOKUP(A97,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A97="","",IFERROR(IF(VLOOKUP(A97,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A97,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I97" s="10">
@@ -3584,7 +3587,7 @@
         <v/>
       </c>
       <c r="L97" s="9">
-        <f>IF(AND(A97="",C97=""),"",IF(A97="","Falta el tipo",IF(C97="","Falta el código",IF(ISNA(MATCH(C97,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D97)&gt;0,N(VLOOKUP(C97,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A97,TIPOS!$A:$C,3,FALSE),"")="Sí",B97=""),"Falta el N° de entrega",IF(N(I97)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A97="",C97=""),"",IF(A97="","Falta el tipo",IF(H97="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C97="","Falta el código",IF(ISNA(MATCH(C97,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D97)&gt;0,N(VLOOKUP(C97,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A97,TIPOS!$A:$C,3,FALSE),"")="Sí",B97=""),"Falta el N° de entrega",IF(N(I97)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -3600,7 +3603,7 @@
         <v/>
       </c>
       <c r="H98" s="9">
-        <f>IF(A98="","",IFERROR(VLOOKUP(A98,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A98="","",IFERROR(IF(VLOOKUP(A98,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A98,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I98" s="10">
@@ -3616,7 +3619,7 @@
         <v/>
       </c>
       <c r="L98" s="9">
-        <f>IF(AND(A98="",C98=""),"",IF(A98="","Falta el tipo",IF(C98="","Falta el código",IF(ISNA(MATCH(C98,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D98)&gt;0,N(VLOOKUP(C98,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A98,TIPOS!$A:$C,3,FALSE),"")="Sí",B98=""),"Falta el N° de entrega",IF(N(I98)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A98="",C98=""),"",IF(A98="","Falta el tipo",IF(H98="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C98="","Falta el código",IF(ISNA(MATCH(C98,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D98)&gt;0,N(VLOOKUP(C98,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A98,TIPOS!$A:$C,3,FALSE),"")="Sí",B98=""),"Falta el N° de entrega",IF(N(I98)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -3632,7 +3635,7 @@
         <v/>
       </c>
       <c r="H99" s="9">
-        <f>IF(A99="","",IFERROR(VLOOKUP(A99,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A99="","",IFERROR(IF(VLOOKUP(A99,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A99,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I99" s="10">
@@ -3648,7 +3651,7 @@
         <v/>
       </c>
       <c r="L99" s="9">
-        <f>IF(AND(A99="",C99=""),"",IF(A99="","Falta el tipo",IF(C99="","Falta el código",IF(ISNA(MATCH(C99,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D99)&gt;0,N(VLOOKUP(C99,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A99,TIPOS!$A:$C,3,FALSE),"")="Sí",B99=""),"Falta el N° de entrega",IF(N(I99)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A99="",C99=""),"",IF(A99="","Falta el tipo",IF(H99="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C99="","Falta el código",IF(ISNA(MATCH(C99,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D99)&gt;0,N(VLOOKUP(C99,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A99,TIPOS!$A:$C,3,FALSE),"")="Sí",B99=""),"Falta el N° de entrega",IF(N(I99)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -3664,7 +3667,7 @@
         <v/>
       </c>
       <c r="H100" s="9">
-        <f>IF(A100="","",IFERROR(VLOOKUP(A100,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A100="","",IFERROR(IF(VLOOKUP(A100,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A100,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I100" s="10">
@@ -3680,7 +3683,7 @@
         <v/>
       </c>
       <c r="L100" s="9">
-        <f>IF(AND(A100="",C100=""),"",IF(A100="","Falta el tipo",IF(C100="","Falta el código",IF(ISNA(MATCH(C100,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D100)&gt;0,N(VLOOKUP(C100,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A100,TIPOS!$A:$C,3,FALSE),"")="Sí",B100=""),"Falta el N° de entrega",IF(N(I100)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A100="",C100=""),"",IF(A100="","Falta el tipo",IF(H100="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C100="","Falta el código",IF(ISNA(MATCH(C100,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D100)&gt;0,N(VLOOKUP(C100,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A100,TIPOS!$A:$C,3,FALSE),"")="Sí",B100=""),"Falta el N° de entrega",IF(N(I100)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -3696,7 +3699,7 @@
         <v/>
       </c>
       <c r="H101" s="9">
-        <f>IF(A101="","",IFERROR(VLOOKUP(A101,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A101="","",IFERROR(IF(VLOOKUP(A101,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A101,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I101" s="10">
@@ -3712,7 +3715,7 @@
         <v/>
       </c>
       <c r="L101" s="9">
-        <f>IF(AND(A101="",C101=""),"",IF(A101="","Falta el tipo",IF(C101="","Falta el código",IF(ISNA(MATCH(C101,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D101)&gt;0,N(VLOOKUP(C101,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A101,TIPOS!$A:$C,3,FALSE),"")="Sí",B101=""),"Falta el N° de entrega",IF(N(I101)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A101="",C101=""),"",IF(A101="","Falta el tipo",IF(H101="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C101="","Falta el código",IF(ISNA(MATCH(C101,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D101)&gt;0,N(VLOOKUP(C101,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A101,TIPOS!$A:$C,3,FALSE),"")="Sí",B101=""),"Falta el N° de entrega",IF(N(I101)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -3728,7 +3731,7 @@
         <v/>
       </c>
       <c r="H102" s="9">
-        <f>IF(A102="","",IFERROR(VLOOKUP(A102,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A102="","",IFERROR(IF(VLOOKUP(A102,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A102,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I102" s="10">
@@ -3744,7 +3747,7 @@
         <v/>
       </c>
       <c r="L102" s="9">
-        <f>IF(AND(A102="",C102=""),"",IF(A102="","Falta el tipo",IF(C102="","Falta el código",IF(ISNA(MATCH(C102,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D102)&gt;0,N(VLOOKUP(C102,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A102,TIPOS!$A:$C,3,FALSE),"")="Sí",B102=""),"Falta el N° de entrega",IF(N(I102)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A102="",C102=""),"",IF(A102="","Falta el tipo",IF(H102="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C102="","Falta el código",IF(ISNA(MATCH(C102,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D102)&gt;0,N(VLOOKUP(C102,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A102,TIPOS!$A:$C,3,FALSE),"")="Sí",B102=""),"Falta el N° de entrega",IF(N(I102)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -3760,7 +3763,7 @@
         <v/>
       </c>
       <c r="H103" s="9">
-        <f>IF(A103="","",IFERROR(VLOOKUP(A103,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A103="","",IFERROR(IF(VLOOKUP(A103,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A103,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I103" s="10">
@@ -3776,7 +3779,7 @@
         <v/>
       </c>
       <c r="L103" s="9">
-        <f>IF(AND(A103="",C103=""),"",IF(A103="","Falta el tipo",IF(C103="","Falta el código",IF(ISNA(MATCH(C103,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D103)&gt;0,N(VLOOKUP(C103,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A103,TIPOS!$A:$C,3,FALSE),"")="Sí",B103=""),"Falta el N° de entrega",IF(N(I103)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A103="",C103=""),"",IF(A103="","Falta el tipo",IF(H103="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C103="","Falta el código",IF(ISNA(MATCH(C103,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D103)&gt;0,N(VLOOKUP(C103,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A103,TIPOS!$A:$C,3,FALSE),"")="Sí",B103=""),"Falta el N° de entrega",IF(N(I103)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -3792,7 +3795,7 @@
         <v/>
       </c>
       <c r="H104" s="9">
-        <f>IF(A104="","",IFERROR(VLOOKUP(A104,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A104="","",IFERROR(IF(VLOOKUP(A104,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A104,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I104" s="10">
@@ -3808,7 +3811,7 @@
         <v/>
       </c>
       <c r="L104" s="9">
-        <f>IF(AND(A104="",C104=""),"",IF(A104="","Falta el tipo",IF(C104="","Falta el código",IF(ISNA(MATCH(C104,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D104)&gt;0,N(VLOOKUP(C104,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A104,TIPOS!$A:$C,3,FALSE),"")="Sí",B104=""),"Falta el N° de entrega",IF(N(I104)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A104="",C104=""),"",IF(A104="","Falta el tipo",IF(H104="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C104="","Falta el código",IF(ISNA(MATCH(C104,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D104)&gt;0,N(VLOOKUP(C104,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A104,TIPOS!$A:$C,3,FALSE),"")="Sí",B104=""),"Falta el N° de entrega",IF(N(I104)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -3824,7 +3827,7 @@
         <v/>
       </c>
       <c r="H105" s="9">
-        <f>IF(A105="","",IFERROR(VLOOKUP(A105,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A105="","",IFERROR(IF(VLOOKUP(A105,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A105,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I105" s="10">
@@ -3840,7 +3843,7 @@
         <v/>
       </c>
       <c r="L105" s="9">
-        <f>IF(AND(A105="",C105=""),"",IF(A105="","Falta el tipo",IF(C105="","Falta el código",IF(ISNA(MATCH(C105,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D105)&gt;0,N(VLOOKUP(C105,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A105,TIPOS!$A:$C,3,FALSE),"")="Sí",B105=""),"Falta el N° de entrega",IF(N(I105)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A105="",C105=""),"",IF(A105="","Falta el tipo",IF(H105="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C105="","Falta el código",IF(ISNA(MATCH(C105,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D105)&gt;0,N(VLOOKUP(C105,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A105,TIPOS!$A:$C,3,FALSE),"")="Sí",B105=""),"Falta el N° de entrega",IF(N(I105)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -3856,7 +3859,7 @@
         <v/>
       </c>
       <c r="H106" s="9">
-        <f>IF(A106="","",IFERROR(VLOOKUP(A106,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A106="","",IFERROR(IF(VLOOKUP(A106,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A106,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I106" s="10">
@@ -3872,7 +3875,7 @@
         <v/>
       </c>
       <c r="L106" s="9">
-        <f>IF(AND(A106="",C106=""),"",IF(A106="","Falta el tipo",IF(C106="","Falta el código",IF(ISNA(MATCH(C106,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D106)&gt;0,N(VLOOKUP(C106,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A106,TIPOS!$A:$C,3,FALSE),"")="Sí",B106=""),"Falta el N° de entrega",IF(N(I106)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A106="",C106=""),"",IF(A106="","Falta el tipo",IF(H106="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C106="","Falta el código",IF(ISNA(MATCH(C106,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D106)&gt;0,N(VLOOKUP(C106,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A106,TIPOS!$A:$C,3,FALSE),"")="Sí",B106=""),"Falta el N° de entrega",IF(N(I106)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -3888,7 +3891,7 @@
         <v/>
       </c>
       <c r="H107" s="9">
-        <f>IF(A107="","",IFERROR(VLOOKUP(A107,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A107="","",IFERROR(IF(VLOOKUP(A107,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A107,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I107" s="10">
@@ -3904,7 +3907,7 @@
         <v/>
       </c>
       <c r="L107" s="9">
-        <f>IF(AND(A107="",C107=""),"",IF(A107="","Falta el tipo",IF(C107="","Falta el código",IF(ISNA(MATCH(C107,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D107)&gt;0,N(VLOOKUP(C107,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A107,TIPOS!$A:$C,3,FALSE),"")="Sí",B107=""),"Falta el N° de entrega",IF(N(I107)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A107="",C107=""),"",IF(A107="","Falta el tipo",IF(H107="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C107="","Falta el código",IF(ISNA(MATCH(C107,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D107)&gt;0,N(VLOOKUP(C107,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A107,TIPOS!$A:$C,3,FALSE),"")="Sí",B107=""),"Falta el N° de entrega",IF(N(I107)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -3920,7 +3923,7 @@
         <v/>
       </c>
       <c r="H108" s="9">
-        <f>IF(A108="","",IFERROR(VLOOKUP(A108,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A108="","",IFERROR(IF(VLOOKUP(A108,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A108,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I108" s="10">
@@ -3936,7 +3939,7 @@
         <v/>
       </c>
       <c r="L108" s="9">
-        <f>IF(AND(A108="",C108=""),"",IF(A108="","Falta el tipo",IF(C108="","Falta el código",IF(ISNA(MATCH(C108,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D108)&gt;0,N(VLOOKUP(C108,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A108,TIPOS!$A:$C,3,FALSE),"")="Sí",B108=""),"Falta el N° de entrega",IF(N(I108)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A108="",C108=""),"",IF(A108="","Falta el tipo",IF(H108="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C108="","Falta el código",IF(ISNA(MATCH(C108,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D108)&gt;0,N(VLOOKUP(C108,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A108,TIPOS!$A:$C,3,FALSE),"")="Sí",B108=""),"Falta el N° de entrega",IF(N(I108)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -3952,7 +3955,7 @@
         <v/>
       </c>
       <c r="H109" s="9">
-        <f>IF(A109="","",IFERROR(VLOOKUP(A109,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A109="","",IFERROR(IF(VLOOKUP(A109,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A109,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I109" s="10">
@@ -3968,7 +3971,7 @@
         <v/>
       </c>
       <c r="L109" s="9">
-        <f>IF(AND(A109="",C109=""),"",IF(A109="","Falta el tipo",IF(C109="","Falta el código",IF(ISNA(MATCH(C109,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D109)&gt;0,N(VLOOKUP(C109,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A109,TIPOS!$A:$C,3,FALSE),"")="Sí",B109=""),"Falta el N° de entrega",IF(N(I109)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A109="",C109=""),"",IF(A109="","Falta el tipo",IF(H109="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C109="","Falta el código",IF(ISNA(MATCH(C109,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D109)&gt;0,N(VLOOKUP(C109,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A109,TIPOS!$A:$C,3,FALSE),"")="Sí",B109=""),"Falta el N° de entrega",IF(N(I109)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -3984,7 +3987,7 @@
         <v/>
       </c>
       <c r="H110" s="9">
-        <f>IF(A110="","",IFERROR(VLOOKUP(A110,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A110="","",IFERROR(IF(VLOOKUP(A110,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A110,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I110" s="10">
@@ -4000,7 +4003,7 @@
         <v/>
       </c>
       <c r="L110" s="9">
-        <f>IF(AND(A110="",C110=""),"",IF(A110="","Falta el tipo",IF(C110="","Falta el código",IF(ISNA(MATCH(C110,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D110)&gt;0,N(VLOOKUP(C110,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A110,TIPOS!$A:$C,3,FALSE),"")="Sí",B110=""),"Falta el N° de entrega",IF(N(I110)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A110="",C110=""),"",IF(A110="","Falta el tipo",IF(H110="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C110="","Falta el código",IF(ISNA(MATCH(C110,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D110)&gt;0,N(VLOOKUP(C110,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A110,TIPOS!$A:$C,3,FALSE),"")="Sí",B110=""),"Falta el N° de entrega",IF(N(I110)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -4016,7 +4019,7 @@
         <v/>
       </c>
       <c r="H111" s="9">
-        <f>IF(A111="","",IFERROR(VLOOKUP(A111,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A111="","",IFERROR(IF(VLOOKUP(A111,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A111,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I111" s="10">
@@ -4032,7 +4035,7 @@
         <v/>
       </c>
       <c r="L111" s="9">
-        <f>IF(AND(A111="",C111=""),"",IF(A111="","Falta el tipo",IF(C111="","Falta el código",IF(ISNA(MATCH(C111,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D111)&gt;0,N(VLOOKUP(C111,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A111,TIPOS!$A:$C,3,FALSE),"")="Sí",B111=""),"Falta el N° de entrega",IF(N(I111)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A111="",C111=""),"",IF(A111="","Falta el tipo",IF(H111="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C111="","Falta el código",IF(ISNA(MATCH(C111,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D111)&gt;0,N(VLOOKUP(C111,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A111,TIPOS!$A:$C,3,FALSE),"")="Sí",B111=""),"Falta el N° de entrega",IF(N(I111)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -4048,7 +4051,7 @@
         <v/>
       </c>
       <c r="H112" s="9">
-        <f>IF(A112="","",IFERROR(VLOOKUP(A112,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A112="","",IFERROR(IF(VLOOKUP(A112,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A112,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I112" s="10">
@@ -4064,7 +4067,7 @@
         <v/>
       </c>
       <c r="L112" s="9">
-        <f>IF(AND(A112="",C112=""),"",IF(A112="","Falta el tipo",IF(C112="","Falta el código",IF(ISNA(MATCH(C112,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D112)&gt;0,N(VLOOKUP(C112,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A112,TIPOS!$A:$C,3,FALSE),"")="Sí",B112=""),"Falta el N° de entrega",IF(N(I112)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A112="",C112=""),"",IF(A112="","Falta el tipo",IF(H112="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C112="","Falta el código",IF(ISNA(MATCH(C112,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D112)&gt;0,N(VLOOKUP(C112,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A112,TIPOS!$A:$C,3,FALSE),"")="Sí",B112=""),"Falta el N° de entrega",IF(N(I112)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -4080,7 +4083,7 @@
         <v/>
       </c>
       <c r="H113" s="9">
-        <f>IF(A113="","",IFERROR(VLOOKUP(A113,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A113="","",IFERROR(IF(VLOOKUP(A113,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A113,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I113" s="10">
@@ -4096,7 +4099,7 @@
         <v/>
       </c>
       <c r="L113" s="9">
-        <f>IF(AND(A113="",C113=""),"",IF(A113="","Falta el tipo",IF(C113="","Falta el código",IF(ISNA(MATCH(C113,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D113)&gt;0,N(VLOOKUP(C113,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A113,TIPOS!$A:$C,3,FALSE),"")="Sí",B113=""),"Falta el N° de entrega",IF(N(I113)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A113="",C113=""),"",IF(A113="","Falta el tipo",IF(H113="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C113="","Falta el código",IF(ISNA(MATCH(C113,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D113)&gt;0,N(VLOOKUP(C113,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A113,TIPOS!$A:$C,3,FALSE),"")="Sí",B113=""),"Falta el N° de entrega",IF(N(I113)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -4112,7 +4115,7 @@
         <v/>
       </c>
       <c r="H114" s="9">
-        <f>IF(A114="","",IFERROR(VLOOKUP(A114,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A114="","",IFERROR(IF(VLOOKUP(A114,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A114,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I114" s="10">
@@ -4128,7 +4131,7 @@
         <v/>
       </c>
       <c r="L114" s="9">
-        <f>IF(AND(A114="",C114=""),"",IF(A114="","Falta el tipo",IF(C114="","Falta el código",IF(ISNA(MATCH(C114,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D114)&gt;0,N(VLOOKUP(C114,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A114,TIPOS!$A:$C,3,FALSE),"")="Sí",B114=""),"Falta el N° de entrega",IF(N(I114)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A114="",C114=""),"",IF(A114="","Falta el tipo",IF(H114="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C114="","Falta el código",IF(ISNA(MATCH(C114,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D114)&gt;0,N(VLOOKUP(C114,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A114,TIPOS!$A:$C,3,FALSE),"")="Sí",B114=""),"Falta el N° de entrega",IF(N(I114)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -4144,7 +4147,7 @@
         <v/>
       </c>
       <c r="H115" s="9">
-        <f>IF(A115="","",IFERROR(VLOOKUP(A115,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A115="","",IFERROR(IF(VLOOKUP(A115,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A115,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I115" s="10">
@@ -4160,7 +4163,7 @@
         <v/>
       </c>
       <c r="L115" s="9">
-        <f>IF(AND(A115="",C115=""),"",IF(A115="","Falta el tipo",IF(C115="","Falta el código",IF(ISNA(MATCH(C115,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D115)&gt;0,N(VLOOKUP(C115,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A115,TIPOS!$A:$C,3,FALSE),"")="Sí",B115=""),"Falta el N° de entrega",IF(N(I115)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A115="",C115=""),"",IF(A115="","Falta el tipo",IF(H115="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C115="","Falta el código",IF(ISNA(MATCH(C115,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D115)&gt;0,N(VLOOKUP(C115,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A115,TIPOS!$A:$C,3,FALSE),"")="Sí",B115=""),"Falta el N° de entrega",IF(N(I115)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -4176,7 +4179,7 @@
         <v/>
       </c>
       <c r="H116" s="9">
-        <f>IF(A116="","",IFERROR(VLOOKUP(A116,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A116="","",IFERROR(IF(VLOOKUP(A116,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A116,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I116" s="10">
@@ -4192,7 +4195,7 @@
         <v/>
       </c>
       <c r="L116" s="9">
-        <f>IF(AND(A116="",C116=""),"",IF(A116="","Falta el tipo",IF(C116="","Falta el código",IF(ISNA(MATCH(C116,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D116)&gt;0,N(VLOOKUP(C116,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A116,TIPOS!$A:$C,3,FALSE),"")="Sí",B116=""),"Falta el N° de entrega",IF(N(I116)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A116="",C116=""),"",IF(A116="","Falta el tipo",IF(H116="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C116="","Falta el código",IF(ISNA(MATCH(C116,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D116)&gt;0,N(VLOOKUP(C116,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A116,TIPOS!$A:$C,3,FALSE),"")="Sí",B116=""),"Falta el N° de entrega",IF(N(I116)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -4208,7 +4211,7 @@
         <v/>
       </c>
       <c r="H117" s="9">
-        <f>IF(A117="","",IFERROR(VLOOKUP(A117,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A117="","",IFERROR(IF(VLOOKUP(A117,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A117,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I117" s="10">
@@ -4224,7 +4227,7 @@
         <v/>
       </c>
       <c r="L117" s="9">
-        <f>IF(AND(A117="",C117=""),"",IF(A117="","Falta el tipo",IF(C117="","Falta el código",IF(ISNA(MATCH(C117,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D117)&gt;0,N(VLOOKUP(C117,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A117,TIPOS!$A:$C,3,FALSE),"")="Sí",B117=""),"Falta el N° de entrega",IF(N(I117)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A117="",C117=""),"",IF(A117="","Falta el tipo",IF(H117="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C117="","Falta el código",IF(ISNA(MATCH(C117,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D117)&gt;0,N(VLOOKUP(C117,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A117,TIPOS!$A:$C,3,FALSE),"")="Sí",B117=""),"Falta el N° de entrega",IF(N(I117)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -4240,7 +4243,7 @@
         <v/>
       </c>
       <c r="H118" s="9">
-        <f>IF(A118="","",IFERROR(VLOOKUP(A118,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A118="","",IFERROR(IF(VLOOKUP(A118,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A118,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I118" s="10">
@@ -4256,7 +4259,7 @@
         <v/>
       </c>
       <c r="L118" s="9">
-        <f>IF(AND(A118="",C118=""),"",IF(A118="","Falta el tipo",IF(C118="","Falta el código",IF(ISNA(MATCH(C118,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D118)&gt;0,N(VLOOKUP(C118,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A118,TIPOS!$A:$C,3,FALSE),"")="Sí",B118=""),"Falta el N° de entrega",IF(N(I118)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A118="",C118=""),"",IF(A118="","Falta el tipo",IF(H118="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C118="","Falta el código",IF(ISNA(MATCH(C118,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D118)&gt;0,N(VLOOKUP(C118,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A118,TIPOS!$A:$C,3,FALSE),"")="Sí",B118=""),"Falta el N° de entrega",IF(N(I118)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -4272,7 +4275,7 @@
         <v/>
       </c>
       <c r="H119" s="9">
-        <f>IF(A119="","",IFERROR(VLOOKUP(A119,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A119="","",IFERROR(IF(VLOOKUP(A119,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A119,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I119" s="10">
@@ -4288,7 +4291,7 @@
         <v/>
       </c>
       <c r="L119" s="9">
-        <f>IF(AND(A119="",C119=""),"",IF(A119="","Falta el tipo",IF(C119="","Falta el código",IF(ISNA(MATCH(C119,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D119)&gt;0,N(VLOOKUP(C119,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A119,TIPOS!$A:$C,3,FALSE),"")="Sí",B119=""),"Falta el N° de entrega",IF(N(I119)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A119="",C119=""),"",IF(A119="","Falta el tipo",IF(H119="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C119="","Falta el código",IF(ISNA(MATCH(C119,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D119)&gt;0,N(VLOOKUP(C119,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A119,TIPOS!$A:$C,3,FALSE),"")="Sí",B119=""),"Falta el N° de entrega",IF(N(I119)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -4304,7 +4307,7 @@
         <v/>
       </c>
       <c r="H120" s="9">
-        <f>IF(A120="","",IFERROR(VLOOKUP(A120,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A120="","",IFERROR(IF(VLOOKUP(A120,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A120,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I120" s="10">
@@ -4320,7 +4323,7 @@
         <v/>
       </c>
       <c r="L120" s="9">
-        <f>IF(AND(A120="",C120=""),"",IF(A120="","Falta el tipo",IF(C120="","Falta el código",IF(ISNA(MATCH(C120,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D120)&gt;0,N(VLOOKUP(C120,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A120,TIPOS!$A:$C,3,FALSE),"")="Sí",B120=""),"Falta el N° de entrega",IF(N(I120)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A120="",C120=""),"",IF(A120="","Falta el tipo",IF(H120="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C120="","Falta el código",IF(ISNA(MATCH(C120,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D120)&gt;0,N(VLOOKUP(C120,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A120,TIPOS!$A:$C,3,FALSE),"")="Sí",B120=""),"Falta el N° de entrega",IF(N(I120)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -4336,7 +4339,7 @@
         <v/>
       </c>
       <c r="H121" s="9">
-        <f>IF(A121="","",IFERROR(VLOOKUP(A121,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A121="","",IFERROR(IF(VLOOKUP(A121,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A121,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I121" s="10">
@@ -4352,7 +4355,7 @@
         <v/>
       </c>
       <c r="L121" s="9">
-        <f>IF(AND(A121="",C121=""),"",IF(A121="","Falta el tipo",IF(C121="","Falta el código",IF(ISNA(MATCH(C121,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D121)&gt;0,N(VLOOKUP(C121,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A121,TIPOS!$A:$C,3,FALSE),"")="Sí",B121=""),"Falta el N° de entrega",IF(N(I121)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A121="",C121=""),"",IF(A121="","Falta el tipo",IF(H121="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C121="","Falta el código",IF(ISNA(MATCH(C121,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D121)&gt;0,N(VLOOKUP(C121,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A121,TIPOS!$A:$C,3,FALSE),"")="Sí",B121=""),"Falta el N° de entrega",IF(N(I121)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -4368,7 +4371,7 @@
         <v/>
       </c>
       <c r="H122" s="9">
-        <f>IF(A122="","",IFERROR(VLOOKUP(A122,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A122="","",IFERROR(IF(VLOOKUP(A122,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A122,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I122" s="10">
@@ -4384,7 +4387,7 @@
         <v/>
       </c>
       <c r="L122" s="9">
-        <f>IF(AND(A122="",C122=""),"",IF(A122="","Falta el tipo",IF(C122="","Falta el código",IF(ISNA(MATCH(C122,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D122)&gt;0,N(VLOOKUP(C122,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A122,TIPOS!$A:$C,3,FALSE),"")="Sí",B122=""),"Falta el N° de entrega",IF(N(I122)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A122="",C122=""),"",IF(A122="","Falta el tipo",IF(H122="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C122="","Falta el código",IF(ISNA(MATCH(C122,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D122)&gt;0,N(VLOOKUP(C122,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A122,TIPOS!$A:$C,3,FALSE),"")="Sí",B122=""),"Falta el N° de entrega",IF(N(I122)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -4400,7 +4403,7 @@
         <v/>
       </c>
       <c r="H123" s="9">
-        <f>IF(A123="","",IFERROR(VLOOKUP(A123,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A123="","",IFERROR(IF(VLOOKUP(A123,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A123,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I123" s="10">
@@ -4416,7 +4419,7 @@
         <v/>
       </c>
       <c r="L123" s="9">
-        <f>IF(AND(A123="",C123=""),"",IF(A123="","Falta el tipo",IF(C123="","Falta el código",IF(ISNA(MATCH(C123,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D123)&gt;0,N(VLOOKUP(C123,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A123,TIPOS!$A:$C,3,FALSE),"")="Sí",B123=""),"Falta el N° de entrega",IF(N(I123)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A123="",C123=""),"",IF(A123="","Falta el tipo",IF(H123="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C123="","Falta el código",IF(ISNA(MATCH(C123,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D123)&gt;0,N(VLOOKUP(C123,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A123,TIPOS!$A:$C,3,FALSE),"")="Sí",B123=""),"Falta el N° de entrega",IF(N(I123)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -4432,7 +4435,7 @@
         <v/>
       </c>
       <c r="H124" s="9">
-        <f>IF(A124="","",IFERROR(VLOOKUP(A124,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A124="","",IFERROR(IF(VLOOKUP(A124,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A124,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I124" s="10">
@@ -4448,7 +4451,7 @@
         <v/>
       </c>
       <c r="L124" s="9">
-        <f>IF(AND(A124="",C124=""),"",IF(A124="","Falta el tipo",IF(C124="","Falta el código",IF(ISNA(MATCH(C124,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D124)&gt;0,N(VLOOKUP(C124,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A124,TIPOS!$A:$C,3,FALSE),"")="Sí",B124=""),"Falta el N° de entrega",IF(N(I124)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A124="",C124=""),"",IF(A124="","Falta el tipo",IF(H124="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C124="","Falta el código",IF(ISNA(MATCH(C124,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D124)&gt;0,N(VLOOKUP(C124,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A124,TIPOS!$A:$C,3,FALSE),"")="Sí",B124=""),"Falta el N° de entrega",IF(N(I124)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -4464,7 +4467,7 @@
         <v/>
       </c>
       <c r="H125" s="9">
-        <f>IF(A125="","",IFERROR(VLOOKUP(A125,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A125="","",IFERROR(IF(VLOOKUP(A125,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A125,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I125" s="10">
@@ -4480,7 +4483,7 @@
         <v/>
       </c>
       <c r="L125" s="9">
-        <f>IF(AND(A125="",C125=""),"",IF(A125="","Falta el tipo",IF(C125="","Falta el código",IF(ISNA(MATCH(C125,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D125)&gt;0,N(VLOOKUP(C125,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A125,TIPOS!$A:$C,3,FALSE),"")="Sí",B125=""),"Falta el N° de entrega",IF(N(I125)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A125="",C125=""),"",IF(A125="","Falta el tipo",IF(H125="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C125="","Falta el código",IF(ISNA(MATCH(C125,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D125)&gt;0,N(VLOOKUP(C125,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A125,TIPOS!$A:$C,3,FALSE),"")="Sí",B125=""),"Falta el N° de entrega",IF(N(I125)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -4496,7 +4499,7 @@
         <v/>
       </c>
       <c r="H126" s="9">
-        <f>IF(A126="","",IFERROR(VLOOKUP(A126,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A126="","",IFERROR(IF(VLOOKUP(A126,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A126,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I126" s="10">
@@ -4512,7 +4515,7 @@
         <v/>
       </c>
       <c r="L126" s="9">
-        <f>IF(AND(A126="",C126=""),"",IF(A126="","Falta el tipo",IF(C126="","Falta el código",IF(ISNA(MATCH(C126,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D126)&gt;0,N(VLOOKUP(C126,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A126,TIPOS!$A:$C,3,FALSE),"")="Sí",B126=""),"Falta el N° de entrega",IF(N(I126)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A126="",C126=""),"",IF(A126="","Falta el tipo",IF(H126="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C126="","Falta el código",IF(ISNA(MATCH(C126,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D126)&gt;0,N(VLOOKUP(C126,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A126,TIPOS!$A:$C,3,FALSE),"")="Sí",B126=""),"Falta el N° de entrega",IF(N(I126)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -4528,7 +4531,7 @@
         <v/>
       </c>
       <c r="H127" s="9">
-        <f>IF(A127="","",IFERROR(VLOOKUP(A127,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A127="","",IFERROR(IF(VLOOKUP(A127,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A127,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I127" s="10">
@@ -4544,7 +4547,7 @@
         <v/>
       </c>
       <c r="L127" s="9">
-        <f>IF(AND(A127="",C127=""),"",IF(A127="","Falta el tipo",IF(C127="","Falta el código",IF(ISNA(MATCH(C127,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D127)&gt;0,N(VLOOKUP(C127,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A127,TIPOS!$A:$C,3,FALSE),"")="Sí",B127=""),"Falta el N° de entrega",IF(N(I127)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A127="",C127=""),"",IF(A127="","Falta el tipo",IF(H127="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C127="","Falta el código",IF(ISNA(MATCH(C127,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D127)&gt;0,N(VLOOKUP(C127,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A127,TIPOS!$A:$C,3,FALSE),"")="Sí",B127=""),"Falta el N° de entrega",IF(N(I127)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -4560,7 +4563,7 @@
         <v/>
       </c>
       <c r="H128" s="9">
-        <f>IF(A128="","",IFERROR(VLOOKUP(A128,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A128="","",IFERROR(IF(VLOOKUP(A128,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A128,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I128" s="10">
@@ -4576,7 +4579,7 @@
         <v/>
       </c>
       <c r="L128" s="9">
-        <f>IF(AND(A128="",C128=""),"",IF(A128="","Falta el tipo",IF(C128="","Falta el código",IF(ISNA(MATCH(C128,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D128)&gt;0,N(VLOOKUP(C128,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A128,TIPOS!$A:$C,3,FALSE),"")="Sí",B128=""),"Falta el N° de entrega",IF(N(I128)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A128="",C128=""),"",IF(A128="","Falta el tipo",IF(H128="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C128="","Falta el código",IF(ISNA(MATCH(C128,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D128)&gt;0,N(VLOOKUP(C128,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A128,TIPOS!$A:$C,3,FALSE),"")="Sí",B128=""),"Falta el N° de entrega",IF(N(I128)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -4592,7 +4595,7 @@
         <v/>
       </c>
       <c r="H129" s="9">
-        <f>IF(A129="","",IFERROR(VLOOKUP(A129,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A129="","",IFERROR(IF(VLOOKUP(A129,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A129,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I129" s="10">
@@ -4608,7 +4611,7 @@
         <v/>
       </c>
       <c r="L129" s="9">
-        <f>IF(AND(A129="",C129=""),"",IF(A129="","Falta el tipo",IF(C129="","Falta el código",IF(ISNA(MATCH(C129,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D129)&gt;0,N(VLOOKUP(C129,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A129,TIPOS!$A:$C,3,FALSE),"")="Sí",B129=""),"Falta el N° de entrega",IF(N(I129)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A129="",C129=""),"",IF(A129="","Falta el tipo",IF(H129="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C129="","Falta el código",IF(ISNA(MATCH(C129,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D129)&gt;0,N(VLOOKUP(C129,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A129,TIPOS!$A:$C,3,FALSE),"")="Sí",B129=""),"Falta el N° de entrega",IF(N(I129)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -4624,7 +4627,7 @@
         <v/>
       </c>
       <c r="H130" s="9">
-        <f>IF(A130="","",IFERROR(VLOOKUP(A130,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A130="","",IFERROR(IF(VLOOKUP(A130,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A130,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I130" s="10">
@@ -4640,7 +4643,7 @@
         <v/>
       </c>
       <c r="L130" s="9">
-        <f>IF(AND(A130="",C130=""),"",IF(A130="","Falta el tipo",IF(C130="","Falta el código",IF(ISNA(MATCH(C130,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D130)&gt;0,N(VLOOKUP(C130,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A130,TIPOS!$A:$C,3,FALSE),"")="Sí",B130=""),"Falta el N° de entrega",IF(N(I130)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A130="",C130=""),"",IF(A130="","Falta el tipo",IF(H130="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C130="","Falta el código",IF(ISNA(MATCH(C130,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D130)&gt;0,N(VLOOKUP(C130,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A130,TIPOS!$A:$C,3,FALSE),"")="Sí",B130=""),"Falta el N° de entrega",IF(N(I130)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -4656,7 +4659,7 @@
         <v/>
       </c>
       <c r="H131" s="9">
-        <f>IF(A131="","",IFERROR(VLOOKUP(A131,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A131="","",IFERROR(IF(VLOOKUP(A131,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A131,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I131" s="10">
@@ -4672,7 +4675,7 @@
         <v/>
       </c>
       <c r="L131" s="9">
-        <f>IF(AND(A131="",C131=""),"",IF(A131="","Falta el tipo",IF(C131="","Falta el código",IF(ISNA(MATCH(C131,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D131)&gt;0,N(VLOOKUP(C131,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A131,TIPOS!$A:$C,3,FALSE),"")="Sí",B131=""),"Falta el N° de entrega",IF(N(I131)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A131="",C131=""),"",IF(A131="","Falta el tipo",IF(H131="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C131="","Falta el código",IF(ISNA(MATCH(C131,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D131)&gt;0,N(VLOOKUP(C131,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A131,TIPOS!$A:$C,3,FALSE),"")="Sí",B131=""),"Falta el N° de entrega",IF(N(I131)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -4688,7 +4691,7 @@
         <v/>
       </c>
       <c r="H132" s="9">
-        <f>IF(A132="","",IFERROR(VLOOKUP(A132,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A132="","",IFERROR(IF(VLOOKUP(A132,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A132,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I132" s="10">
@@ -4704,7 +4707,7 @@
         <v/>
       </c>
       <c r="L132" s="9">
-        <f>IF(AND(A132="",C132=""),"",IF(A132="","Falta el tipo",IF(C132="","Falta el código",IF(ISNA(MATCH(C132,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D132)&gt;0,N(VLOOKUP(C132,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A132,TIPOS!$A:$C,3,FALSE),"")="Sí",B132=""),"Falta el N° de entrega",IF(N(I132)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A132="",C132=""),"",IF(A132="","Falta el tipo",IF(H132="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C132="","Falta el código",IF(ISNA(MATCH(C132,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D132)&gt;0,N(VLOOKUP(C132,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A132,TIPOS!$A:$C,3,FALSE),"")="Sí",B132=""),"Falta el N° de entrega",IF(N(I132)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -4720,7 +4723,7 @@
         <v/>
       </c>
       <c r="H133" s="9">
-        <f>IF(A133="","",IFERROR(VLOOKUP(A133,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A133="","",IFERROR(IF(VLOOKUP(A133,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A133,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I133" s="10">
@@ -4736,7 +4739,7 @@
         <v/>
       </c>
       <c r="L133" s="9">
-        <f>IF(AND(A133="",C133=""),"",IF(A133="","Falta el tipo",IF(C133="","Falta el código",IF(ISNA(MATCH(C133,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D133)&gt;0,N(VLOOKUP(C133,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A133,TIPOS!$A:$C,3,FALSE),"")="Sí",B133=""),"Falta el N° de entrega",IF(N(I133)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A133="",C133=""),"",IF(A133="","Falta el tipo",IF(H133="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C133="","Falta el código",IF(ISNA(MATCH(C133,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D133)&gt;0,N(VLOOKUP(C133,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A133,TIPOS!$A:$C,3,FALSE),"")="Sí",B133=""),"Falta el N° de entrega",IF(N(I133)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -4752,7 +4755,7 @@
         <v/>
       </c>
       <c r="H134" s="9">
-        <f>IF(A134="","",IFERROR(VLOOKUP(A134,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A134="","",IFERROR(IF(VLOOKUP(A134,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A134,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I134" s="10">
@@ -4768,7 +4771,7 @@
         <v/>
       </c>
       <c r="L134" s="9">
-        <f>IF(AND(A134="",C134=""),"",IF(A134="","Falta el tipo",IF(C134="","Falta el código",IF(ISNA(MATCH(C134,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D134)&gt;0,N(VLOOKUP(C134,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A134,TIPOS!$A:$C,3,FALSE),"")="Sí",B134=""),"Falta el N° de entrega",IF(N(I134)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A134="",C134=""),"",IF(A134="","Falta el tipo",IF(H134="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C134="","Falta el código",IF(ISNA(MATCH(C134,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D134)&gt;0,N(VLOOKUP(C134,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A134,TIPOS!$A:$C,3,FALSE),"")="Sí",B134=""),"Falta el N° de entrega",IF(N(I134)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -4784,7 +4787,7 @@
         <v/>
       </c>
       <c r="H135" s="9">
-        <f>IF(A135="","",IFERROR(VLOOKUP(A135,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A135="","",IFERROR(IF(VLOOKUP(A135,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A135,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I135" s="10">
@@ -4800,7 +4803,7 @@
         <v/>
       </c>
       <c r="L135" s="9">
-        <f>IF(AND(A135="",C135=""),"",IF(A135="","Falta el tipo",IF(C135="","Falta el código",IF(ISNA(MATCH(C135,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D135)&gt;0,N(VLOOKUP(C135,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A135,TIPOS!$A:$C,3,FALSE),"")="Sí",B135=""),"Falta el N° de entrega",IF(N(I135)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A135="",C135=""),"",IF(A135="","Falta el tipo",IF(H135="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C135="","Falta el código",IF(ISNA(MATCH(C135,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D135)&gt;0,N(VLOOKUP(C135,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A135,TIPOS!$A:$C,3,FALSE),"")="Sí",B135=""),"Falta el N° de entrega",IF(N(I135)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -4816,7 +4819,7 @@
         <v/>
       </c>
       <c r="H136" s="9">
-        <f>IF(A136="","",IFERROR(VLOOKUP(A136,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A136="","",IFERROR(IF(VLOOKUP(A136,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A136,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I136" s="10">
@@ -4832,7 +4835,7 @@
         <v/>
       </c>
       <c r="L136" s="9">
-        <f>IF(AND(A136="",C136=""),"",IF(A136="","Falta el tipo",IF(C136="","Falta el código",IF(ISNA(MATCH(C136,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D136)&gt;0,N(VLOOKUP(C136,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A136,TIPOS!$A:$C,3,FALSE),"")="Sí",B136=""),"Falta el N° de entrega",IF(N(I136)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A136="",C136=""),"",IF(A136="","Falta el tipo",IF(H136="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C136="","Falta el código",IF(ISNA(MATCH(C136,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D136)&gt;0,N(VLOOKUP(C136,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A136,TIPOS!$A:$C,3,FALSE),"")="Sí",B136=""),"Falta el N° de entrega",IF(N(I136)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -4848,7 +4851,7 @@
         <v/>
       </c>
       <c r="H137" s="9">
-        <f>IF(A137="","",IFERROR(VLOOKUP(A137,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A137="","",IFERROR(IF(VLOOKUP(A137,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A137,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I137" s="10">
@@ -4864,7 +4867,7 @@
         <v/>
       </c>
       <c r="L137" s="9">
-        <f>IF(AND(A137="",C137=""),"",IF(A137="","Falta el tipo",IF(C137="","Falta el código",IF(ISNA(MATCH(C137,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D137)&gt;0,N(VLOOKUP(C137,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A137,TIPOS!$A:$C,3,FALSE),"")="Sí",B137=""),"Falta el N° de entrega",IF(N(I137)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A137="",C137=""),"",IF(A137="","Falta el tipo",IF(H137="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C137="","Falta el código",IF(ISNA(MATCH(C137,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D137)&gt;0,N(VLOOKUP(C137,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A137,TIPOS!$A:$C,3,FALSE),"")="Sí",B137=""),"Falta el N° de entrega",IF(N(I137)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -4880,7 +4883,7 @@
         <v/>
       </c>
       <c r="H138" s="9">
-        <f>IF(A138="","",IFERROR(VLOOKUP(A138,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A138="","",IFERROR(IF(VLOOKUP(A138,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A138,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I138" s="10">
@@ -4896,7 +4899,7 @@
         <v/>
       </c>
       <c r="L138" s="9">
-        <f>IF(AND(A138="",C138=""),"",IF(A138="","Falta el tipo",IF(C138="","Falta el código",IF(ISNA(MATCH(C138,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D138)&gt;0,N(VLOOKUP(C138,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A138,TIPOS!$A:$C,3,FALSE),"")="Sí",B138=""),"Falta el N° de entrega",IF(N(I138)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A138="",C138=""),"",IF(A138="","Falta el tipo",IF(H138="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C138="","Falta el código",IF(ISNA(MATCH(C138,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D138)&gt;0,N(VLOOKUP(C138,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A138,TIPOS!$A:$C,3,FALSE),"")="Sí",B138=""),"Falta el N° de entrega",IF(N(I138)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -4912,7 +4915,7 @@
         <v/>
       </c>
       <c r="H139" s="9">
-        <f>IF(A139="","",IFERROR(VLOOKUP(A139,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A139="","",IFERROR(IF(VLOOKUP(A139,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A139,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I139" s="10">
@@ -4928,7 +4931,7 @@
         <v/>
       </c>
       <c r="L139" s="9">
-        <f>IF(AND(A139="",C139=""),"",IF(A139="","Falta el tipo",IF(C139="","Falta el código",IF(ISNA(MATCH(C139,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D139)&gt;0,N(VLOOKUP(C139,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A139,TIPOS!$A:$C,3,FALSE),"")="Sí",B139=""),"Falta el N° de entrega",IF(N(I139)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A139="",C139=""),"",IF(A139="","Falta el tipo",IF(H139="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C139="","Falta el código",IF(ISNA(MATCH(C139,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D139)&gt;0,N(VLOOKUP(C139,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A139,TIPOS!$A:$C,3,FALSE),"")="Sí",B139=""),"Falta el N° de entrega",IF(N(I139)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -4944,7 +4947,7 @@
         <v/>
       </c>
       <c r="H140" s="9">
-        <f>IF(A140="","",IFERROR(VLOOKUP(A140,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A140="","",IFERROR(IF(VLOOKUP(A140,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A140,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I140" s="10">
@@ -4960,7 +4963,7 @@
         <v/>
       </c>
       <c r="L140" s="9">
-        <f>IF(AND(A140="",C140=""),"",IF(A140="","Falta el tipo",IF(C140="","Falta el código",IF(ISNA(MATCH(C140,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D140)&gt;0,N(VLOOKUP(C140,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A140,TIPOS!$A:$C,3,FALSE),"")="Sí",B140=""),"Falta el N° de entrega",IF(N(I140)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A140="",C140=""),"",IF(A140="","Falta el tipo",IF(H140="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C140="","Falta el código",IF(ISNA(MATCH(C140,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D140)&gt;0,N(VLOOKUP(C140,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A140,TIPOS!$A:$C,3,FALSE),"")="Sí",B140=""),"Falta el N° de entrega",IF(N(I140)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -4976,7 +4979,7 @@
         <v/>
       </c>
       <c r="H141" s="9">
-        <f>IF(A141="","",IFERROR(VLOOKUP(A141,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A141="","",IFERROR(IF(VLOOKUP(A141,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A141,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I141" s="10">
@@ -4992,7 +4995,7 @@
         <v/>
       </c>
       <c r="L141" s="9">
-        <f>IF(AND(A141="",C141=""),"",IF(A141="","Falta el tipo",IF(C141="","Falta el código",IF(ISNA(MATCH(C141,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D141)&gt;0,N(VLOOKUP(C141,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A141,TIPOS!$A:$C,3,FALSE),"")="Sí",B141=""),"Falta el N° de entrega",IF(N(I141)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A141="",C141=""),"",IF(A141="","Falta el tipo",IF(H141="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C141="","Falta el código",IF(ISNA(MATCH(C141,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D141)&gt;0,N(VLOOKUP(C141,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A141,TIPOS!$A:$C,3,FALSE),"")="Sí",B141=""),"Falta el N° de entrega",IF(N(I141)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -5008,7 +5011,7 @@
         <v/>
       </c>
       <c r="H142" s="9">
-        <f>IF(A142="","",IFERROR(VLOOKUP(A142,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A142="","",IFERROR(IF(VLOOKUP(A142,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A142,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I142" s="10">
@@ -5024,7 +5027,7 @@
         <v/>
       </c>
       <c r="L142" s="9">
-        <f>IF(AND(A142="",C142=""),"",IF(A142="","Falta el tipo",IF(C142="","Falta el código",IF(ISNA(MATCH(C142,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D142)&gt;0,N(VLOOKUP(C142,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A142,TIPOS!$A:$C,3,FALSE),"")="Sí",B142=""),"Falta el N° de entrega",IF(N(I142)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A142="",C142=""),"",IF(A142="","Falta el tipo",IF(H142="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C142="","Falta el código",IF(ISNA(MATCH(C142,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D142)&gt;0,N(VLOOKUP(C142,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A142,TIPOS!$A:$C,3,FALSE),"")="Sí",B142=""),"Falta el N° de entrega",IF(N(I142)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -5040,7 +5043,7 @@
         <v/>
       </c>
       <c r="H143" s="9">
-        <f>IF(A143="","",IFERROR(VLOOKUP(A143,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A143="","",IFERROR(IF(VLOOKUP(A143,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A143,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I143" s="10">
@@ -5056,7 +5059,7 @@
         <v/>
       </c>
       <c r="L143" s="9">
-        <f>IF(AND(A143="",C143=""),"",IF(A143="","Falta el tipo",IF(C143="","Falta el código",IF(ISNA(MATCH(C143,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D143)&gt;0,N(VLOOKUP(C143,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A143,TIPOS!$A:$C,3,FALSE),"")="Sí",B143=""),"Falta el N° de entrega",IF(N(I143)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A143="",C143=""),"",IF(A143="","Falta el tipo",IF(H143="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C143="","Falta el código",IF(ISNA(MATCH(C143,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D143)&gt;0,N(VLOOKUP(C143,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A143,TIPOS!$A:$C,3,FALSE),"")="Sí",B143=""),"Falta el N° de entrega",IF(N(I143)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -5072,7 +5075,7 @@
         <v/>
       </c>
       <c r="H144" s="9">
-        <f>IF(A144="","",IFERROR(VLOOKUP(A144,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A144="","",IFERROR(IF(VLOOKUP(A144,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A144,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I144" s="10">
@@ -5088,7 +5091,7 @@
         <v/>
       </c>
       <c r="L144" s="9">
-        <f>IF(AND(A144="",C144=""),"",IF(A144="","Falta el tipo",IF(C144="","Falta el código",IF(ISNA(MATCH(C144,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D144)&gt;0,N(VLOOKUP(C144,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A144,TIPOS!$A:$C,3,FALSE),"")="Sí",B144=""),"Falta el N° de entrega",IF(N(I144)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A144="",C144=""),"",IF(A144="","Falta el tipo",IF(H144="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C144="","Falta el código",IF(ISNA(MATCH(C144,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D144)&gt;0,N(VLOOKUP(C144,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A144,TIPOS!$A:$C,3,FALSE),"")="Sí",B144=""),"Falta el N° de entrega",IF(N(I144)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -5104,7 +5107,7 @@
         <v/>
       </c>
       <c r="H145" s="9">
-        <f>IF(A145="","",IFERROR(VLOOKUP(A145,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A145="","",IFERROR(IF(VLOOKUP(A145,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A145,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I145" s="10">
@@ -5120,7 +5123,7 @@
         <v/>
       </c>
       <c r="L145" s="9">
-        <f>IF(AND(A145="",C145=""),"",IF(A145="","Falta el tipo",IF(C145="","Falta el código",IF(ISNA(MATCH(C145,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D145)&gt;0,N(VLOOKUP(C145,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A145,TIPOS!$A:$C,3,FALSE),"")="Sí",B145=""),"Falta el N° de entrega",IF(N(I145)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A145="",C145=""),"",IF(A145="","Falta el tipo",IF(H145="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C145="","Falta el código",IF(ISNA(MATCH(C145,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D145)&gt;0,N(VLOOKUP(C145,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A145,TIPOS!$A:$C,3,FALSE),"")="Sí",B145=""),"Falta el N° de entrega",IF(N(I145)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -5136,7 +5139,7 @@
         <v/>
       </c>
       <c r="H146" s="9">
-        <f>IF(A146="","",IFERROR(VLOOKUP(A146,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A146="","",IFERROR(IF(VLOOKUP(A146,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A146,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I146" s="10">
@@ -5152,7 +5155,7 @@
         <v/>
       </c>
       <c r="L146" s="9">
-        <f>IF(AND(A146="",C146=""),"",IF(A146="","Falta el tipo",IF(C146="","Falta el código",IF(ISNA(MATCH(C146,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D146)&gt;0,N(VLOOKUP(C146,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A146,TIPOS!$A:$C,3,FALSE),"")="Sí",B146=""),"Falta el N° de entrega",IF(N(I146)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A146="",C146=""),"",IF(A146="","Falta el tipo",IF(H146="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C146="","Falta el código",IF(ISNA(MATCH(C146,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D146)&gt;0,N(VLOOKUP(C146,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A146,TIPOS!$A:$C,3,FALSE),"")="Sí",B146=""),"Falta el N° de entrega",IF(N(I146)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -5168,7 +5171,7 @@
         <v/>
       </c>
       <c r="H147" s="9">
-        <f>IF(A147="","",IFERROR(VLOOKUP(A147,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A147="","",IFERROR(IF(VLOOKUP(A147,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A147,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I147" s="10">
@@ -5184,7 +5187,7 @@
         <v/>
       </c>
       <c r="L147" s="9">
-        <f>IF(AND(A147="",C147=""),"",IF(A147="","Falta el tipo",IF(C147="","Falta el código",IF(ISNA(MATCH(C147,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D147)&gt;0,N(VLOOKUP(C147,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A147,TIPOS!$A:$C,3,FALSE),"")="Sí",B147=""),"Falta el N° de entrega",IF(N(I147)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A147="",C147=""),"",IF(A147="","Falta el tipo",IF(H147="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C147="","Falta el código",IF(ISNA(MATCH(C147,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D147)&gt;0,N(VLOOKUP(C147,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A147,TIPOS!$A:$C,3,FALSE),"")="Sí",B147=""),"Falta el N° de entrega",IF(N(I147)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -5200,7 +5203,7 @@
         <v/>
       </c>
       <c r="H148" s="9">
-        <f>IF(A148="","",IFERROR(VLOOKUP(A148,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A148="","",IFERROR(IF(VLOOKUP(A148,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A148,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I148" s="10">
@@ -5216,7 +5219,7 @@
         <v/>
       </c>
       <c r="L148" s="9">
-        <f>IF(AND(A148="",C148=""),"",IF(A148="","Falta el tipo",IF(C148="","Falta el código",IF(ISNA(MATCH(C148,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D148)&gt;0,N(VLOOKUP(C148,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A148,TIPOS!$A:$C,3,FALSE),"")="Sí",B148=""),"Falta el N° de entrega",IF(N(I148)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A148="",C148=""),"",IF(A148="","Falta el tipo",IF(H148="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C148="","Falta el código",IF(ISNA(MATCH(C148,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D148)&gt;0,N(VLOOKUP(C148,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A148,TIPOS!$A:$C,3,FALSE),"")="Sí",B148=""),"Falta el N° de entrega",IF(N(I148)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -5232,7 +5235,7 @@
         <v/>
       </c>
       <c r="H149" s="9">
-        <f>IF(A149="","",IFERROR(VLOOKUP(A149,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A149="","",IFERROR(IF(VLOOKUP(A149,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A149,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I149" s="10">
@@ -5248,7 +5251,7 @@
         <v/>
       </c>
       <c r="L149" s="9">
-        <f>IF(AND(A149="",C149=""),"",IF(A149="","Falta el tipo",IF(C149="","Falta el código",IF(ISNA(MATCH(C149,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D149)&gt;0,N(VLOOKUP(C149,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A149,TIPOS!$A:$C,3,FALSE),"")="Sí",B149=""),"Falta el N° de entrega",IF(N(I149)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A149="",C149=""),"",IF(A149="","Falta el tipo",IF(H149="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C149="","Falta el código",IF(ISNA(MATCH(C149,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D149)&gt;0,N(VLOOKUP(C149,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A149,TIPOS!$A:$C,3,FALSE),"")="Sí",B149=""),"Falta el N° de entrega",IF(N(I149)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -5264,7 +5267,7 @@
         <v/>
       </c>
       <c r="H150" s="9">
-        <f>IF(A150="","",IFERROR(VLOOKUP(A150,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A150="","",IFERROR(IF(VLOOKUP(A150,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A150,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I150" s="10">
@@ -5280,7 +5283,7 @@
         <v/>
       </c>
       <c r="L150" s="9">
-        <f>IF(AND(A150="",C150=""),"",IF(A150="","Falta el tipo",IF(C150="","Falta el código",IF(ISNA(MATCH(C150,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D150)&gt;0,N(VLOOKUP(C150,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A150,TIPOS!$A:$C,3,FALSE),"")="Sí",B150=""),"Falta el N° de entrega",IF(N(I150)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A150="",C150=""),"",IF(A150="","Falta el tipo",IF(H150="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C150="","Falta el código",IF(ISNA(MATCH(C150,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D150)&gt;0,N(VLOOKUP(C150,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A150,TIPOS!$A:$C,3,FALSE),"")="Sí",B150=""),"Falta el N° de entrega",IF(N(I150)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -5296,7 +5299,7 @@
         <v/>
       </c>
       <c r="H151" s="9">
-        <f>IF(A151="","",IFERROR(VLOOKUP(A151,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A151="","",IFERROR(IF(VLOOKUP(A151,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A151,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I151" s="10">
@@ -5312,7 +5315,7 @@
         <v/>
       </c>
       <c r="L151" s="9">
-        <f>IF(AND(A151="",C151=""),"",IF(A151="","Falta el tipo",IF(C151="","Falta el código",IF(ISNA(MATCH(C151,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D151)&gt;0,N(VLOOKUP(C151,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A151,TIPOS!$A:$C,3,FALSE),"")="Sí",B151=""),"Falta el N° de entrega",IF(N(I151)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A151="",C151=""),"",IF(A151="","Falta el tipo",IF(H151="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C151="","Falta el código",IF(ISNA(MATCH(C151,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D151)&gt;0,N(VLOOKUP(C151,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A151,TIPOS!$A:$C,3,FALSE),"")="Sí",B151=""),"Falta el N° de entrega",IF(N(I151)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -5328,7 +5331,7 @@
         <v/>
       </c>
       <c r="H152" s="9">
-        <f>IF(A152="","",IFERROR(VLOOKUP(A152,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A152="","",IFERROR(IF(VLOOKUP(A152,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A152,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I152" s="10">
@@ -5344,7 +5347,7 @@
         <v/>
       </c>
       <c r="L152" s="9">
-        <f>IF(AND(A152="",C152=""),"",IF(A152="","Falta el tipo",IF(C152="","Falta el código",IF(ISNA(MATCH(C152,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D152)&gt;0,N(VLOOKUP(C152,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A152,TIPOS!$A:$C,3,FALSE),"")="Sí",B152=""),"Falta el N° de entrega",IF(N(I152)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A152="",C152=""),"",IF(A152="","Falta el tipo",IF(H152="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C152="","Falta el código",IF(ISNA(MATCH(C152,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D152)&gt;0,N(VLOOKUP(C152,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A152,TIPOS!$A:$C,3,FALSE),"")="Sí",B152=""),"Falta el N° de entrega",IF(N(I152)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -5360,7 +5363,7 @@
         <v/>
       </c>
       <c r="H153" s="9">
-        <f>IF(A153="","",IFERROR(VLOOKUP(A153,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A153="","",IFERROR(IF(VLOOKUP(A153,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A153,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I153" s="10">
@@ -5376,7 +5379,7 @@
         <v/>
       </c>
       <c r="L153" s="9">
-        <f>IF(AND(A153="",C153=""),"",IF(A153="","Falta el tipo",IF(C153="","Falta el código",IF(ISNA(MATCH(C153,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D153)&gt;0,N(VLOOKUP(C153,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A153,TIPOS!$A:$C,3,FALSE),"")="Sí",B153=""),"Falta el N° de entrega",IF(N(I153)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A153="",C153=""),"",IF(A153="","Falta el tipo",IF(H153="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C153="","Falta el código",IF(ISNA(MATCH(C153,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D153)&gt;0,N(VLOOKUP(C153,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A153,TIPOS!$A:$C,3,FALSE),"")="Sí",B153=""),"Falta el N° de entrega",IF(N(I153)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -5392,7 +5395,7 @@
         <v/>
       </c>
       <c r="H154" s="9">
-        <f>IF(A154="","",IFERROR(VLOOKUP(A154,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A154="","",IFERROR(IF(VLOOKUP(A154,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A154,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I154" s="10">
@@ -5408,7 +5411,7 @@
         <v/>
       </c>
       <c r="L154" s="9">
-        <f>IF(AND(A154="",C154=""),"",IF(A154="","Falta el tipo",IF(C154="","Falta el código",IF(ISNA(MATCH(C154,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D154)&gt;0,N(VLOOKUP(C154,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A154,TIPOS!$A:$C,3,FALSE),"")="Sí",B154=""),"Falta el N° de entrega",IF(N(I154)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A154="",C154=""),"",IF(A154="","Falta el tipo",IF(H154="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C154="","Falta el código",IF(ISNA(MATCH(C154,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D154)&gt;0,N(VLOOKUP(C154,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A154,TIPOS!$A:$C,3,FALSE),"")="Sí",B154=""),"Falta el N° de entrega",IF(N(I154)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -5424,7 +5427,7 @@
         <v/>
       </c>
       <c r="H155" s="9">
-        <f>IF(A155="","",IFERROR(VLOOKUP(A155,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A155="","",IFERROR(IF(VLOOKUP(A155,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A155,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I155" s="10">
@@ -5440,7 +5443,7 @@
         <v/>
       </c>
       <c r="L155" s="9">
-        <f>IF(AND(A155="",C155=""),"",IF(A155="","Falta el tipo",IF(C155="","Falta el código",IF(ISNA(MATCH(C155,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D155)&gt;0,N(VLOOKUP(C155,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A155,TIPOS!$A:$C,3,FALSE),"")="Sí",B155=""),"Falta el N° de entrega",IF(N(I155)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A155="",C155=""),"",IF(A155="","Falta el tipo",IF(H155="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C155="","Falta el código",IF(ISNA(MATCH(C155,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D155)&gt;0,N(VLOOKUP(C155,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A155,TIPOS!$A:$C,3,FALSE),"")="Sí",B155=""),"Falta el N° de entrega",IF(N(I155)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -5456,7 +5459,7 @@
         <v/>
       </c>
       <c r="H156" s="9">
-        <f>IF(A156="","",IFERROR(VLOOKUP(A156,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A156="","",IFERROR(IF(VLOOKUP(A156,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A156,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I156" s="10">
@@ -5472,7 +5475,7 @@
         <v/>
       </c>
       <c r="L156" s="9">
-        <f>IF(AND(A156="",C156=""),"",IF(A156="","Falta el tipo",IF(C156="","Falta el código",IF(ISNA(MATCH(C156,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D156)&gt;0,N(VLOOKUP(C156,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A156,TIPOS!$A:$C,3,FALSE),"")="Sí",B156=""),"Falta el N° de entrega",IF(N(I156)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A156="",C156=""),"",IF(A156="","Falta el tipo",IF(H156="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C156="","Falta el código",IF(ISNA(MATCH(C156,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D156)&gt;0,N(VLOOKUP(C156,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A156,TIPOS!$A:$C,3,FALSE),"")="Sí",B156=""),"Falta el N° de entrega",IF(N(I156)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -5488,7 +5491,7 @@
         <v/>
       </c>
       <c r="H157" s="9">
-        <f>IF(A157="","",IFERROR(VLOOKUP(A157,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A157="","",IFERROR(IF(VLOOKUP(A157,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A157,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I157" s="10">
@@ -5504,7 +5507,7 @@
         <v/>
       </c>
       <c r="L157" s="9">
-        <f>IF(AND(A157="",C157=""),"",IF(A157="","Falta el tipo",IF(C157="","Falta el código",IF(ISNA(MATCH(C157,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D157)&gt;0,N(VLOOKUP(C157,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A157,TIPOS!$A:$C,3,FALSE),"")="Sí",B157=""),"Falta el N° de entrega",IF(N(I157)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A157="",C157=""),"",IF(A157="","Falta el tipo",IF(H157="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C157="","Falta el código",IF(ISNA(MATCH(C157,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D157)&gt;0,N(VLOOKUP(C157,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A157,TIPOS!$A:$C,3,FALSE),"")="Sí",B157=""),"Falta el N° de entrega",IF(N(I157)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -5520,7 +5523,7 @@
         <v/>
       </c>
       <c r="H158" s="9">
-        <f>IF(A158="","",IFERROR(VLOOKUP(A158,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A158="","",IFERROR(IF(VLOOKUP(A158,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A158,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I158" s="10">
@@ -5536,7 +5539,7 @@
         <v/>
       </c>
       <c r="L158" s="9">
-        <f>IF(AND(A158="",C158=""),"",IF(A158="","Falta el tipo",IF(C158="","Falta el código",IF(ISNA(MATCH(C158,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D158)&gt;0,N(VLOOKUP(C158,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A158,TIPOS!$A:$C,3,FALSE),"")="Sí",B158=""),"Falta el N° de entrega",IF(N(I158)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A158="",C158=""),"",IF(A158="","Falta el tipo",IF(H158="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C158="","Falta el código",IF(ISNA(MATCH(C158,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D158)&gt;0,N(VLOOKUP(C158,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A158,TIPOS!$A:$C,3,FALSE),"")="Sí",B158=""),"Falta el N° de entrega",IF(N(I158)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -5552,7 +5555,7 @@
         <v/>
       </c>
       <c r="H159" s="9">
-        <f>IF(A159="","",IFERROR(VLOOKUP(A159,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A159="","",IFERROR(IF(VLOOKUP(A159,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A159,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I159" s="10">
@@ -5568,7 +5571,7 @@
         <v/>
       </c>
       <c r="L159" s="9">
-        <f>IF(AND(A159="",C159=""),"",IF(A159="","Falta el tipo",IF(C159="","Falta el código",IF(ISNA(MATCH(C159,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D159)&gt;0,N(VLOOKUP(C159,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A159,TIPOS!$A:$C,3,FALSE),"")="Sí",B159=""),"Falta el N° de entrega",IF(N(I159)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A159="",C159=""),"",IF(A159="","Falta el tipo",IF(H159="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C159="","Falta el código",IF(ISNA(MATCH(C159,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D159)&gt;0,N(VLOOKUP(C159,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A159,TIPOS!$A:$C,3,FALSE),"")="Sí",B159=""),"Falta el N° de entrega",IF(N(I159)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -5584,7 +5587,7 @@
         <v/>
       </c>
       <c r="H160" s="9">
-        <f>IF(A160="","",IFERROR(VLOOKUP(A160,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A160="","",IFERROR(IF(VLOOKUP(A160,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A160,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I160" s="10">
@@ -5600,7 +5603,7 @@
         <v/>
       </c>
       <c r="L160" s="9">
-        <f>IF(AND(A160="",C160=""),"",IF(A160="","Falta el tipo",IF(C160="","Falta el código",IF(ISNA(MATCH(C160,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D160)&gt;0,N(VLOOKUP(C160,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A160,TIPOS!$A:$C,3,FALSE),"")="Sí",B160=""),"Falta el N° de entrega",IF(N(I160)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A160="",C160=""),"",IF(A160="","Falta el tipo",IF(H160="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C160="","Falta el código",IF(ISNA(MATCH(C160,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D160)&gt;0,N(VLOOKUP(C160,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A160,TIPOS!$A:$C,3,FALSE),"")="Sí",B160=""),"Falta el N° de entrega",IF(N(I160)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -5616,7 +5619,7 @@
         <v/>
       </c>
       <c r="H161" s="9">
-        <f>IF(A161="","",IFERROR(VLOOKUP(A161,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A161="","",IFERROR(IF(VLOOKUP(A161,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A161,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I161" s="10">
@@ -5632,7 +5635,7 @@
         <v/>
       </c>
       <c r="L161" s="9">
-        <f>IF(AND(A161="",C161=""),"",IF(A161="","Falta el tipo",IF(C161="","Falta el código",IF(ISNA(MATCH(C161,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D161)&gt;0,N(VLOOKUP(C161,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A161,TIPOS!$A:$C,3,FALSE),"")="Sí",B161=""),"Falta el N° de entrega",IF(N(I161)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A161="",C161=""),"",IF(A161="","Falta el tipo",IF(H161="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C161="","Falta el código",IF(ISNA(MATCH(C161,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D161)&gt;0,N(VLOOKUP(C161,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A161,TIPOS!$A:$C,3,FALSE),"")="Sí",B161=""),"Falta el N° de entrega",IF(N(I161)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -5648,7 +5651,7 @@
         <v/>
       </c>
       <c r="H162" s="9">
-        <f>IF(A162="","",IFERROR(VLOOKUP(A162,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A162="","",IFERROR(IF(VLOOKUP(A162,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A162,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I162" s="10">
@@ -5664,7 +5667,7 @@
         <v/>
       </c>
       <c r="L162" s="9">
-        <f>IF(AND(A162="",C162=""),"",IF(A162="","Falta el tipo",IF(C162="","Falta el código",IF(ISNA(MATCH(C162,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D162)&gt;0,N(VLOOKUP(C162,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A162,TIPOS!$A:$C,3,FALSE),"")="Sí",B162=""),"Falta el N° de entrega",IF(N(I162)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A162="",C162=""),"",IF(A162="","Falta el tipo",IF(H162="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C162="","Falta el código",IF(ISNA(MATCH(C162,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D162)&gt;0,N(VLOOKUP(C162,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A162,TIPOS!$A:$C,3,FALSE),"")="Sí",B162=""),"Falta el N° de entrega",IF(N(I162)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -5680,7 +5683,7 @@
         <v/>
       </c>
       <c r="H163" s="9">
-        <f>IF(A163="","",IFERROR(VLOOKUP(A163,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A163="","",IFERROR(IF(VLOOKUP(A163,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A163,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I163" s="10">
@@ -5696,7 +5699,7 @@
         <v/>
       </c>
       <c r="L163" s="9">
-        <f>IF(AND(A163="",C163=""),"",IF(A163="","Falta el tipo",IF(C163="","Falta el código",IF(ISNA(MATCH(C163,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D163)&gt;0,N(VLOOKUP(C163,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A163,TIPOS!$A:$C,3,FALSE),"")="Sí",B163=""),"Falta el N° de entrega",IF(N(I163)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A163="",C163=""),"",IF(A163="","Falta el tipo",IF(H163="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C163="","Falta el código",IF(ISNA(MATCH(C163,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D163)&gt;0,N(VLOOKUP(C163,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A163,TIPOS!$A:$C,3,FALSE),"")="Sí",B163=""),"Falta el N° de entrega",IF(N(I163)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -5712,7 +5715,7 @@
         <v/>
       </c>
       <c r="H164" s="9">
-        <f>IF(A164="","",IFERROR(VLOOKUP(A164,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A164="","",IFERROR(IF(VLOOKUP(A164,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A164,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I164" s="10">
@@ -5728,7 +5731,7 @@
         <v/>
       </c>
       <c r="L164" s="9">
-        <f>IF(AND(A164="",C164=""),"",IF(A164="","Falta el tipo",IF(C164="","Falta el código",IF(ISNA(MATCH(C164,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D164)&gt;0,N(VLOOKUP(C164,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A164,TIPOS!$A:$C,3,FALSE),"")="Sí",B164=""),"Falta el N° de entrega",IF(N(I164)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A164="",C164=""),"",IF(A164="","Falta el tipo",IF(H164="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C164="","Falta el código",IF(ISNA(MATCH(C164,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D164)&gt;0,N(VLOOKUP(C164,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A164,TIPOS!$A:$C,3,FALSE),"")="Sí",B164=""),"Falta el N° de entrega",IF(N(I164)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -5744,7 +5747,7 @@
         <v/>
       </c>
       <c r="H165" s="9">
-        <f>IF(A165="","",IFERROR(VLOOKUP(A165,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A165="","",IFERROR(IF(VLOOKUP(A165,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A165,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I165" s="10">
@@ -5760,7 +5763,7 @@
         <v/>
       </c>
       <c r="L165" s="9">
-        <f>IF(AND(A165="",C165=""),"",IF(A165="","Falta el tipo",IF(C165="","Falta el código",IF(ISNA(MATCH(C165,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D165)&gt;0,N(VLOOKUP(C165,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A165,TIPOS!$A:$C,3,FALSE),"")="Sí",B165=""),"Falta el N° de entrega",IF(N(I165)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A165="",C165=""),"",IF(A165="","Falta el tipo",IF(H165="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C165="","Falta el código",IF(ISNA(MATCH(C165,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D165)&gt;0,N(VLOOKUP(C165,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A165,TIPOS!$A:$C,3,FALSE),"")="Sí",B165=""),"Falta el N° de entrega",IF(N(I165)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -5776,7 +5779,7 @@
         <v/>
       </c>
       <c r="H166" s="9">
-        <f>IF(A166="","",IFERROR(VLOOKUP(A166,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A166="","",IFERROR(IF(VLOOKUP(A166,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A166,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I166" s="10">
@@ -5792,7 +5795,7 @@
         <v/>
       </c>
       <c r="L166" s="9">
-        <f>IF(AND(A166="",C166=""),"",IF(A166="","Falta el tipo",IF(C166="","Falta el código",IF(ISNA(MATCH(C166,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D166)&gt;0,N(VLOOKUP(C166,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A166,TIPOS!$A:$C,3,FALSE),"")="Sí",B166=""),"Falta el N° de entrega",IF(N(I166)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A166="",C166=""),"",IF(A166="","Falta el tipo",IF(H166="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C166="","Falta el código",IF(ISNA(MATCH(C166,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D166)&gt;0,N(VLOOKUP(C166,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A166,TIPOS!$A:$C,3,FALSE),"")="Sí",B166=""),"Falta el N° de entrega",IF(N(I166)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -5808,7 +5811,7 @@
         <v/>
       </c>
       <c r="H167" s="9">
-        <f>IF(A167="","",IFERROR(VLOOKUP(A167,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A167="","",IFERROR(IF(VLOOKUP(A167,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A167,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I167" s="10">
@@ -5824,7 +5827,7 @@
         <v/>
       </c>
       <c r="L167" s="9">
-        <f>IF(AND(A167="",C167=""),"",IF(A167="","Falta el tipo",IF(C167="","Falta el código",IF(ISNA(MATCH(C167,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D167)&gt;0,N(VLOOKUP(C167,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A167,TIPOS!$A:$C,3,FALSE),"")="Sí",B167=""),"Falta el N° de entrega",IF(N(I167)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A167="",C167=""),"",IF(A167="","Falta el tipo",IF(H167="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C167="","Falta el código",IF(ISNA(MATCH(C167,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D167)&gt;0,N(VLOOKUP(C167,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A167,TIPOS!$A:$C,3,FALSE),"")="Sí",B167=""),"Falta el N° de entrega",IF(N(I167)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -5840,7 +5843,7 @@
         <v/>
       </c>
       <c r="H168" s="9">
-        <f>IF(A168="","",IFERROR(VLOOKUP(A168,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A168="","",IFERROR(IF(VLOOKUP(A168,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A168,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I168" s="10">
@@ -5856,7 +5859,7 @@
         <v/>
       </c>
       <c r="L168" s="9">
-        <f>IF(AND(A168="",C168=""),"",IF(A168="","Falta el tipo",IF(C168="","Falta el código",IF(ISNA(MATCH(C168,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D168)&gt;0,N(VLOOKUP(C168,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A168,TIPOS!$A:$C,3,FALSE),"")="Sí",B168=""),"Falta el N° de entrega",IF(N(I168)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A168="",C168=""),"",IF(A168="","Falta el tipo",IF(H168="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C168="","Falta el código",IF(ISNA(MATCH(C168,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D168)&gt;0,N(VLOOKUP(C168,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A168,TIPOS!$A:$C,3,FALSE),"")="Sí",B168=""),"Falta el N° de entrega",IF(N(I168)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -5872,7 +5875,7 @@
         <v/>
       </c>
       <c r="H169" s="9">
-        <f>IF(A169="","",IFERROR(VLOOKUP(A169,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A169="","",IFERROR(IF(VLOOKUP(A169,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A169,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I169" s="10">
@@ -5888,7 +5891,7 @@
         <v/>
       </c>
       <c r="L169" s="9">
-        <f>IF(AND(A169="",C169=""),"",IF(A169="","Falta el tipo",IF(C169="","Falta el código",IF(ISNA(MATCH(C169,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D169)&gt;0,N(VLOOKUP(C169,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A169,TIPOS!$A:$C,3,FALSE),"")="Sí",B169=""),"Falta el N° de entrega",IF(N(I169)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A169="",C169=""),"",IF(A169="","Falta el tipo",IF(H169="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C169="","Falta el código",IF(ISNA(MATCH(C169,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D169)&gt;0,N(VLOOKUP(C169,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A169,TIPOS!$A:$C,3,FALSE),"")="Sí",B169=""),"Falta el N° de entrega",IF(N(I169)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -5904,7 +5907,7 @@
         <v/>
       </c>
       <c r="H170" s="9">
-        <f>IF(A170="","",IFERROR(VLOOKUP(A170,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A170="","",IFERROR(IF(VLOOKUP(A170,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A170,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I170" s="10">
@@ -5920,7 +5923,7 @@
         <v/>
       </c>
       <c r="L170" s="9">
-        <f>IF(AND(A170="",C170=""),"",IF(A170="","Falta el tipo",IF(C170="","Falta el código",IF(ISNA(MATCH(C170,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D170)&gt;0,N(VLOOKUP(C170,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A170,TIPOS!$A:$C,3,FALSE),"")="Sí",B170=""),"Falta el N° de entrega",IF(N(I170)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A170="",C170=""),"",IF(A170="","Falta el tipo",IF(H170="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C170="","Falta el código",IF(ISNA(MATCH(C170,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D170)&gt;0,N(VLOOKUP(C170,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A170,TIPOS!$A:$C,3,FALSE),"")="Sí",B170=""),"Falta el N° de entrega",IF(N(I170)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -5936,7 +5939,7 @@
         <v/>
       </c>
       <c r="H171" s="9">
-        <f>IF(A171="","",IFERROR(VLOOKUP(A171,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A171="","",IFERROR(IF(VLOOKUP(A171,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A171,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I171" s="10">
@@ -5952,7 +5955,7 @@
         <v/>
       </c>
       <c r="L171" s="9">
-        <f>IF(AND(A171="",C171=""),"",IF(A171="","Falta el tipo",IF(C171="","Falta el código",IF(ISNA(MATCH(C171,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D171)&gt;0,N(VLOOKUP(C171,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A171,TIPOS!$A:$C,3,FALSE),"")="Sí",B171=""),"Falta el N° de entrega",IF(N(I171)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A171="",C171=""),"",IF(A171="","Falta el tipo",IF(H171="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C171="","Falta el código",IF(ISNA(MATCH(C171,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D171)&gt;0,N(VLOOKUP(C171,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A171,TIPOS!$A:$C,3,FALSE),"")="Sí",B171=""),"Falta el N° de entrega",IF(N(I171)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -5968,7 +5971,7 @@
         <v/>
       </c>
       <c r="H172" s="9">
-        <f>IF(A172="","",IFERROR(VLOOKUP(A172,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A172="","",IFERROR(IF(VLOOKUP(A172,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A172,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I172" s="10">
@@ -5984,7 +5987,7 @@
         <v/>
       </c>
       <c r="L172" s="9">
-        <f>IF(AND(A172="",C172=""),"",IF(A172="","Falta el tipo",IF(C172="","Falta el código",IF(ISNA(MATCH(C172,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D172)&gt;0,N(VLOOKUP(C172,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A172,TIPOS!$A:$C,3,FALSE),"")="Sí",B172=""),"Falta el N° de entrega",IF(N(I172)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A172="",C172=""),"",IF(A172="","Falta el tipo",IF(H172="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C172="","Falta el código",IF(ISNA(MATCH(C172,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D172)&gt;0,N(VLOOKUP(C172,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A172,TIPOS!$A:$C,3,FALSE),"")="Sí",B172=""),"Falta el N° de entrega",IF(N(I172)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -6000,7 +6003,7 @@
         <v/>
       </c>
       <c r="H173" s="9">
-        <f>IF(A173="","",IFERROR(VLOOKUP(A173,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A173="","",IFERROR(IF(VLOOKUP(A173,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A173,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I173" s="10">
@@ -6016,7 +6019,7 @@
         <v/>
       </c>
       <c r="L173" s="9">
-        <f>IF(AND(A173="",C173=""),"",IF(A173="","Falta el tipo",IF(C173="","Falta el código",IF(ISNA(MATCH(C173,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D173)&gt;0,N(VLOOKUP(C173,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A173,TIPOS!$A:$C,3,FALSE),"")="Sí",B173=""),"Falta el N° de entrega",IF(N(I173)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A173="",C173=""),"",IF(A173="","Falta el tipo",IF(H173="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C173="","Falta el código",IF(ISNA(MATCH(C173,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D173)&gt;0,N(VLOOKUP(C173,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A173,TIPOS!$A:$C,3,FALSE),"")="Sí",B173=""),"Falta el N° de entrega",IF(N(I173)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -6032,7 +6035,7 @@
         <v/>
       </c>
       <c r="H174" s="9">
-        <f>IF(A174="","",IFERROR(VLOOKUP(A174,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A174="","",IFERROR(IF(VLOOKUP(A174,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A174,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I174" s="10">
@@ -6048,7 +6051,7 @@
         <v/>
       </c>
       <c r="L174" s="9">
-        <f>IF(AND(A174="",C174=""),"",IF(A174="","Falta el tipo",IF(C174="","Falta el código",IF(ISNA(MATCH(C174,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D174)&gt;0,N(VLOOKUP(C174,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A174,TIPOS!$A:$C,3,FALSE),"")="Sí",B174=""),"Falta el N° de entrega",IF(N(I174)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A174="",C174=""),"",IF(A174="","Falta el tipo",IF(H174="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C174="","Falta el código",IF(ISNA(MATCH(C174,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D174)&gt;0,N(VLOOKUP(C174,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A174,TIPOS!$A:$C,3,FALSE),"")="Sí",B174=""),"Falta el N° de entrega",IF(N(I174)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -6064,7 +6067,7 @@
         <v/>
       </c>
       <c r="H175" s="9">
-        <f>IF(A175="","",IFERROR(VLOOKUP(A175,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A175="","",IFERROR(IF(VLOOKUP(A175,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A175,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I175" s="10">
@@ -6080,7 +6083,7 @@
         <v/>
       </c>
       <c r="L175" s="9">
-        <f>IF(AND(A175="",C175=""),"",IF(A175="","Falta el tipo",IF(C175="","Falta el código",IF(ISNA(MATCH(C175,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D175)&gt;0,N(VLOOKUP(C175,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A175,TIPOS!$A:$C,3,FALSE),"")="Sí",B175=""),"Falta el N° de entrega",IF(N(I175)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A175="",C175=""),"",IF(A175="","Falta el tipo",IF(H175="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C175="","Falta el código",IF(ISNA(MATCH(C175,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D175)&gt;0,N(VLOOKUP(C175,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A175,TIPOS!$A:$C,3,FALSE),"")="Sí",B175=""),"Falta el N° de entrega",IF(N(I175)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -6096,7 +6099,7 @@
         <v/>
       </c>
       <c r="H176" s="9">
-        <f>IF(A176="","",IFERROR(VLOOKUP(A176,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A176="","",IFERROR(IF(VLOOKUP(A176,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A176,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I176" s="10">
@@ -6112,7 +6115,7 @@
         <v/>
       </c>
       <c r="L176" s="9">
-        <f>IF(AND(A176="",C176=""),"",IF(A176="","Falta el tipo",IF(C176="","Falta el código",IF(ISNA(MATCH(C176,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D176)&gt;0,N(VLOOKUP(C176,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A176,TIPOS!$A:$C,3,FALSE),"")="Sí",B176=""),"Falta el N° de entrega",IF(N(I176)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A176="",C176=""),"",IF(A176="","Falta el tipo",IF(H176="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C176="","Falta el código",IF(ISNA(MATCH(C176,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D176)&gt;0,N(VLOOKUP(C176,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A176,TIPOS!$A:$C,3,FALSE),"")="Sí",B176=""),"Falta el N° de entrega",IF(N(I176)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -6128,7 +6131,7 @@
         <v/>
       </c>
       <c r="H177" s="9">
-        <f>IF(A177="","",IFERROR(VLOOKUP(A177,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A177="","",IFERROR(IF(VLOOKUP(A177,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A177,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I177" s="10">
@@ -6144,7 +6147,7 @@
         <v/>
       </c>
       <c r="L177" s="9">
-        <f>IF(AND(A177="",C177=""),"",IF(A177="","Falta el tipo",IF(C177="","Falta el código",IF(ISNA(MATCH(C177,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D177)&gt;0,N(VLOOKUP(C177,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A177,TIPOS!$A:$C,3,FALSE),"")="Sí",B177=""),"Falta el N° de entrega",IF(N(I177)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A177="",C177=""),"",IF(A177="","Falta el tipo",IF(H177="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C177="","Falta el código",IF(ISNA(MATCH(C177,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D177)&gt;0,N(VLOOKUP(C177,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A177,TIPOS!$A:$C,3,FALSE),"")="Sí",B177=""),"Falta el N° de entrega",IF(N(I177)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -6160,7 +6163,7 @@
         <v/>
       </c>
       <c r="H178" s="9">
-        <f>IF(A178="","",IFERROR(VLOOKUP(A178,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A178="","",IFERROR(IF(VLOOKUP(A178,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A178,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I178" s="10">
@@ -6176,7 +6179,7 @@
         <v/>
       </c>
       <c r="L178" s="9">
-        <f>IF(AND(A178="",C178=""),"",IF(A178="","Falta el tipo",IF(C178="","Falta el código",IF(ISNA(MATCH(C178,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D178)&gt;0,N(VLOOKUP(C178,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A178,TIPOS!$A:$C,3,FALSE),"")="Sí",B178=""),"Falta el N° de entrega",IF(N(I178)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A178="",C178=""),"",IF(A178="","Falta el tipo",IF(H178="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C178="","Falta el código",IF(ISNA(MATCH(C178,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D178)&gt;0,N(VLOOKUP(C178,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A178,TIPOS!$A:$C,3,FALSE),"")="Sí",B178=""),"Falta el N° de entrega",IF(N(I178)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -6192,7 +6195,7 @@
         <v/>
       </c>
       <c r="H179" s="9">
-        <f>IF(A179="","",IFERROR(VLOOKUP(A179,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A179="","",IFERROR(IF(VLOOKUP(A179,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A179,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I179" s="10">
@@ -6208,7 +6211,7 @@
         <v/>
       </c>
       <c r="L179" s="9">
-        <f>IF(AND(A179="",C179=""),"",IF(A179="","Falta el tipo",IF(C179="","Falta el código",IF(ISNA(MATCH(C179,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D179)&gt;0,N(VLOOKUP(C179,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A179,TIPOS!$A:$C,3,FALSE),"")="Sí",B179=""),"Falta el N° de entrega",IF(N(I179)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A179="",C179=""),"",IF(A179="","Falta el tipo",IF(H179="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C179="","Falta el código",IF(ISNA(MATCH(C179,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D179)&gt;0,N(VLOOKUP(C179,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A179,TIPOS!$A:$C,3,FALSE),"")="Sí",B179=""),"Falta el N° de entrega",IF(N(I179)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -6224,7 +6227,7 @@
         <v/>
       </c>
       <c r="H180" s="9">
-        <f>IF(A180="","",IFERROR(VLOOKUP(A180,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A180="","",IFERROR(IF(VLOOKUP(A180,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A180,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I180" s="10">
@@ -6240,7 +6243,7 @@
         <v/>
       </c>
       <c r="L180" s="9">
-        <f>IF(AND(A180="",C180=""),"",IF(A180="","Falta el tipo",IF(C180="","Falta el código",IF(ISNA(MATCH(C180,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D180)&gt;0,N(VLOOKUP(C180,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A180,TIPOS!$A:$C,3,FALSE),"")="Sí",B180=""),"Falta el N° de entrega",IF(N(I180)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A180="",C180=""),"",IF(A180="","Falta el tipo",IF(H180="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C180="","Falta el código",IF(ISNA(MATCH(C180,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D180)&gt;0,N(VLOOKUP(C180,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A180,TIPOS!$A:$C,3,FALSE),"")="Sí",B180=""),"Falta el N° de entrega",IF(N(I180)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -6256,7 +6259,7 @@
         <v/>
       </c>
       <c r="H181" s="9">
-        <f>IF(A181="","",IFERROR(VLOOKUP(A181,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A181="","",IFERROR(IF(VLOOKUP(A181,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A181,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I181" s="10">
@@ -6272,7 +6275,7 @@
         <v/>
       </c>
       <c r="L181" s="9">
-        <f>IF(AND(A181="",C181=""),"",IF(A181="","Falta el tipo",IF(C181="","Falta el código",IF(ISNA(MATCH(C181,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D181)&gt;0,N(VLOOKUP(C181,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A181,TIPOS!$A:$C,3,FALSE),"")="Sí",B181=""),"Falta el N° de entrega",IF(N(I181)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A181="",C181=""),"",IF(A181="","Falta el tipo",IF(H181="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C181="","Falta el código",IF(ISNA(MATCH(C181,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D181)&gt;0,N(VLOOKUP(C181,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A181,TIPOS!$A:$C,3,FALSE),"")="Sí",B181=""),"Falta el N° de entrega",IF(N(I181)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -6288,7 +6291,7 @@
         <v/>
       </c>
       <c r="H182" s="9">
-        <f>IF(A182="","",IFERROR(VLOOKUP(A182,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A182="","",IFERROR(IF(VLOOKUP(A182,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A182,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I182" s="10">
@@ -6304,7 +6307,7 @@
         <v/>
       </c>
       <c r="L182" s="9">
-        <f>IF(AND(A182="",C182=""),"",IF(A182="","Falta el tipo",IF(C182="","Falta el código",IF(ISNA(MATCH(C182,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D182)&gt;0,N(VLOOKUP(C182,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A182,TIPOS!$A:$C,3,FALSE),"")="Sí",B182=""),"Falta el N° de entrega",IF(N(I182)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A182="",C182=""),"",IF(A182="","Falta el tipo",IF(H182="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C182="","Falta el código",IF(ISNA(MATCH(C182,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D182)&gt;0,N(VLOOKUP(C182,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A182,TIPOS!$A:$C,3,FALSE),"")="Sí",B182=""),"Falta el N° de entrega",IF(N(I182)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -6320,7 +6323,7 @@
         <v/>
       </c>
       <c r="H183" s="9">
-        <f>IF(A183="","",IFERROR(VLOOKUP(A183,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A183="","",IFERROR(IF(VLOOKUP(A183,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A183,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I183" s="10">
@@ -6336,7 +6339,7 @@
         <v/>
       </c>
       <c r="L183" s="9">
-        <f>IF(AND(A183="",C183=""),"",IF(A183="","Falta el tipo",IF(C183="","Falta el código",IF(ISNA(MATCH(C183,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D183)&gt;0,N(VLOOKUP(C183,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A183,TIPOS!$A:$C,3,FALSE),"")="Sí",B183=""),"Falta el N° de entrega",IF(N(I183)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A183="",C183=""),"",IF(A183="","Falta el tipo",IF(H183="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C183="","Falta el código",IF(ISNA(MATCH(C183,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D183)&gt;0,N(VLOOKUP(C183,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A183,TIPOS!$A:$C,3,FALSE),"")="Sí",B183=""),"Falta el N° de entrega",IF(N(I183)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -6352,7 +6355,7 @@
         <v/>
       </c>
       <c r="H184" s="9">
-        <f>IF(A184="","",IFERROR(VLOOKUP(A184,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A184="","",IFERROR(IF(VLOOKUP(A184,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A184,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I184" s="10">
@@ -6368,7 +6371,7 @@
         <v/>
       </c>
       <c r="L184" s="9">
-        <f>IF(AND(A184="",C184=""),"",IF(A184="","Falta el tipo",IF(C184="","Falta el código",IF(ISNA(MATCH(C184,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D184)&gt;0,N(VLOOKUP(C184,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A184,TIPOS!$A:$C,3,FALSE),"")="Sí",B184=""),"Falta el N° de entrega",IF(N(I184)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A184="",C184=""),"",IF(A184="","Falta el tipo",IF(H184="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C184="","Falta el código",IF(ISNA(MATCH(C184,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D184)&gt;0,N(VLOOKUP(C184,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A184,TIPOS!$A:$C,3,FALSE),"")="Sí",B184=""),"Falta el N° de entrega",IF(N(I184)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -6384,7 +6387,7 @@
         <v/>
       </c>
       <c r="H185" s="9">
-        <f>IF(A185="","",IFERROR(VLOOKUP(A185,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A185="","",IFERROR(IF(VLOOKUP(A185,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A185,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I185" s="10">
@@ -6400,7 +6403,7 @@
         <v/>
       </c>
       <c r="L185" s="9">
-        <f>IF(AND(A185="",C185=""),"",IF(A185="","Falta el tipo",IF(C185="","Falta el código",IF(ISNA(MATCH(C185,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D185)&gt;0,N(VLOOKUP(C185,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A185,TIPOS!$A:$C,3,FALSE),"")="Sí",B185=""),"Falta el N° de entrega",IF(N(I185)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A185="",C185=""),"",IF(A185="","Falta el tipo",IF(H185="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C185="","Falta el código",IF(ISNA(MATCH(C185,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D185)&gt;0,N(VLOOKUP(C185,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A185,TIPOS!$A:$C,3,FALSE),"")="Sí",B185=""),"Falta el N° de entrega",IF(N(I185)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -6416,7 +6419,7 @@
         <v/>
       </c>
       <c r="H186" s="9">
-        <f>IF(A186="","",IFERROR(VLOOKUP(A186,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A186="","",IFERROR(IF(VLOOKUP(A186,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A186,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I186" s="10">
@@ -6432,7 +6435,7 @@
         <v/>
       </c>
       <c r="L186" s="9">
-        <f>IF(AND(A186="",C186=""),"",IF(A186="","Falta el tipo",IF(C186="","Falta el código",IF(ISNA(MATCH(C186,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D186)&gt;0,N(VLOOKUP(C186,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A186,TIPOS!$A:$C,3,FALSE),"")="Sí",B186=""),"Falta el N° de entrega",IF(N(I186)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A186="",C186=""),"",IF(A186="","Falta el tipo",IF(H186="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C186="","Falta el código",IF(ISNA(MATCH(C186,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D186)&gt;0,N(VLOOKUP(C186,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A186,TIPOS!$A:$C,3,FALSE),"")="Sí",B186=""),"Falta el N° de entrega",IF(N(I186)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -6448,7 +6451,7 @@
         <v/>
       </c>
       <c r="H187" s="9">
-        <f>IF(A187="","",IFERROR(VLOOKUP(A187,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A187="","",IFERROR(IF(VLOOKUP(A187,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A187,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I187" s="10">
@@ -6464,7 +6467,7 @@
         <v/>
       </c>
       <c r="L187" s="9">
-        <f>IF(AND(A187="",C187=""),"",IF(A187="","Falta el tipo",IF(C187="","Falta el código",IF(ISNA(MATCH(C187,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D187)&gt;0,N(VLOOKUP(C187,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A187,TIPOS!$A:$C,3,FALSE),"")="Sí",B187=""),"Falta el N° de entrega",IF(N(I187)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A187="",C187=""),"",IF(A187="","Falta el tipo",IF(H187="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C187="","Falta el código",IF(ISNA(MATCH(C187,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D187)&gt;0,N(VLOOKUP(C187,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A187,TIPOS!$A:$C,3,FALSE),"")="Sí",B187=""),"Falta el N° de entrega",IF(N(I187)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -6480,7 +6483,7 @@
         <v/>
       </c>
       <c r="H188" s="9">
-        <f>IF(A188="","",IFERROR(VLOOKUP(A188,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A188="","",IFERROR(IF(VLOOKUP(A188,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A188,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I188" s="10">
@@ -6496,7 +6499,7 @@
         <v/>
       </c>
       <c r="L188" s="9">
-        <f>IF(AND(A188="",C188=""),"",IF(A188="","Falta el tipo",IF(C188="","Falta el código",IF(ISNA(MATCH(C188,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D188)&gt;0,N(VLOOKUP(C188,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A188,TIPOS!$A:$C,3,FALSE),"")="Sí",B188=""),"Falta el N° de entrega",IF(N(I188)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A188="",C188=""),"",IF(A188="","Falta el tipo",IF(H188="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C188="","Falta el código",IF(ISNA(MATCH(C188,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D188)&gt;0,N(VLOOKUP(C188,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A188,TIPOS!$A:$C,3,FALSE),"")="Sí",B188=""),"Falta el N° de entrega",IF(N(I188)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -6512,7 +6515,7 @@
         <v/>
       </c>
       <c r="H189" s="9">
-        <f>IF(A189="","",IFERROR(VLOOKUP(A189,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A189="","",IFERROR(IF(VLOOKUP(A189,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A189,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I189" s="10">
@@ -6528,7 +6531,7 @@
         <v/>
       </c>
       <c r="L189" s="9">
-        <f>IF(AND(A189="",C189=""),"",IF(A189="","Falta el tipo",IF(C189="","Falta el código",IF(ISNA(MATCH(C189,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D189)&gt;0,N(VLOOKUP(C189,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A189,TIPOS!$A:$C,3,FALSE),"")="Sí",B189=""),"Falta el N° de entrega",IF(N(I189)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A189="",C189=""),"",IF(A189="","Falta el tipo",IF(H189="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C189="","Falta el código",IF(ISNA(MATCH(C189,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D189)&gt;0,N(VLOOKUP(C189,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A189,TIPOS!$A:$C,3,FALSE),"")="Sí",B189=""),"Falta el N° de entrega",IF(N(I189)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -6544,7 +6547,7 @@
         <v/>
       </c>
       <c r="H190" s="9">
-        <f>IF(A190="","",IFERROR(VLOOKUP(A190,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A190="","",IFERROR(IF(VLOOKUP(A190,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A190,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I190" s="10">
@@ -6560,7 +6563,7 @@
         <v/>
       </c>
       <c r="L190" s="9">
-        <f>IF(AND(A190="",C190=""),"",IF(A190="","Falta el tipo",IF(C190="","Falta el código",IF(ISNA(MATCH(C190,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D190)&gt;0,N(VLOOKUP(C190,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A190,TIPOS!$A:$C,3,FALSE),"")="Sí",B190=""),"Falta el N° de entrega",IF(N(I190)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A190="",C190=""),"",IF(A190="","Falta el tipo",IF(H190="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C190="","Falta el código",IF(ISNA(MATCH(C190,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D190)&gt;0,N(VLOOKUP(C190,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A190,TIPOS!$A:$C,3,FALSE),"")="Sí",B190=""),"Falta el N° de entrega",IF(N(I190)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -6576,7 +6579,7 @@
         <v/>
       </c>
       <c r="H191" s="9">
-        <f>IF(A191="","",IFERROR(VLOOKUP(A191,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A191="","",IFERROR(IF(VLOOKUP(A191,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A191,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I191" s="10">
@@ -6592,7 +6595,7 @@
         <v/>
       </c>
       <c r="L191" s="9">
-        <f>IF(AND(A191="",C191=""),"",IF(A191="","Falta el tipo",IF(C191="","Falta el código",IF(ISNA(MATCH(C191,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D191)&gt;0,N(VLOOKUP(C191,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A191,TIPOS!$A:$C,3,FALSE),"")="Sí",B191=""),"Falta el N° de entrega",IF(N(I191)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A191="",C191=""),"",IF(A191="","Falta el tipo",IF(H191="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C191="","Falta el código",IF(ISNA(MATCH(C191,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D191)&gt;0,N(VLOOKUP(C191,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A191,TIPOS!$A:$C,3,FALSE),"")="Sí",B191=""),"Falta el N° de entrega",IF(N(I191)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -6608,7 +6611,7 @@
         <v/>
       </c>
       <c r="H192" s="9">
-        <f>IF(A192="","",IFERROR(VLOOKUP(A192,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A192="","",IFERROR(IF(VLOOKUP(A192,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A192,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I192" s="10">
@@ -6624,7 +6627,7 @@
         <v/>
       </c>
       <c r="L192" s="9">
-        <f>IF(AND(A192="",C192=""),"",IF(A192="","Falta el tipo",IF(C192="","Falta el código",IF(ISNA(MATCH(C192,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D192)&gt;0,N(VLOOKUP(C192,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A192,TIPOS!$A:$C,3,FALSE),"")="Sí",B192=""),"Falta el N° de entrega",IF(N(I192)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A192="",C192=""),"",IF(A192="","Falta el tipo",IF(H192="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C192="","Falta el código",IF(ISNA(MATCH(C192,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D192)&gt;0,N(VLOOKUP(C192,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A192,TIPOS!$A:$C,3,FALSE),"")="Sí",B192=""),"Falta el N° de entrega",IF(N(I192)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -6640,7 +6643,7 @@
         <v/>
       </c>
       <c r="H193" s="9">
-        <f>IF(A193="","",IFERROR(VLOOKUP(A193,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A193="","",IFERROR(IF(VLOOKUP(A193,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A193,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I193" s="10">
@@ -6656,7 +6659,7 @@
         <v/>
       </c>
       <c r="L193" s="9">
-        <f>IF(AND(A193="",C193=""),"",IF(A193="","Falta el tipo",IF(C193="","Falta el código",IF(ISNA(MATCH(C193,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D193)&gt;0,N(VLOOKUP(C193,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A193,TIPOS!$A:$C,3,FALSE),"")="Sí",B193=""),"Falta el N° de entrega",IF(N(I193)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A193="",C193=""),"",IF(A193="","Falta el tipo",IF(H193="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C193="","Falta el código",IF(ISNA(MATCH(C193,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D193)&gt;0,N(VLOOKUP(C193,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A193,TIPOS!$A:$C,3,FALSE),"")="Sí",B193=""),"Falta el N° de entrega",IF(N(I193)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -6672,7 +6675,7 @@
         <v/>
       </c>
       <c r="H194" s="9">
-        <f>IF(A194="","",IFERROR(VLOOKUP(A194,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A194="","",IFERROR(IF(VLOOKUP(A194,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A194,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I194" s="10">
@@ -6688,7 +6691,7 @@
         <v/>
       </c>
       <c r="L194" s="9">
-        <f>IF(AND(A194="",C194=""),"",IF(A194="","Falta el tipo",IF(C194="","Falta el código",IF(ISNA(MATCH(C194,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D194)&gt;0,N(VLOOKUP(C194,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A194,TIPOS!$A:$C,3,FALSE),"")="Sí",B194=""),"Falta el N° de entrega",IF(N(I194)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A194="",C194=""),"",IF(A194="","Falta el tipo",IF(H194="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C194="","Falta el código",IF(ISNA(MATCH(C194,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D194)&gt;0,N(VLOOKUP(C194,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A194,TIPOS!$A:$C,3,FALSE),"")="Sí",B194=""),"Falta el N° de entrega",IF(N(I194)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -6704,7 +6707,7 @@
         <v/>
       </c>
       <c r="H195" s="9">
-        <f>IF(A195="","",IFERROR(VLOOKUP(A195,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A195="","",IFERROR(IF(VLOOKUP(A195,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A195,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I195" s="10">
@@ -6720,7 +6723,7 @@
         <v/>
       </c>
       <c r="L195" s="9">
-        <f>IF(AND(A195="",C195=""),"",IF(A195="","Falta el tipo",IF(C195="","Falta el código",IF(ISNA(MATCH(C195,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D195)&gt;0,N(VLOOKUP(C195,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A195,TIPOS!$A:$C,3,FALSE),"")="Sí",B195=""),"Falta el N° de entrega",IF(N(I195)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A195="",C195=""),"",IF(A195="","Falta el tipo",IF(H195="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C195="","Falta el código",IF(ISNA(MATCH(C195,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D195)&gt;0,N(VLOOKUP(C195,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A195,TIPOS!$A:$C,3,FALSE),"")="Sí",B195=""),"Falta el N° de entrega",IF(N(I195)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -6736,7 +6739,7 @@
         <v/>
       </c>
       <c r="H196" s="9">
-        <f>IF(A196="","",IFERROR(VLOOKUP(A196,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A196="","",IFERROR(IF(VLOOKUP(A196,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A196,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I196" s="10">
@@ -6752,7 +6755,7 @@
         <v/>
       </c>
       <c r="L196" s="9">
-        <f>IF(AND(A196="",C196=""),"",IF(A196="","Falta el tipo",IF(C196="","Falta el código",IF(ISNA(MATCH(C196,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D196)&gt;0,N(VLOOKUP(C196,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A196,TIPOS!$A:$C,3,FALSE),"")="Sí",B196=""),"Falta el N° de entrega",IF(N(I196)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A196="",C196=""),"",IF(A196="","Falta el tipo",IF(H196="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C196="","Falta el código",IF(ISNA(MATCH(C196,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D196)&gt;0,N(VLOOKUP(C196,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A196,TIPOS!$A:$C,3,FALSE),"")="Sí",B196=""),"Falta el N° de entrega",IF(N(I196)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -6768,7 +6771,7 @@
         <v/>
       </c>
       <c r="H197" s="9">
-        <f>IF(A197="","",IFERROR(VLOOKUP(A197,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A197="","",IFERROR(IF(VLOOKUP(A197,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A197,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I197" s="10">
@@ -6784,7 +6787,7 @@
         <v/>
       </c>
       <c r="L197" s="9">
-        <f>IF(AND(A197="",C197=""),"",IF(A197="","Falta el tipo",IF(C197="","Falta el código",IF(ISNA(MATCH(C197,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D197)&gt;0,N(VLOOKUP(C197,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A197,TIPOS!$A:$C,3,FALSE),"")="Sí",B197=""),"Falta el N° de entrega",IF(N(I197)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A197="",C197=""),"",IF(A197="","Falta el tipo",IF(H197="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C197="","Falta el código",IF(ISNA(MATCH(C197,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D197)&gt;0,N(VLOOKUP(C197,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A197,TIPOS!$A:$C,3,FALSE),"")="Sí",B197=""),"Falta el N° de entrega",IF(N(I197)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -6800,7 +6803,7 @@
         <v/>
       </c>
       <c r="H198" s="9">
-        <f>IF(A198="","",IFERROR(VLOOKUP(A198,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A198="","",IFERROR(IF(VLOOKUP(A198,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A198,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I198" s="10">
@@ -6816,7 +6819,7 @@
         <v/>
       </c>
       <c r="L198" s="9">
-        <f>IF(AND(A198="",C198=""),"",IF(A198="","Falta el tipo",IF(C198="","Falta el código",IF(ISNA(MATCH(C198,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D198)&gt;0,N(VLOOKUP(C198,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A198,TIPOS!$A:$C,3,FALSE),"")="Sí",B198=""),"Falta el N° de entrega",IF(N(I198)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A198="",C198=""),"",IF(A198="","Falta el tipo",IF(H198="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C198="","Falta el código",IF(ISNA(MATCH(C198,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D198)&gt;0,N(VLOOKUP(C198,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A198,TIPOS!$A:$C,3,FALSE),"")="Sí",B198=""),"Falta el N° de entrega",IF(N(I198)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -6832,7 +6835,7 @@
         <v/>
       </c>
       <c r="H199" s="9">
-        <f>IF(A199="","",IFERROR(VLOOKUP(A199,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A199="","",IFERROR(IF(VLOOKUP(A199,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A199,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I199" s="10">
@@ -6848,7 +6851,7 @@
         <v/>
       </c>
       <c r="L199" s="9">
-        <f>IF(AND(A199="",C199=""),"",IF(A199="","Falta el tipo",IF(C199="","Falta el código",IF(ISNA(MATCH(C199,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D199)&gt;0,N(VLOOKUP(C199,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A199,TIPOS!$A:$C,3,FALSE),"")="Sí",B199=""),"Falta el N° de entrega",IF(N(I199)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A199="",C199=""),"",IF(A199="","Falta el tipo",IF(H199="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C199="","Falta el código",IF(ISNA(MATCH(C199,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D199)&gt;0,N(VLOOKUP(C199,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A199,TIPOS!$A:$C,3,FALSE),"")="Sí",B199=""),"Falta el N° de entrega",IF(N(I199)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -6864,7 +6867,7 @@
         <v/>
       </c>
       <c r="H200" s="9">
-        <f>IF(A200="","",IFERROR(VLOOKUP(A200,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A200="","",IFERROR(IF(VLOOKUP(A200,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A200,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I200" s="10">
@@ -6880,7 +6883,7 @@
         <v/>
       </c>
       <c r="L200" s="9">
-        <f>IF(AND(A200="",C200=""),"",IF(A200="","Falta el tipo",IF(C200="","Falta el código",IF(ISNA(MATCH(C200,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D200)&gt;0,N(VLOOKUP(C200,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A200,TIPOS!$A:$C,3,FALSE),"")="Sí",B200=""),"Falta el N° de entrega",IF(N(I200)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A200="",C200=""),"",IF(A200="","Falta el tipo",IF(H200="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C200="","Falta el código",IF(ISNA(MATCH(C200,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D200)&gt;0,N(VLOOKUP(C200,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A200,TIPOS!$A:$C,3,FALSE),"")="Sí",B200=""),"Falta el N° de entrega",IF(N(I200)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -6896,7 +6899,7 @@
         <v/>
       </c>
       <c r="H201" s="9">
-        <f>IF(A201="","",IFERROR(VLOOKUP(A201,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A201="","",IFERROR(IF(VLOOKUP(A201,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A201,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I201" s="10">
@@ -6912,7 +6915,7 @@
         <v/>
       </c>
       <c r="L201" s="9">
-        <f>IF(AND(A201="",C201=""),"",IF(A201="","Falta el tipo",IF(C201="","Falta el código",IF(ISNA(MATCH(C201,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D201)&gt;0,N(VLOOKUP(C201,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A201,TIPOS!$A:$C,3,FALSE),"")="Sí",B201=""),"Falta el N° de entrega",IF(N(I201)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A201="",C201=""),"",IF(A201="","Falta el tipo",IF(H201="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C201="","Falta el código",IF(ISNA(MATCH(C201,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D201)&gt;0,N(VLOOKUP(C201,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A201,TIPOS!$A:$C,3,FALSE),"")="Sí",B201=""),"Falta el N° de entrega",IF(N(I201)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -6928,7 +6931,7 @@
         <v/>
       </c>
       <c r="H202" s="9">
-        <f>IF(A202="","",IFERROR(VLOOKUP(A202,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A202="","",IFERROR(IF(VLOOKUP(A202,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A202,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I202" s="10">
@@ -6944,7 +6947,7 @@
         <v/>
       </c>
       <c r="L202" s="9">
-        <f>IF(AND(A202="",C202=""),"",IF(A202="","Falta el tipo",IF(C202="","Falta el código",IF(ISNA(MATCH(C202,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D202)&gt;0,N(VLOOKUP(C202,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A202,TIPOS!$A:$C,3,FALSE),"")="Sí",B202=""),"Falta el N° de entrega",IF(N(I202)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A202="",C202=""),"",IF(A202="","Falta el tipo",IF(H202="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C202="","Falta el código",IF(ISNA(MATCH(C202,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D202)&gt;0,N(VLOOKUP(C202,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A202,TIPOS!$A:$C,3,FALSE),"")="Sí",B202=""),"Falta el N° de entrega",IF(N(I202)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -6960,7 +6963,7 @@
         <v/>
       </c>
       <c r="H203" s="9">
-        <f>IF(A203="","",IFERROR(VLOOKUP(A203,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A203="","",IFERROR(IF(VLOOKUP(A203,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A203,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I203" s="10">
@@ -6976,7 +6979,7 @@
         <v/>
       </c>
       <c r="L203" s="9">
-        <f>IF(AND(A203="",C203=""),"",IF(A203="","Falta el tipo",IF(C203="","Falta el código",IF(ISNA(MATCH(C203,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D203)&gt;0,N(VLOOKUP(C203,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A203,TIPOS!$A:$C,3,FALSE),"")="Sí",B203=""),"Falta el N° de entrega",IF(N(I203)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A203="",C203=""),"",IF(A203="","Falta el tipo",IF(H203="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C203="","Falta el código",IF(ISNA(MATCH(C203,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D203)&gt;0,N(VLOOKUP(C203,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A203,TIPOS!$A:$C,3,FALSE),"")="Sí",B203=""),"Falta el N° de entrega",IF(N(I203)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -6992,7 +6995,7 @@
         <v/>
       </c>
       <c r="H204" s="9">
-        <f>IF(A204="","",IFERROR(VLOOKUP(A204,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A204="","",IFERROR(IF(VLOOKUP(A204,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A204,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I204" s="10">
@@ -7008,7 +7011,7 @@
         <v/>
       </c>
       <c r="L204" s="9">
-        <f>IF(AND(A204="",C204=""),"",IF(A204="","Falta el tipo",IF(C204="","Falta el código",IF(ISNA(MATCH(C204,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D204)&gt;0,N(VLOOKUP(C204,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A204,TIPOS!$A:$C,3,FALSE),"")="Sí",B204=""),"Falta el N° de entrega",IF(N(I204)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A204="",C204=""),"",IF(A204="","Falta el tipo",IF(H204="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C204="","Falta el código",IF(ISNA(MATCH(C204,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D204)&gt;0,N(VLOOKUP(C204,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A204,TIPOS!$A:$C,3,FALSE),"")="Sí",B204=""),"Falta el N° de entrega",IF(N(I204)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -7024,7 +7027,7 @@
         <v/>
       </c>
       <c r="H205" s="9">
-        <f>IF(A205="","",IFERROR(VLOOKUP(A205,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A205="","",IFERROR(IF(VLOOKUP(A205,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A205,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I205" s="10">
@@ -7040,7 +7043,7 @@
         <v/>
       </c>
       <c r="L205" s="9">
-        <f>IF(AND(A205="",C205=""),"",IF(A205="","Falta el tipo",IF(C205="","Falta el código",IF(ISNA(MATCH(C205,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D205)&gt;0,N(VLOOKUP(C205,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A205,TIPOS!$A:$C,3,FALSE),"")="Sí",B205=""),"Falta el N° de entrega",IF(N(I205)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A205="",C205=""),"",IF(A205="","Falta el tipo",IF(H205="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C205="","Falta el código",IF(ISNA(MATCH(C205,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D205)&gt;0,N(VLOOKUP(C205,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A205,TIPOS!$A:$C,3,FALSE),"")="Sí",B205=""),"Falta el N° de entrega",IF(N(I205)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -7056,7 +7059,7 @@
         <v/>
       </c>
       <c r="H206" s="9">
-        <f>IF(A206="","",IFERROR(VLOOKUP(A206,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A206="","",IFERROR(IF(VLOOKUP(A206,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A206,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I206" s="10">
@@ -7072,7 +7075,7 @@
         <v/>
       </c>
       <c r="L206" s="9">
-        <f>IF(AND(A206="",C206=""),"",IF(A206="","Falta el tipo",IF(C206="","Falta el código",IF(ISNA(MATCH(C206,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D206)&gt;0,N(VLOOKUP(C206,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A206,TIPOS!$A:$C,3,FALSE),"")="Sí",B206=""),"Falta el N° de entrega",IF(N(I206)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A206="",C206=""),"",IF(A206="","Falta el tipo",IF(H206="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C206="","Falta el código",IF(ISNA(MATCH(C206,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D206)&gt;0,N(VLOOKUP(C206,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A206,TIPOS!$A:$C,3,FALSE),"")="Sí",B206=""),"Falta el N° de entrega",IF(N(I206)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -7088,7 +7091,7 @@
         <v/>
       </c>
       <c r="H207" s="9">
-        <f>IF(A207="","",IFERROR(VLOOKUP(A207,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A207="","",IFERROR(IF(VLOOKUP(A207,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A207,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I207" s="10">
@@ -7104,7 +7107,7 @@
         <v/>
       </c>
       <c r="L207" s="9">
-        <f>IF(AND(A207="",C207=""),"",IF(A207="","Falta el tipo",IF(C207="","Falta el código",IF(ISNA(MATCH(C207,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D207)&gt;0,N(VLOOKUP(C207,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A207,TIPOS!$A:$C,3,FALSE),"")="Sí",B207=""),"Falta el N° de entrega",IF(N(I207)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A207="",C207=""),"",IF(A207="","Falta el tipo",IF(H207="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C207="","Falta el código",IF(ISNA(MATCH(C207,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D207)&gt;0,N(VLOOKUP(C207,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A207,TIPOS!$A:$C,3,FALSE),"")="Sí",B207=""),"Falta el N° de entrega",IF(N(I207)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -7120,7 +7123,7 @@
         <v/>
       </c>
       <c r="H208" s="9">
-        <f>IF(A208="","",IFERROR(VLOOKUP(A208,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A208="","",IFERROR(IF(VLOOKUP(A208,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A208,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I208" s="10">
@@ -7136,7 +7139,7 @@
         <v/>
       </c>
       <c r="L208" s="9">
-        <f>IF(AND(A208="",C208=""),"",IF(A208="","Falta el tipo",IF(C208="","Falta el código",IF(ISNA(MATCH(C208,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D208)&gt;0,N(VLOOKUP(C208,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A208,TIPOS!$A:$C,3,FALSE),"")="Sí",B208=""),"Falta el N° de entrega",IF(N(I208)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A208="",C208=""),"",IF(A208="","Falta el tipo",IF(H208="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C208="","Falta el código",IF(ISNA(MATCH(C208,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D208)&gt;0,N(VLOOKUP(C208,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A208,TIPOS!$A:$C,3,FALSE),"")="Sí",B208=""),"Falta el N° de entrega",IF(N(I208)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -7152,7 +7155,7 @@
         <v/>
       </c>
       <c r="H209" s="9">
-        <f>IF(A209="","",IFERROR(VLOOKUP(A209,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A209="","",IFERROR(IF(VLOOKUP(A209,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A209,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I209" s="10">
@@ -7168,7 +7171,7 @@
         <v/>
       </c>
       <c r="L209" s="9">
-        <f>IF(AND(A209="",C209=""),"",IF(A209="","Falta el tipo",IF(C209="","Falta el código",IF(ISNA(MATCH(C209,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D209)&gt;0,N(VLOOKUP(C209,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A209,TIPOS!$A:$C,3,FALSE),"")="Sí",B209=""),"Falta el N° de entrega",IF(N(I209)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A209="",C209=""),"",IF(A209="","Falta el tipo",IF(H209="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C209="","Falta el código",IF(ISNA(MATCH(C209,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D209)&gt;0,N(VLOOKUP(C209,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A209,TIPOS!$A:$C,3,FALSE),"")="Sí",B209=""),"Falta el N° de entrega",IF(N(I209)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -7184,7 +7187,7 @@
         <v/>
       </c>
       <c r="H210" s="9">
-        <f>IF(A210="","",IFERROR(VLOOKUP(A210,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A210="","",IFERROR(IF(VLOOKUP(A210,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A210,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I210" s="10">
@@ -7200,7 +7203,7 @@
         <v/>
       </c>
       <c r="L210" s="9">
-        <f>IF(AND(A210="",C210=""),"",IF(A210="","Falta el tipo",IF(C210="","Falta el código",IF(ISNA(MATCH(C210,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D210)&gt;0,N(VLOOKUP(C210,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A210,TIPOS!$A:$C,3,FALSE),"")="Sí",B210=""),"Falta el N° de entrega",IF(N(I210)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A210="",C210=""),"",IF(A210="","Falta el tipo",IF(H210="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C210="","Falta el código",IF(ISNA(MATCH(C210,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D210)&gt;0,N(VLOOKUP(C210,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A210,TIPOS!$A:$C,3,FALSE),"")="Sí",B210=""),"Falta el N° de entrega",IF(N(I210)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -7216,7 +7219,7 @@
         <v/>
       </c>
       <c r="H211" s="9">
-        <f>IF(A211="","",IFERROR(VLOOKUP(A211,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A211="","",IFERROR(IF(VLOOKUP(A211,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A211,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I211" s="10">
@@ -7232,7 +7235,7 @@
         <v/>
       </c>
       <c r="L211" s="9">
-        <f>IF(AND(A211="",C211=""),"",IF(A211="","Falta el tipo",IF(C211="","Falta el código",IF(ISNA(MATCH(C211,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D211)&gt;0,N(VLOOKUP(C211,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A211,TIPOS!$A:$C,3,FALSE),"")="Sí",B211=""),"Falta el N° de entrega",IF(N(I211)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A211="",C211=""),"",IF(A211="","Falta el tipo",IF(H211="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C211="","Falta el código",IF(ISNA(MATCH(C211,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D211)&gt;0,N(VLOOKUP(C211,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A211,TIPOS!$A:$C,3,FALSE),"")="Sí",B211=""),"Falta el N° de entrega",IF(N(I211)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -7248,7 +7251,7 @@
         <v/>
       </c>
       <c r="H212" s="9">
-        <f>IF(A212="","",IFERROR(VLOOKUP(A212,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A212="","",IFERROR(IF(VLOOKUP(A212,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A212,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I212" s="10">
@@ -7264,7 +7267,7 @@
         <v/>
       </c>
       <c r="L212" s="9">
-        <f>IF(AND(A212="",C212=""),"",IF(A212="","Falta el tipo",IF(C212="","Falta el código",IF(ISNA(MATCH(C212,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D212)&gt;0,N(VLOOKUP(C212,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A212,TIPOS!$A:$C,3,FALSE),"")="Sí",B212=""),"Falta el N° de entrega",IF(N(I212)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A212="",C212=""),"",IF(A212="","Falta el tipo",IF(H212="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C212="","Falta el código",IF(ISNA(MATCH(C212,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D212)&gt;0,N(VLOOKUP(C212,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A212,TIPOS!$A:$C,3,FALSE),"")="Sí",B212=""),"Falta el N° de entrega",IF(N(I212)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -7280,7 +7283,7 @@
         <v/>
       </c>
       <c r="H213" s="9">
-        <f>IF(A213="","",IFERROR(VLOOKUP(A213,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A213="","",IFERROR(IF(VLOOKUP(A213,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A213,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I213" s="10">
@@ -7296,7 +7299,7 @@
         <v/>
       </c>
       <c r="L213" s="9">
-        <f>IF(AND(A213="",C213=""),"",IF(A213="","Falta el tipo",IF(C213="","Falta el código",IF(ISNA(MATCH(C213,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D213)&gt;0,N(VLOOKUP(C213,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A213,TIPOS!$A:$C,3,FALSE),"")="Sí",B213=""),"Falta el N° de entrega",IF(N(I213)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A213="",C213=""),"",IF(A213="","Falta el tipo",IF(H213="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C213="","Falta el código",IF(ISNA(MATCH(C213,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D213)&gt;0,N(VLOOKUP(C213,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A213,TIPOS!$A:$C,3,FALSE),"")="Sí",B213=""),"Falta el N° de entrega",IF(N(I213)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -7312,7 +7315,7 @@
         <v/>
       </c>
       <c r="H214" s="9">
-        <f>IF(A214="","",IFERROR(VLOOKUP(A214,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A214="","",IFERROR(IF(VLOOKUP(A214,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A214,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I214" s="10">
@@ -7328,7 +7331,7 @@
         <v/>
       </c>
       <c r="L214" s="9">
-        <f>IF(AND(A214="",C214=""),"",IF(A214="","Falta el tipo",IF(C214="","Falta el código",IF(ISNA(MATCH(C214,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D214)&gt;0,N(VLOOKUP(C214,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A214,TIPOS!$A:$C,3,FALSE),"")="Sí",B214=""),"Falta el N° de entrega",IF(N(I214)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A214="",C214=""),"",IF(A214="","Falta el tipo",IF(H214="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C214="","Falta el código",IF(ISNA(MATCH(C214,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D214)&gt;0,N(VLOOKUP(C214,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A214,TIPOS!$A:$C,3,FALSE),"")="Sí",B214=""),"Falta el N° de entrega",IF(N(I214)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -7344,7 +7347,7 @@
         <v/>
       </c>
       <c r="H215" s="9">
-        <f>IF(A215="","",IFERROR(VLOOKUP(A215,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A215="","",IFERROR(IF(VLOOKUP(A215,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A215,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I215" s="10">
@@ -7360,7 +7363,7 @@
         <v/>
       </c>
       <c r="L215" s="9">
-        <f>IF(AND(A215="",C215=""),"",IF(A215="","Falta el tipo",IF(C215="","Falta el código",IF(ISNA(MATCH(C215,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D215)&gt;0,N(VLOOKUP(C215,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A215,TIPOS!$A:$C,3,FALSE),"")="Sí",B215=""),"Falta el N° de entrega",IF(N(I215)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A215="",C215=""),"",IF(A215="","Falta el tipo",IF(H215="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C215="","Falta el código",IF(ISNA(MATCH(C215,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D215)&gt;0,N(VLOOKUP(C215,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A215,TIPOS!$A:$C,3,FALSE),"")="Sí",B215=""),"Falta el N° de entrega",IF(N(I215)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -7376,7 +7379,7 @@
         <v/>
       </c>
       <c r="H216" s="9">
-        <f>IF(A216="","",IFERROR(VLOOKUP(A216,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A216="","",IFERROR(IF(VLOOKUP(A216,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A216,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I216" s="10">
@@ -7392,7 +7395,7 @@
         <v/>
       </c>
       <c r="L216" s="9">
-        <f>IF(AND(A216="",C216=""),"",IF(A216="","Falta el tipo",IF(C216="","Falta el código",IF(ISNA(MATCH(C216,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D216)&gt;0,N(VLOOKUP(C216,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A216,TIPOS!$A:$C,3,FALSE),"")="Sí",B216=""),"Falta el N° de entrega",IF(N(I216)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A216="",C216=""),"",IF(A216="","Falta el tipo",IF(H216="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C216="","Falta el código",IF(ISNA(MATCH(C216,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D216)&gt;0,N(VLOOKUP(C216,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A216,TIPOS!$A:$C,3,FALSE),"")="Sí",B216=""),"Falta el N° de entrega",IF(N(I216)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -7408,7 +7411,7 @@
         <v/>
       </c>
       <c r="H217" s="9">
-        <f>IF(A217="","",IFERROR(VLOOKUP(A217,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A217="","",IFERROR(IF(VLOOKUP(A217,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A217,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I217" s="10">
@@ -7424,7 +7427,7 @@
         <v/>
       </c>
       <c r="L217" s="9">
-        <f>IF(AND(A217="",C217=""),"",IF(A217="","Falta el tipo",IF(C217="","Falta el código",IF(ISNA(MATCH(C217,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D217)&gt;0,N(VLOOKUP(C217,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A217,TIPOS!$A:$C,3,FALSE),"")="Sí",B217=""),"Falta el N° de entrega",IF(N(I217)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A217="",C217=""),"",IF(A217="","Falta el tipo",IF(H217="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C217="","Falta el código",IF(ISNA(MATCH(C217,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D217)&gt;0,N(VLOOKUP(C217,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A217,TIPOS!$A:$C,3,FALSE),"")="Sí",B217=""),"Falta el N° de entrega",IF(N(I217)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -7440,7 +7443,7 @@
         <v/>
       </c>
       <c r="H218" s="9">
-        <f>IF(A218="","",IFERROR(VLOOKUP(A218,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A218="","",IFERROR(IF(VLOOKUP(A218,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A218,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I218" s="10">
@@ -7456,7 +7459,7 @@
         <v/>
       </c>
       <c r="L218" s="9">
-        <f>IF(AND(A218="",C218=""),"",IF(A218="","Falta el tipo",IF(C218="","Falta el código",IF(ISNA(MATCH(C218,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D218)&gt;0,N(VLOOKUP(C218,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A218,TIPOS!$A:$C,3,FALSE),"")="Sí",B218=""),"Falta el N° de entrega",IF(N(I218)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A218="",C218=""),"",IF(A218="","Falta el tipo",IF(H218="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C218="","Falta el código",IF(ISNA(MATCH(C218,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D218)&gt;0,N(VLOOKUP(C218,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A218,TIPOS!$A:$C,3,FALSE),"")="Sí",B218=""),"Falta el N° de entrega",IF(N(I218)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -7472,7 +7475,7 @@
         <v/>
       </c>
       <c r="H219" s="9">
-        <f>IF(A219="","",IFERROR(VLOOKUP(A219,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A219="","",IFERROR(IF(VLOOKUP(A219,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A219,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I219" s="10">
@@ -7488,7 +7491,7 @@
         <v/>
       </c>
       <c r="L219" s="9">
-        <f>IF(AND(A219="",C219=""),"",IF(A219="","Falta el tipo",IF(C219="","Falta el código",IF(ISNA(MATCH(C219,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D219)&gt;0,N(VLOOKUP(C219,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A219,TIPOS!$A:$C,3,FALSE),"")="Sí",B219=""),"Falta el N° de entrega",IF(N(I219)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A219="",C219=""),"",IF(A219="","Falta el tipo",IF(H219="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C219="","Falta el código",IF(ISNA(MATCH(C219,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D219)&gt;0,N(VLOOKUP(C219,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A219,TIPOS!$A:$C,3,FALSE),"")="Sí",B219=""),"Falta el N° de entrega",IF(N(I219)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -7504,7 +7507,7 @@
         <v/>
       </c>
       <c r="H220" s="9">
-        <f>IF(A220="","",IFERROR(VLOOKUP(A220,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A220="","",IFERROR(IF(VLOOKUP(A220,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A220,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I220" s="10">
@@ -7520,7 +7523,7 @@
         <v/>
       </c>
       <c r="L220" s="9">
-        <f>IF(AND(A220="",C220=""),"",IF(A220="","Falta el tipo",IF(C220="","Falta el código",IF(ISNA(MATCH(C220,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D220)&gt;0,N(VLOOKUP(C220,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A220,TIPOS!$A:$C,3,FALSE),"")="Sí",B220=""),"Falta el N° de entrega",IF(N(I220)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A220="",C220=""),"",IF(A220="","Falta el tipo",IF(H220="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C220="","Falta el código",IF(ISNA(MATCH(C220,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D220)&gt;0,N(VLOOKUP(C220,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A220,TIPOS!$A:$C,3,FALSE),"")="Sí",B220=""),"Falta el N° de entrega",IF(N(I220)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -7536,7 +7539,7 @@
         <v/>
       </c>
       <c r="H221" s="9">
-        <f>IF(A221="","",IFERROR(VLOOKUP(A221,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A221="","",IFERROR(IF(VLOOKUP(A221,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A221,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I221" s="10">
@@ -7552,7 +7555,7 @@
         <v/>
       </c>
       <c r="L221" s="9">
-        <f>IF(AND(A221="",C221=""),"",IF(A221="","Falta el tipo",IF(C221="","Falta el código",IF(ISNA(MATCH(C221,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D221)&gt;0,N(VLOOKUP(C221,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A221,TIPOS!$A:$C,3,FALSE),"")="Sí",B221=""),"Falta el N° de entrega",IF(N(I221)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A221="",C221=""),"",IF(A221="","Falta el tipo",IF(H221="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C221="","Falta el código",IF(ISNA(MATCH(C221,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D221)&gt;0,N(VLOOKUP(C221,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A221,TIPOS!$A:$C,3,FALSE),"")="Sí",B221=""),"Falta el N° de entrega",IF(N(I221)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -7568,7 +7571,7 @@
         <v/>
       </c>
       <c r="H222" s="9">
-        <f>IF(A222="","",IFERROR(VLOOKUP(A222,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A222="","",IFERROR(IF(VLOOKUP(A222,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A222,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I222" s="10">
@@ -7584,7 +7587,7 @@
         <v/>
       </c>
       <c r="L222" s="9">
-        <f>IF(AND(A222="",C222=""),"",IF(A222="","Falta el tipo",IF(C222="","Falta el código",IF(ISNA(MATCH(C222,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D222)&gt;0,N(VLOOKUP(C222,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A222,TIPOS!$A:$C,3,FALSE),"")="Sí",B222=""),"Falta el N° de entrega",IF(N(I222)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A222="",C222=""),"",IF(A222="","Falta el tipo",IF(H222="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C222="","Falta el código",IF(ISNA(MATCH(C222,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D222)&gt;0,N(VLOOKUP(C222,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A222,TIPOS!$A:$C,3,FALSE),"")="Sí",B222=""),"Falta el N° de entrega",IF(N(I222)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -7600,7 +7603,7 @@
         <v/>
       </c>
       <c r="H223" s="9">
-        <f>IF(A223="","",IFERROR(VLOOKUP(A223,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A223="","",IFERROR(IF(VLOOKUP(A223,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A223,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I223" s="10">
@@ -7616,7 +7619,7 @@
         <v/>
       </c>
       <c r="L223" s="9">
-        <f>IF(AND(A223="",C223=""),"",IF(A223="","Falta el tipo",IF(C223="","Falta el código",IF(ISNA(MATCH(C223,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D223)&gt;0,N(VLOOKUP(C223,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A223,TIPOS!$A:$C,3,FALSE),"")="Sí",B223=""),"Falta el N° de entrega",IF(N(I223)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A223="",C223=""),"",IF(A223="","Falta el tipo",IF(H223="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C223="","Falta el código",IF(ISNA(MATCH(C223,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D223)&gt;0,N(VLOOKUP(C223,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A223,TIPOS!$A:$C,3,FALSE),"")="Sí",B223=""),"Falta el N° de entrega",IF(N(I223)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -7632,7 +7635,7 @@
         <v/>
       </c>
       <c r="H224" s="9">
-        <f>IF(A224="","",IFERROR(VLOOKUP(A224,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A224="","",IFERROR(IF(VLOOKUP(A224,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A224,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I224" s="10">
@@ -7648,7 +7651,7 @@
         <v/>
       </c>
       <c r="L224" s="9">
-        <f>IF(AND(A224="",C224=""),"",IF(A224="","Falta el tipo",IF(C224="","Falta el código",IF(ISNA(MATCH(C224,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D224)&gt;0,N(VLOOKUP(C224,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A224,TIPOS!$A:$C,3,FALSE),"")="Sí",B224=""),"Falta el N° de entrega",IF(N(I224)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A224="",C224=""),"",IF(A224="","Falta el tipo",IF(H224="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C224="","Falta el código",IF(ISNA(MATCH(C224,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D224)&gt;0,N(VLOOKUP(C224,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A224,TIPOS!$A:$C,3,FALSE),"")="Sí",B224=""),"Falta el N° de entrega",IF(N(I224)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -7664,7 +7667,7 @@
         <v/>
       </c>
       <c r="H225" s="9">
-        <f>IF(A225="","",IFERROR(VLOOKUP(A225,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A225="","",IFERROR(IF(VLOOKUP(A225,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A225,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I225" s="10">
@@ -7680,7 +7683,7 @@
         <v/>
       </c>
       <c r="L225" s="9">
-        <f>IF(AND(A225="",C225=""),"",IF(A225="","Falta el tipo",IF(C225="","Falta el código",IF(ISNA(MATCH(C225,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D225)&gt;0,N(VLOOKUP(C225,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A225,TIPOS!$A:$C,3,FALSE),"")="Sí",B225=""),"Falta el N° de entrega",IF(N(I225)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A225="",C225=""),"",IF(A225="","Falta el tipo",IF(H225="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C225="","Falta el código",IF(ISNA(MATCH(C225,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D225)&gt;0,N(VLOOKUP(C225,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A225,TIPOS!$A:$C,3,FALSE),"")="Sí",B225=""),"Falta el N° de entrega",IF(N(I225)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -7696,7 +7699,7 @@
         <v/>
       </c>
       <c r="H226" s="9">
-        <f>IF(A226="","",IFERROR(VLOOKUP(A226,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A226="","",IFERROR(IF(VLOOKUP(A226,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A226,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I226" s="10">
@@ -7712,7 +7715,7 @@
         <v/>
       </c>
       <c r="L226" s="9">
-        <f>IF(AND(A226="",C226=""),"",IF(A226="","Falta el tipo",IF(C226="","Falta el código",IF(ISNA(MATCH(C226,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D226)&gt;0,N(VLOOKUP(C226,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A226,TIPOS!$A:$C,3,FALSE),"")="Sí",B226=""),"Falta el N° de entrega",IF(N(I226)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A226="",C226=""),"",IF(A226="","Falta el tipo",IF(H226="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C226="","Falta el código",IF(ISNA(MATCH(C226,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D226)&gt;0,N(VLOOKUP(C226,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A226,TIPOS!$A:$C,3,FALSE),"")="Sí",B226=""),"Falta el N° de entrega",IF(N(I226)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -7728,7 +7731,7 @@
         <v/>
       </c>
       <c r="H227" s="9">
-        <f>IF(A227="","",IFERROR(VLOOKUP(A227,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A227="","",IFERROR(IF(VLOOKUP(A227,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A227,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I227" s="10">
@@ -7744,7 +7747,7 @@
         <v/>
       </c>
       <c r="L227" s="9">
-        <f>IF(AND(A227="",C227=""),"",IF(A227="","Falta el tipo",IF(C227="","Falta el código",IF(ISNA(MATCH(C227,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D227)&gt;0,N(VLOOKUP(C227,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A227,TIPOS!$A:$C,3,FALSE),"")="Sí",B227=""),"Falta el N° de entrega",IF(N(I227)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A227="",C227=""),"",IF(A227="","Falta el tipo",IF(H227="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C227="","Falta el código",IF(ISNA(MATCH(C227,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D227)&gt;0,N(VLOOKUP(C227,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A227,TIPOS!$A:$C,3,FALSE),"")="Sí",B227=""),"Falta el N° de entrega",IF(N(I227)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -7760,7 +7763,7 @@
         <v/>
       </c>
       <c r="H228" s="9">
-        <f>IF(A228="","",IFERROR(VLOOKUP(A228,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A228="","",IFERROR(IF(VLOOKUP(A228,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A228,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I228" s="10">
@@ -7776,7 +7779,7 @@
         <v/>
       </c>
       <c r="L228" s="9">
-        <f>IF(AND(A228="",C228=""),"",IF(A228="","Falta el tipo",IF(C228="","Falta el código",IF(ISNA(MATCH(C228,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D228)&gt;0,N(VLOOKUP(C228,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A228,TIPOS!$A:$C,3,FALSE),"")="Sí",B228=""),"Falta el N° de entrega",IF(N(I228)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A228="",C228=""),"",IF(A228="","Falta el tipo",IF(H228="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C228="","Falta el código",IF(ISNA(MATCH(C228,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D228)&gt;0,N(VLOOKUP(C228,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A228,TIPOS!$A:$C,3,FALSE),"")="Sí",B228=""),"Falta el N° de entrega",IF(N(I228)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -7792,7 +7795,7 @@
         <v/>
       </c>
       <c r="H229" s="9">
-        <f>IF(A229="","",IFERROR(VLOOKUP(A229,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A229="","",IFERROR(IF(VLOOKUP(A229,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A229,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I229" s="10">
@@ -7808,7 +7811,7 @@
         <v/>
       </c>
       <c r="L229" s="9">
-        <f>IF(AND(A229="",C229=""),"",IF(A229="","Falta el tipo",IF(C229="","Falta el código",IF(ISNA(MATCH(C229,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D229)&gt;0,N(VLOOKUP(C229,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A229,TIPOS!$A:$C,3,FALSE),"")="Sí",B229=""),"Falta el N° de entrega",IF(N(I229)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A229="",C229=""),"",IF(A229="","Falta el tipo",IF(H229="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C229="","Falta el código",IF(ISNA(MATCH(C229,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D229)&gt;0,N(VLOOKUP(C229,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A229,TIPOS!$A:$C,3,FALSE),"")="Sí",B229=""),"Falta el N° de entrega",IF(N(I229)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -7824,7 +7827,7 @@
         <v/>
       </c>
       <c r="H230" s="9">
-        <f>IF(A230="","",IFERROR(VLOOKUP(A230,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A230="","",IFERROR(IF(VLOOKUP(A230,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A230,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I230" s="10">
@@ -7840,7 +7843,7 @@
         <v/>
       </c>
       <c r="L230" s="9">
-        <f>IF(AND(A230="",C230=""),"",IF(A230="","Falta el tipo",IF(C230="","Falta el código",IF(ISNA(MATCH(C230,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D230)&gt;0,N(VLOOKUP(C230,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A230,TIPOS!$A:$C,3,FALSE),"")="Sí",B230=""),"Falta el N° de entrega",IF(N(I230)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A230="",C230=""),"",IF(A230="","Falta el tipo",IF(H230="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C230="","Falta el código",IF(ISNA(MATCH(C230,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D230)&gt;0,N(VLOOKUP(C230,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A230,TIPOS!$A:$C,3,FALSE),"")="Sí",B230=""),"Falta el N° de entrega",IF(N(I230)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -7856,7 +7859,7 @@
         <v/>
       </c>
       <c r="H231" s="9">
-        <f>IF(A231="","",IFERROR(VLOOKUP(A231,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A231="","",IFERROR(IF(VLOOKUP(A231,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A231,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I231" s="10">
@@ -7872,7 +7875,7 @@
         <v/>
       </c>
       <c r="L231" s="9">
-        <f>IF(AND(A231="",C231=""),"",IF(A231="","Falta el tipo",IF(C231="","Falta el código",IF(ISNA(MATCH(C231,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D231)&gt;0,N(VLOOKUP(C231,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A231,TIPOS!$A:$C,3,FALSE),"")="Sí",B231=""),"Falta el N° de entrega",IF(N(I231)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A231="",C231=""),"",IF(A231="","Falta el tipo",IF(H231="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C231="","Falta el código",IF(ISNA(MATCH(C231,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D231)&gt;0,N(VLOOKUP(C231,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A231,TIPOS!$A:$C,3,FALSE),"")="Sí",B231=""),"Falta el N° de entrega",IF(N(I231)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -7888,7 +7891,7 @@
         <v/>
       </c>
       <c r="H232" s="9">
-        <f>IF(A232="","",IFERROR(VLOOKUP(A232,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A232="","",IFERROR(IF(VLOOKUP(A232,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A232,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I232" s="10">
@@ -7904,7 +7907,7 @@
         <v/>
       </c>
       <c r="L232" s="9">
-        <f>IF(AND(A232="",C232=""),"",IF(A232="","Falta el tipo",IF(C232="","Falta el código",IF(ISNA(MATCH(C232,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D232)&gt;0,N(VLOOKUP(C232,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A232,TIPOS!$A:$C,3,FALSE),"")="Sí",B232=""),"Falta el N° de entrega",IF(N(I232)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A232="",C232=""),"",IF(A232="","Falta el tipo",IF(H232="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C232="","Falta el código",IF(ISNA(MATCH(C232,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D232)&gt;0,N(VLOOKUP(C232,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A232,TIPOS!$A:$C,3,FALSE),"")="Sí",B232=""),"Falta el N° de entrega",IF(N(I232)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -7920,7 +7923,7 @@
         <v/>
       </c>
       <c r="H233" s="9">
-        <f>IF(A233="","",IFERROR(VLOOKUP(A233,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A233="","",IFERROR(IF(VLOOKUP(A233,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A233,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I233" s="10">
@@ -7936,7 +7939,7 @@
         <v/>
       </c>
       <c r="L233" s="9">
-        <f>IF(AND(A233="",C233=""),"",IF(A233="","Falta el tipo",IF(C233="","Falta el código",IF(ISNA(MATCH(C233,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D233)&gt;0,N(VLOOKUP(C233,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A233,TIPOS!$A:$C,3,FALSE),"")="Sí",B233=""),"Falta el N° de entrega",IF(N(I233)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A233="",C233=""),"",IF(A233="","Falta el tipo",IF(H233="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C233="","Falta el código",IF(ISNA(MATCH(C233,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D233)&gt;0,N(VLOOKUP(C233,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A233,TIPOS!$A:$C,3,FALSE),"")="Sí",B233=""),"Falta el N° de entrega",IF(N(I233)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -7952,7 +7955,7 @@
         <v/>
       </c>
       <c r="H234" s="9">
-        <f>IF(A234="","",IFERROR(VLOOKUP(A234,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A234="","",IFERROR(IF(VLOOKUP(A234,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A234,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I234" s="10">
@@ -7968,7 +7971,7 @@
         <v/>
       </c>
       <c r="L234" s="9">
-        <f>IF(AND(A234="",C234=""),"",IF(A234="","Falta el tipo",IF(C234="","Falta el código",IF(ISNA(MATCH(C234,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D234)&gt;0,N(VLOOKUP(C234,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A234,TIPOS!$A:$C,3,FALSE),"")="Sí",B234=""),"Falta el N° de entrega",IF(N(I234)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A234="",C234=""),"",IF(A234="","Falta el tipo",IF(H234="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C234="","Falta el código",IF(ISNA(MATCH(C234,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D234)&gt;0,N(VLOOKUP(C234,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A234,TIPOS!$A:$C,3,FALSE),"")="Sí",B234=""),"Falta el N° de entrega",IF(N(I234)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -7984,7 +7987,7 @@
         <v/>
       </c>
       <c r="H235" s="9">
-        <f>IF(A235="","",IFERROR(VLOOKUP(A235,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A235="","",IFERROR(IF(VLOOKUP(A235,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A235,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I235" s="10">
@@ -8000,7 +8003,7 @@
         <v/>
       </c>
       <c r="L235" s="9">
-        <f>IF(AND(A235="",C235=""),"",IF(A235="","Falta el tipo",IF(C235="","Falta el código",IF(ISNA(MATCH(C235,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D235)&gt;0,N(VLOOKUP(C235,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A235,TIPOS!$A:$C,3,FALSE),"")="Sí",B235=""),"Falta el N° de entrega",IF(N(I235)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A235="",C235=""),"",IF(A235="","Falta el tipo",IF(H235="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C235="","Falta el código",IF(ISNA(MATCH(C235,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D235)&gt;0,N(VLOOKUP(C235,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A235,TIPOS!$A:$C,3,FALSE),"")="Sí",B235=""),"Falta el N° de entrega",IF(N(I235)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -8016,7 +8019,7 @@
         <v/>
       </c>
       <c r="H236" s="9">
-        <f>IF(A236="","",IFERROR(VLOOKUP(A236,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A236="","",IFERROR(IF(VLOOKUP(A236,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A236,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I236" s="10">
@@ -8032,7 +8035,7 @@
         <v/>
       </c>
       <c r="L236" s="9">
-        <f>IF(AND(A236="",C236=""),"",IF(A236="","Falta el tipo",IF(C236="","Falta el código",IF(ISNA(MATCH(C236,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D236)&gt;0,N(VLOOKUP(C236,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A236,TIPOS!$A:$C,3,FALSE),"")="Sí",B236=""),"Falta el N° de entrega",IF(N(I236)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A236="",C236=""),"",IF(A236="","Falta el tipo",IF(H236="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C236="","Falta el código",IF(ISNA(MATCH(C236,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D236)&gt;0,N(VLOOKUP(C236,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A236,TIPOS!$A:$C,3,FALSE),"")="Sí",B236=""),"Falta el N° de entrega",IF(N(I236)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -8048,7 +8051,7 @@
         <v/>
       </c>
       <c r="H237" s="9">
-        <f>IF(A237="","",IFERROR(VLOOKUP(A237,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A237="","",IFERROR(IF(VLOOKUP(A237,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A237,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I237" s="10">
@@ -8064,7 +8067,7 @@
         <v/>
       </c>
       <c r="L237" s="9">
-        <f>IF(AND(A237="",C237=""),"",IF(A237="","Falta el tipo",IF(C237="","Falta el código",IF(ISNA(MATCH(C237,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D237)&gt;0,N(VLOOKUP(C237,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A237,TIPOS!$A:$C,3,FALSE),"")="Sí",B237=""),"Falta el N° de entrega",IF(N(I237)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A237="",C237=""),"",IF(A237="","Falta el tipo",IF(H237="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C237="","Falta el código",IF(ISNA(MATCH(C237,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D237)&gt;0,N(VLOOKUP(C237,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A237,TIPOS!$A:$C,3,FALSE),"")="Sí",B237=""),"Falta el N° de entrega",IF(N(I237)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -8080,7 +8083,7 @@
         <v/>
       </c>
       <c r="H238" s="9">
-        <f>IF(A238="","",IFERROR(VLOOKUP(A238,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A238="","",IFERROR(IF(VLOOKUP(A238,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A238,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I238" s="10">
@@ -8096,7 +8099,7 @@
         <v/>
       </c>
       <c r="L238" s="9">
-        <f>IF(AND(A238="",C238=""),"",IF(A238="","Falta el tipo",IF(C238="","Falta el código",IF(ISNA(MATCH(C238,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D238)&gt;0,N(VLOOKUP(C238,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A238,TIPOS!$A:$C,3,FALSE),"")="Sí",B238=""),"Falta el N° de entrega",IF(N(I238)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A238="",C238=""),"",IF(A238="","Falta el tipo",IF(H238="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C238="","Falta el código",IF(ISNA(MATCH(C238,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D238)&gt;0,N(VLOOKUP(C238,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A238,TIPOS!$A:$C,3,FALSE),"")="Sí",B238=""),"Falta el N° de entrega",IF(N(I238)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -8112,7 +8115,7 @@
         <v/>
       </c>
       <c r="H239" s="9">
-        <f>IF(A239="","",IFERROR(VLOOKUP(A239,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A239="","",IFERROR(IF(VLOOKUP(A239,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A239,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I239" s="10">
@@ -8128,7 +8131,7 @@
         <v/>
       </c>
       <c r="L239" s="9">
-        <f>IF(AND(A239="",C239=""),"",IF(A239="","Falta el tipo",IF(C239="","Falta el código",IF(ISNA(MATCH(C239,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D239)&gt;0,N(VLOOKUP(C239,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A239,TIPOS!$A:$C,3,FALSE),"")="Sí",B239=""),"Falta el N° de entrega",IF(N(I239)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A239="",C239=""),"",IF(A239="","Falta el tipo",IF(H239="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C239="","Falta el código",IF(ISNA(MATCH(C239,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D239)&gt;0,N(VLOOKUP(C239,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A239,TIPOS!$A:$C,3,FALSE),"")="Sí",B239=""),"Falta el N° de entrega",IF(N(I239)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -8144,7 +8147,7 @@
         <v/>
       </c>
       <c r="H240" s="9">
-        <f>IF(A240="","",IFERROR(VLOOKUP(A240,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A240="","",IFERROR(IF(VLOOKUP(A240,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A240,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I240" s="10">
@@ -8160,7 +8163,7 @@
         <v/>
       </c>
       <c r="L240" s="9">
-        <f>IF(AND(A240="",C240=""),"",IF(A240="","Falta el tipo",IF(C240="","Falta el código",IF(ISNA(MATCH(C240,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D240)&gt;0,N(VLOOKUP(C240,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A240,TIPOS!$A:$C,3,FALSE),"")="Sí",B240=""),"Falta el N° de entrega",IF(N(I240)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A240="",C240=""),"",IF(A240="","Falta el tipo",IF(H240="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C240="","Falta el código",IF(ISNA(MATCH(C240,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D240)&gt;0,N(VLOOKUP(C240,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A240,TIPOS!$A:$C,3,FALSE),"")="Sí",B240=""),"Falta el N° de entrega",IF(N(I240)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -8176,7 +8179,7 @@
         <v/>
       </c>
       <c r="H241" s="9">
-        <f>IF(A241="","",IFERROR(VLOOKUP(A241,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A241="","",IFERROR(IF(VLOOKUP(A241,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A241,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I241" s="10">
@@ -8192,7 +8195,7 @@
         <v/>
       </c>
       <c r="L241" s="9">
-        <f>IF(AND(A241="",C241=""),"",IF(A241="","Falta el tipo",IF(C241="","Falta el código",IF(ISNA(MATCH(C241,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D241)&gt;0,N(VLOOKUP(C241,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A241,TIPOS!$A:$C,3,FALSE),"")="Sí",B241=""),"Falta el N° de entrega",IF(N(I241)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A241="",C241=""),"",IF(A241="","Falta el tipo",IF(H241="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C241="","Falta el código",IF(ISNA(MATCH(C241,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D241)&gt;0,N(VLOOKUP(C241,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A241,TIPOS!$A:$C,3,FALSE),"")="Sí",B241=""),"Falta el N° de entrega",IF(N(I241)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -8208,7 +8211,7 @@
         <v/>
       </c>
       <c r="H242" s="9">
-        <f>IF(A242="","",IFERROR(VLOOKUP(A242,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A242="","",IFERROR(IF(VLOOKUP(A242,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A242,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I242" s="10">
@@ -8224,7 +8227,7 @@
         <v/>
       </c>
       <c r="L242" s="9">
-        <f>IF(AND(A242="",C242=""),"",IF(A242="","Falta el tipo",IF(C242="","Falta el código",IF(ISNA(MATCH(C242,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D242)&gt;0,N(VLOOKUP(C242,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A242,TIPOS!$A:$C,3,FALSE),"")="Sí",B242=""),"Falta el N° de entrega",IF(N(I242)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A242="",C242=""),"",IF(A242="","Falta el tipo",IF(H242="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C242="","Falta el código",IF(ISNA(MATCH(C242,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D242)&gt;0,N(VLOOKUP(C242,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A242,TIPOS!$A:$C,3,FALSE),"")="Sí",B242=""),"Falta el N° de entrega",IF(N(I242)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -8240,7 +8243,7 @@
         <v/>
       </c>
       <c r="H243" s="9">
-        <f>IF(A243="","",IFERROR(VLOOKUP(A243,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A243="","",IFERROR(IF(VLOOKUP(A243,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A243,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I243" s="10">
@@ -8256,7 +8259,7 @@
         <v/>
       </c>
       <c r="L243" s="9">
-        <f>IF(AND(A243="",C243=""),"",IF(A243="","Falta el tipo",IF(C243="","Falta el código",IF(ISNA(MATCH(C243,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D243)&gt;0,N(VLOOKUP(C243,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A243,TIPOS!$A:$C,3,FALSE),"")="Sí",B243=""),"Falta el N° de entrega",IF(N(I243)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A243="",C243=""),"",IF(A243="","Falta el tipo",IF(H243="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C243="","Falta el código",IF(ISNA(MATCH(C243,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D243)&gt;0,N(VLOOKUP(C243,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A243,TIPOS!$A:$C,3,FALSE),"")="Sí",B243=""),"Falta el N° de entrega",IF(N(I243)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -8272,7 +8275,7 @@
         <v/>
       </c>
       <c r="H244" s="9">
-        <f>IF(A244="","",IFERROR(VLOOKUP(A244,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A244="","",IFERROR(IF(VLOOKUP(A244,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A244,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I244" s="10">
@@ -8288,7 +8291,7 @@
         <v/>
       </c>
       <c r="L244" s="9">
-        <f>IF(AND(A244="",C244=""),"",IF(A244="","Falta el tipo",IF(C244="","Falta el código",IF(ISNA(MATCH(C244,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D244)&gt;0,N(VLOOKUP(C244,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A244,TIPOS!$A:$C,3,FALSE),"")="Sí",B244=""),"Falta el N° de entrega",IF(N(I244)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A244="",C244=""),"",IF(A244="","Falta el tipo",IF(H244="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C244="","Falta el código",IF(ISNA(MATCH(C244,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D244)&gt;0,N(VLOOKUP(C244,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A244,TIPOS!$A:$C,3,FALSE),"")="Sí",B244=""),"Falta el N° de entrega",IF(N(I244)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -8304,7 +8307,7 @@
         <v/>
       </c>
       <c r="H245" s="9">
-        <f>IF(A245="","",IFERROR(VLOOKUP(A245,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A245="","",IFERROR(IF(VLOOKUP(A245,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A245,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I245" s="10">
@@ -8320,7 +8323,7 @@
         <v/>
       </c>
       <c r="L245" s="9">
-        <f>IF(AND(A245="",C245=""),"",IF(A245="","Falta el tipo",IF(C245="","Falta el código",IF(ISNA(MATCH(C245,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D245)&gt;0,N(VLOOKUP(C245,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A245,TIPOS!$A:$C,3,FALSE),"")="Sí",B245=""),"Falta el N° de entrega",IF(N(I245)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A245="",C245=""),"",IF(A245="","Falta el tipo",IF(H245="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C245="","Falta el código",IF(ISNA(MATCH(C245,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D245)&gt;0,N(VLOOKUP(C245,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A245,TIPOS!$A:$C,3,FALSE),"")="Sí",B245=""),"Falta el N° de entrega",IF(N(I245)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -8336,7 +8339,7 @@
         <v/>
       </c>
       <c r="H246" s="9">
-        <f>IF(A246="","",IFERROR(VLOOKUP(A246,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A246="","",IFERROR(IF(VLOOKUP(A246,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A246,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I246" s="10">
@@ -8352,7 +8355,7 @@
         <v/>
       </c>
       <c r="L246" s="9">
-        <f>IF(AND(A246="",C246=""),"",IF(A246="","Falta el tipo",IF(C246="","Falta el código",IF(ISNA(MATCH(C246,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D246)&gt;0,N(VLOOKUP(C246,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A246,TIPOS!$A:$C,3,FALSE),"")="Sí",B246=""),"Falta el N° de entrega",IF(N(I246)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A246="",C246=""),"",IF(A246="","Falta el tipo",IF(H246="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C246="","Falta el código",IF(ISNA(MATCH(C246,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D246)&gt;0,N(VLOOKUP(C246,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A246,TIPOS!$A:$C,3,FALSE),"")="Sí",B246=""),"Falta el N° de entrega",IF(N(I246)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -8368,7 +8371,7 @@
         <v/>
       </c>
       <c r="H247" s="9">
-        <f>IF(A247="","",IFERROR(VLOOKUP(A247,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A247="","",IFERROR(IF(VLOOKUP(A247,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A247,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I247" s="10">
@@ -8384,7 +8387,7 @@
         <v/>
       </c>
       <c r="L247" s="9">
-        <f>IF(AND(A247="",C247=""),"",IF(A247="","Falta el tipo",IF(C247="","Falta el código",IF(ISNA(MATCH(C247,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D247)&gt;0,N(VLOOKUP(C247,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A247,TIPOS!$A:$C,3,FALSE),"")="Sí",B247=""),"Falta el N° de entrega",IF(N(I247)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A247="",C247=""),"",IF(A247="","Falta el tipo",IF(H247="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C247="","Falta el código",IF(ISNA(MATCH(C247,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D247)&gt;0,N(VLOOKUP(C247,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A247,TIPOS!$A:$C,3,FALSE),"")="Sí",B247=""),"Falta el N° de entrega",IF(N(I247)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -8400,7 +8403,7 @@
         <v/>
       </c>
       <c r="H248" s="9">
-        <f>IF(A248="","",IFERROR(VLOOKUP(A248,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A248="","",IFERROR(IF(VLOOKUP(A248,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A248,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I248" s="10">
@@ -8416,7 +8419,7 @@
         <v/>
       </c>
       <c r="L248" s="9">
-        <f>IF(AND(A248="",C248=""),"",IF(A248="","Falta el tipo",IF(C248="","Falta el código",IF(ISNA(MATCH(C248,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D248)&gt;0,N(VLOOKUP(C248,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A248,TIPOS!$A:$C,3,FALSE),"")="Sí",B248=""),"Falta el N° de entrega",IF(N(I248)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A248="",C248=""),"",IF(A248="","Falta el tipo",IF(H248="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C248="","Falta el código",IF(ISNA(MATCH(C248,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D248)&gt;0,N(VLOOKUP(C248,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A248,TIPOS!$A:$C,3,FALSE),"")="Sí",B248=""),"Falta el N° de entrega",IF(N(I248)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -8432,7 +8435,7 @@
         <v/>
       </c>
       <c r="H249" s="9">
-        <f>IF(A249="","",IFERROR(VLOOKUP(A249,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A249="","",IFERROR(IF(VLOOKUP(A249,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A249,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I249" s="10">
@@ -8448,7 +8451,7 @@
         <v/>
       </c>
       <c r="L249" s="9">
-        <f>IF(AND(A249="",C249=""),"",IF(A249="","Falta el tipo",IF(C249="","Falta el código",IF(ISNA(MATCH(C249,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D249)&gt;0,N(VLOOKUP(C249,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A249,TIPOS!$A:$C,3,FALSE),"")="Sí",B249=""),"Falta el N° de entrega",IF(N(I249)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A249="",C249=""),"",IF(A249="","Falta el tipo",IF(H249="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C249="","Falta el código",IF(ISNA(MATCH(C249,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D249)&gt;0,N(VLOOKUP(C249,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A249,TIPOS!$A:$C,3,FALSE),"")="Sí",B249=""),"Falta el N° de entrega",IF(N(I249)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -8464,7 +8467,7 @@
         <v/>
       </c>
       <c r="H250" s="9">
-        <f>IF(A250="","",IFERROR(VLOOKUP(A250,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A250="","",IFERROR(IF(VLOOKUP(A250,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A250,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I250" s="10">
@@ -8480,7 +8483,7 @@
         <v/>
       </c>
       <c r="L250" s="9">
-        <f>IF(AND(A250="",C250=""),"",IF(A250="","Falta el tipo",IF(C250="","Falta el código",IF(ISNA(MATCH(C250,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D250)&gt;0,N(VLOOKUP(C250,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A250,TIPOS!$A:$C,3,FALSE),"")="Sí",B250=""),"Falta el N° de entrega",IF(N(I250)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A250="",C250=""),"",IF(A250="","Falta el tipo",IF(H250="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C250="","Falta el código",IF(ISNA(MATCH(C250,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D250)&gt;0,N(VLOOKUP(C250,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A250,TIPOS!$A:$C,3,FALSE),"")="Sí",B250=""),"Falta el N° de entrega",IF(N(I250)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -8496,7 +8499,7 @@
         <v/>
       </c>
       <c r="H251" s="9">
-        <f>IF(A251="","",IFERROR(VLOOKUP(A251,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A251="","",IFERROR(IF(VLOOKUP(A251,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A251,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I251" s="10">
@@ -8512,7 +8515,7 @@
         <v/>
       </c>
       <c r="L251" s="9">
-        <f>IF(AND(A251="",C251=""),"",IF(A251="","Falta el tipo",IF(C251="","Falta el código",IF(ISNA(MATCH(C251,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D251)&gt;0,N(VLOOKUP(C251,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A251,TIPOS!$A:$C,3,FALSE),"")="Sí",B251=""),"Falta el N° de entrega",IF(N(I251)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A251="",C251=""),"",IF(A251="","Falta el tipo",IF(H251="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C251="","Falta el código",IF(ISNA(MATCH(C251,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D251)&gt;0,N(VLOOKUP(C251,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A251,TIPOS!$A:$C,3,FALSE),"")="Sí",B251=""),"Falta el N° de entrega",IF(N(I251)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -8528,7 +8531,7 @@
         <v/>
       </c>
       <c r="H252" s="9">
-        <f>IF(A252="","",IFERROR(VLOOKUP(A252,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A252="","",IFERROR(IF(VLOOKUP(A252,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A252,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I252" s="10">
@@ -8544,7 +8547,7 @@
         <v/>
       </c>
       <c r="L252" s="9">
-        <f>IF(AND(A252="",C252=""),"",IF(A252="","Falta el tipo",IF(C252="","Falta el código",IF(ISNA(MATCH(C252,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D252)&gt;0,N(VLOOKUP(C252,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A252,TIPOS!$A:$C,3,FALSE),"")="Sí",B252=""),"Falta el N° de entrega",IF(N(I252)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A252="",C252=""),"",IF(A252="","Falta el tipo",IF(H252="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C252="","Falta el código",IF(ISNA(MATCH(C252,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D252)&gt;0,N(VLOOKUP(C252,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A252,TIPOS!$A:$C,3,FALSE),"")="Sí",B252=""),"Falta el N° de entrega",IF(N(I252)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -8560,7 +8563,7 @@
         <v/>
       </c>
       <c r="H253" s="9">
-        <f>IF(A253="","",IFERROR(VLOOKUP(A253,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A253="","",IFERROR(IF(VLOOKUP(A253,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A253,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I253" s="10">
@@ -8576,7 +8579,7 @@
         <v/>
       </c>
       <c r="L253" s="9">
-        <f>IF(AND(A253="",C253=""),"",IF(A253="","Falta el tipo",IF(C253="","Falta el código",IF(ISNA(MATCH(C253,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D253)&gt;0,N(VLOOKUP(C253,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A253,TIPOS!$A:$C,3,FALSE),"")="Sí",B253=""),"Falta el N° de entrega",IF(N(I253)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A253="",C253=""),"",IF(A253="","Falta el tipo",IF(H253="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C253="","Falta el código",IF(ISNA(MATCH(C253,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D253)&gt;0,N(VLOOKUP(C253,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A253,TIPOS!$A:$C,3,FALSE),"")="Sí",B253=""),"Falta el N° de entrega",IF(N(I253)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -8592,7 +8595,7 @@
         <v/>
       </c>
       <c r="H254" s="9">
-        <f>IF(A254="","",IFERROR(VLOOKUP(A254,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A254="","",IFERROR(IF(VLOOKUP(A254,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A254,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I254" s="10">
@@ -8608,7 +8611,7 @@
         <v/>
       </c>
       <c r="L254" s="9">
-        <f>IF(AND(A254="",C254=""),"",IF(A254="","Falta el tipo",IF(C254="","Falta el código",IF(ISNA(MATCH(C254,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D254)&gt;0,N(VLOOKUP(C254,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A254,TIPOS!$A:$C,3,FALSE),"")="Sí",B254=""),"Falta el N° de entrega",IF(N(I254)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A254="",C254=""),"",IF(A254="","Falta el tipo",IF(H254="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C254="","Falta el código",IF(ISNA(MATCH(C254,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D254)&gt;0,N(VLOOKUP(C254,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A254,TIPOS!$A:$C,3,FALSE),"")="Sí",B254=""),"Falta el N° de entrega",IF(N(I254)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -8624,7 +8627,7 @@
         <v/>
       </c>
       <c r="H255" s="9">
-        <f>IF(A255="","",IFERROR(VLOOKUP(A255,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A255="","",IFERROR(IF(VLOOKUP(A255,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A255,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I255" s="10">
@@ -8640,7 +8643,7 @@
         <v/>
       </c>
       <c r="L255" s="9">
-        <f>IF(AND(A255="",C255=""),"",IF(A255="","Falta el tipo",IF(C255="","Falta el código",IF(ISNA(MATCH(C255,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D255)&gt;0,N(VLOOKUP(C255,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A255,TIPOS!$A:$C,3,FALSE),"")="Sí",B255=""),"Falta el N° de entrega",IF(N(I255)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A255="",C255=""),"",IF(A255="","Falta el tipo",IF(H255="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C255="","Falta el código",IF(ISNA(MATCH(C255,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D255)&gt;0,N(VLOOKUP(C255,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A255,TIPOS!$A:$C,3,FALSE),"")="Sí",B255=""),"Falta el N° de entrega",IF(N(I255)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -8656,7 +8659,7 @@
         <v/>
       </c>
       <c r="H256" s="9">
-        <f>IF(A256="","",IFERROR(VLOOKUP(A256,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A256="","",IFERROR(IF(VLOOKUP(A256,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A256,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I256" s="10">
@@ -8672,7 +8675,7 @@
         <v/>
       </c>
       <c r="L256" s="9">
-        <f>IF(AND(A256="",C256=""),"",IF(A256="","Falta el tipo",IF(C256="","Falta el código",IF(ISNA(MATCH(C256,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D256)&gt;0,N(VLOOKUP(C256,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A256,TIPOS!$A:$C,3,FALSE),"")="Sí",B256=""),"Falta el N° de entrega",IF(N(I256)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A256="",C256=""),"",IF(A256="","Falta el tipo",IF(H256="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C256="","Falta el código",IF(ISNA(MATCH(C256,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D256)&gt;0,N(VLOOKUP(C256,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A256,TIPOS!$A:$C,3,FALSE),"")="Sí",B256=""),"Falta el N° de entrega",IF(N(I256)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -8688,7 +8691,7 @@
         <v/>
       </c>
       <c r="H257" s="9">
-        <f>IF(A257="","",IFERROR(VLOOKUP(A257,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A257="","",IFERROR(IF(VLOOKUP(A257,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A257,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I257" s="10">
@@ -8704,7 +8707,7 @@
         <v/>
       </c>
       <c r="L257" s="9">
-        <f>IF(AND(A257="",C257=""),"",IF(A257="","Falta el tipo",IF(C257="","Falta el código",IF(ISNA(MATCH(C257,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D257)&gt;0,N(VLOOKUP(C257,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A257,TIPOS!$A:$C,3,FALSE),"")="Sí",B257=""),"Falta el N° de entrega",IF(N(I257)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A257="",C257=""),"",IF(A257="","Falta el tipo",IF(H257="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C257="","Falta el código",IF(ISNA(MATCH(C257,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D257)&gt;0,N(VLOOKUP(C257,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A257,TIPOS!$A:$C,3,FALSE),"")="Sí",B257=""),"Falta el N° de entrega",IF(N(I257)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -8720,7 +8723,7 @@
         <v/>
       </c>
       <c r="H258" s="9">
-        <f>IF(A258="","",IFERROR(VLOOKUP(A258,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A258="","",IFERROR(IF(VLOOKUP(A258,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A258,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I258" s="10">
@@ -8736,7 +8739,7 @@
         <v/>
       </c>
       <c r="L258" s="9">
-        <f>IF(AND(A258="",C258=""),"",IF(A258="","Falta el tipo",IF(C258="","Falta el código",IF(ISNA(MATCH(C258,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D258)&gt;0,N(VLOOKUP(C258,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A258,TIPOS!$A:$C,3,FALSE),"")="Sí",B258=""),"Falta el N° de entrega",IF(N(I258)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A258="",C258=""),"",IF(A258="","Falta el tipo",IF(H258="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C258="","Falta el código",IF(ISNA(MATCH(C258,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D258)&gt;0,N(VLOOKUP(C258,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A258,TIPOS!$A:$C,3,FALSE),"")="Sí",B258=""),"Falta el N° de entrega",IF(N(I258)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -8752,7 +8755,7 @@
         <v/>
       </c>
       <c r="H259" s="9">
-        <f>IF(A259="","",IFERROR(VLOOKUP(A259,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A259="","",IFERROR(IF(VLOOKUP(A259,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A259,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I259" s="10">
@@ -8768,7 +8771,7 @@
         <v/>
       </c>
       <c r="L259" s="9">
-        <f>IF(AND(A259="",C259=""),"",IF(A259="","Falta el tipo",IF(C259="","Falta el código",IF(ISNA(MATCH(C259,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D259)&gt;0,N(VLOOKUP(C259,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A259,TIPOS!$A:$C,3,FALSE),"")="Sí",B259=""),"Falta el N° de entrega",IF(N(I259)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A259="",C259=""),"",IF(A259="","Falta el tipo",IF(H259="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C259="","Falta el código",IF(ISNA(MATCH(C259,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D259)&gt;0,N(VLOOKUP(C259,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A259,TIPOS!$A:$C,3,FALSE),"")="Sí",B259=""),"Falta el N° de entrega",IF(N(I259)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -8784,7 +8787,7 @@
         <v/>
       </c>
       <c r="H260" s="9">
-        <f>IF(A260="","",IFERROR(VLOOKUP(A260,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A260="","",IFERROR(IF(VLOOKUP(A260,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A260,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I260" s="10">
@@ -8800,7 +8803,7 @@
         <v/>
       </c>
       <c r="L260" s="9">
-        <f>IF(AND(A260="",C260=""),"",IF(A260="","Falta el tipo",IF(C260="","Falta el código",IF(ISNA(MATCH(C260,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D260)&gt;0,N(VLOOKUP(C260,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A260,TIPOS!$A:$C,3,FALSE),"")="Sí",B260=""),"Falta el N° de entrega",IF(N(I260)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A260="",C260=""),"",IF(A260="","Falta el tipo",IF(H260="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C260="","Falta el código",IF(ISNA(MATCH(C260,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D260)&gt;0,N(VLOOKUP(C260,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A260,TIPOS!$A:$C,3,FALSE),"")="Sí",B260=""),"Falta el N° de entrega",IF(N(I260)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -8816,7 +8819,7 @@
         <v/>
       </c>
       <c r="H261" s="9">
-        <f>IF(A261="","",IFERROR(VLOOKUP(A261,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A261="","",IFERROR(IF(VLOOKUP(A261,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A261,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I261" s="10">
@@ -8832,7 +8835,7 @@
         <v/>
       </c>
       <c r="L261" s="9">
-        <f>IF(AND(A261="",C261=""),"",IF(A261="","Falta el tipo",IF(C261="","Falta el código",IF(ISNA(MATCH(C261,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D261)&gt;0,N(VLOOKUP(C261,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A261,TIPOS!$A:$C,3,FALSE),"")="Sí",B261=""),"Falta el N° de entrega",IF(N(I261)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A261="",C261=""),"",IF(A261="","Falta el tipo",IF(H261="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C261="","Falta el código",IF(ISNA(MATCH(C261,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D261)&gt;0,N(VLOOKUP(C261,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A261,TIPOS!$A:$C,3,FALSE),"")="Sí",B261=""),"Falta el N° de entrega",IF(N(I261)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -8848,7 +8851,7 @@
         <v/>
       </c>
       <c r="H262" s="9">
-        <f>IF(A262="","",IFERROR(VLOOKUP(A262,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A262="","",IFERROR(IF(VLOOKUP(A262,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A262,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I262" s="10">
@@ -8864,7 +8867,7 @@
         <v/>
       </c>
       <c r="L262" s="9">
-        <f>IF(AND(A262="",C262=""),"",IF(A262="","Falta el tipo",IF(C262="","Falta el código",IF(ISNA(MATCH(C262,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D262)&gt;0,N(VLOOKUP(C262,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A262,TIPOS!$A:$C,3,FALSE),"")="Sí",B262=""),"Falta el N° de entrega",IF(N(I262)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A262="",C262=""),"",IF(A262="","Falta el tipo",IF(H262="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C262="","Falta el código",IF(ISNA(MATCH(C262,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D262)&gt;0,N(VLOOKUP(C262,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A262,TIPOS!$A:$C,3,FALSE),"")="Sí",B262=""),"Falta el N° de entrega",IF(N(I262)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -8880,7 +8883,7 @@
         <v/>
       </c>
       <c r="H263" s="9">
-        <f>IF(A263="","",IFERROR(VLOOKUP(A263,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A263="","",IFERROR(IF(VLOOKUP(A263,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A263,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I263" s="10">
@@ -8896,7 +8899,7 @@
         <v/>
       </c>
       <c r="L263" s="9">
-        <f>IF(AND(A263="",C263=""),"",IF(A263="","Falta el tipo",IF(C263="","Falta el código",IF(ISNA(MATCH(C263,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D263)&gt;0,N(VLOOKUP(C263,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A263,TIPOS!$A:$C,3,FALSE),"")="Sí",B263=""),"Falta el N° de entrega",IF(N(I263)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A263="",C263=""),"",IF(A263="","Falta el tipo",IF(H263="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C263="","Falta el código",IF(ISNA(MATCH(C263,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D263)&gt;0,N(VLOOKUP(C263,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A263,TIPOS!$A:$C,3,FALSE),"")="Sí",B263=""),"Falta el N° de entrega",IF(N(I263)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -8912,7 +8915,7 @@
         <v/>
       </c>
       <c r="H264" s="9">
-        <f>IF(A264="","",IFERROR(VLOOKUP(A264,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A264="","",IFERROR(IF(VLOOKUP(A264,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A264,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I264" s="10">
@@ -8928,7 +8931,7 @@
         <v/>
       </c>
       <c r="L264" s="9">
-        <f>IF(AND(A264="",C264=""),"",IF(A264="","Falta el tipo",IF(C264="","Falta el código",IF(ISNA(MATCH(C264,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D264)&gt;0,N(VLOOKUP(C264,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A264,TIPOS!$A:$C,3,FALSE),"")="Sí",B264=""),"Falta el N° de entrega",IF(N(I264)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A264="",C264=""),"",IF(A264="","Falta el tipo",IF(H264="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C264="","Falta el código",IF(ISNA(MATCH(C264,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D264)&gt;0,N(VLOOKUP(C264,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A264,TIPOS!$A:$C,3,FALSE),"")="Sí",B264=""),"Falta el N° de entrega",IF(N(I264)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -8944,7 +8947,7 @@
         <v/>
       </c>
       <c r="H265" s="9">
-        <f>IF(A265="","",IFERROR(VLOOKUP(A265,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A265="","",IFERROR(IF(VLOOKUP(A265,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A265,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I265" s="10">
@@ -8960,7 +8963,7 @@
         <v/>
       </c>
       <c r="L265" s="9">
-        <f>IF(AND(A265="",C265=""),"",IF(A265="","Falta el tipo",IF(C265="","Falta el código",IF(ISNA(MATCH(C265,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D265)&gt;0,N(VLOOKUP(C265,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A265,TIPOS!$A:$C,3,FALSE),"")="Sí",B265=""),"Falta el N° de entrega",IF(N(I265)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A265="",C265=""),"",IF(A265="","Falta el tipo",IF(H265="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C265="","Falta el código",IF(ISNA(MATCH(C265,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D265)&gt;0,N(VLOOKUP(C265,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A265,TIPOS!$A:$C,3,FALSE),"")="Sí",B265=""),"Falta el N° de entrega",IF(N(I265)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -8976,7 +8979,7 @@
         <v/>
       </c>
       <c r="H266" s="9">
-        <f>IF(A266="","",IFERROR(VLOOKUP(A266,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A266="","",IFERROR(IF(VLOOKUP(A266,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A266,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I266" s="10">
@@ -8992,7 +8995,7 @@
         <v/>
       </c>
       <c r="L266" s="9">
-        <f>IF(AND(A266="",C266=""),"",IF(A266="","Falta el tipo",IF(C266="","Falta el código",IF(ISNA(MATCH(C266,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D266)&gt;0,N(VLOOKUP(C266,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A266,TIPOS!$A:$C,3,FALSE),"")="Sí",B266=""),"Falta el N° de entrega",IF(N(I266)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A266="",C266=""),"",IF(A266="","Falta el tipo",IF(H266="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C266="","Falta el código",IF(ISNA(MATCH(C266,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D266)&gt;0,N(VLOOKUP(C266,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A266,TIPOS!$A:$C,3,FALSE),"")="Sí",B266=""),"Falta el N° de entrega",IF(N(I266)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -9008,7 +9011,7 @@
         <v/>
       </c>
       <c r="H267" s="9">
-        <f>IF(A267="","",IFERROR(VLOOKUP(A267,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A267="","",IFERROR(IF(VLOOKUP(A267,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A267,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I267" s="10">
@@ -9024,7 +9027,7 @@
         <v/>
       </c>
       <c r="L267" s="9">
-        <f>IF(AND(A267="",C267=""),"",IF(A267="","Falta el tipo",IF(C267="","Falta el código",IF(ISNA(MATCH(C267,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D267)&gt;0,N(VLOOKUP(C267,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A267,TIPOS!$A:$C,3,FALSE),"")="Sí",B267=""),"Falta el N° de entrega",IF(N(I267)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A267="",C267=""),"",IF(A267="","Falta el tipo",IF(H267="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C267="","Falta el código",IF(ISNA(MATCH(C267,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D267)&gt;0,N(VLOOKUP(C267,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A267,TIPOS!$A:$C,3,FALSE),"")="Sí",B267=""),"Falta el N° de entrega",IF(N(I267)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -9040,7 +9043,7 @@
         <v/>
       </c>
       <c r="H268" s="9">
-        <f>IF(A268="","",IFERROR(VLOOKUP(A268,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A268="","",IFERROR(IF(VLOOKUP(A268,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A268,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I268" s="10">
@@ -9056,7 +9059,7 @@
         <v/>
       </c>
       <c r="L268" s="9">
-        <f>IF(AND(A268="",C268=""),"",IF(A268="","Falta el tipo",IF(C268="","Falta el código",IF(ISNA(MATCH(C268,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D268)&gt;0,N(VLOOKUP(C268,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A268,TIPOS!$A:$C,3,FALSE),"")="Sí",B268=""),"Falta el N° de entrega",IF(N(I268)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A268="",C268=""),"",IF(A268="","Falta el tipo",IF(H268="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C268="","Falta el código",IF(ISNA(MATCH(C268,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D268)&gt;0,N(VLOOKUP(C268,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A268,TIPOS!$A:$C,3,FALSE),"")="Sí",B268=""),"Falta el N° de entrega",IF(N(I268)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -9072,7 +9075,7 @@
         <v/>
       </c>
       <c r="H269" s="9">
-        <f>IF(A269="","",IFERROR(VLOOKUP(A269,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A269="","",IFERROR(IF(VLOOKUP(A269,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A269,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I269" s="10">
@@ -9088,7 +9091,7 @@
         <v/>
       </c>
       <c r="L269" s="9">
-        <f>IF(AND(A269="",C269=""),"",IF(A269="","Falta el tipo",IF(C269="","Falta el código",IF(ISNA(MATCH(C269,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D269)&gt;0,N(VLOOKUP(C269,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A269,TIPOS!$A:$C,3,FALSE),"")="Sí",B269=""),"Falta el N° de entrega",IF(N(I269)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A269="",C269=""),"",IF(A269="","Falta el tipo",IF(H269="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C269="","Falta el código",IF(ISNA(MATCH(C269,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D269)&gt;0,N(VLOOKUP(C269,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A269,TIPOS!$A:$C,3,FALSE),"")="Sí",B269=""),"Falta el N° de entrega",IF(N(I269)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -9104,7 +9107,7 @@
         <v/>
       </c>
       <c r="H270" s="9">
-        <f>IF(A270="","",IFERROR(VLOOKUP(A270,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A270="","",IFERROR(IF(VLOOKUP(A270,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A270,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I270" s="10">
@@ -9120,7 +9123,7 @@
         <v/>
       </c>
       <c r="L270" s="9">
-        <f>IF(AND(A270="",C270=""),"",IF(A270="","Falta el tipo",IF(C270="","Falta el código",IF(ISNA(MATCH(C270,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D270)&gt;0,N(VLOOKUP(C270,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A270,TIPOS!$A:$C,3,FALSE),"")="Sí",B270=""),"Falta el N° de entrega",IF(N(I270)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A270="",C270=""),"",IF(A270="","Falta el tipo",IF(H270="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C270="","Falta el código",IF(ISNA(MATCH(C270,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D270)&gt;0,N(VLOOKUP(C270,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A270,TIPOS!$A:$C,3,FALSE),"")="Sí",B270=""),"Falta el N° de entrega",IF(N(I270)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -9136,7 +9139,7 @@
         <v/>
       </c>
       <c r="H271" s="9">
-        <f>IF(A271="","",IFERROR(VLOOKUP(A271,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A271="","",IFERROR(IF(VLOOKUP(A271,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A271,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I271" s="10">
@@ -9152,7 +9155,7 @@
         <v/>
       </c>
       <c r="L271" s="9">
-        <f>IF(AND(A271="",C271=""),"",IF(A271="","Falta el tipo",IF(C271="","Falta el código",IF(ISNA(MATCH(C271,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D271)&gt;0,N(VLOOKUP(C271,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A271,TIPOS!$A:$C,3,FALSE),"")="Sí",B271=""),"Falta el N° de entrega",IF(N(I271)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A271="",C271=""),"",IF(A271="","Falta el tipo",IF(H271="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C271="","Falta el código",IF(ISNA(MATCH(C271,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D271)&gt;0,N(VLOOKUP(C271,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A271,TIPOS!$A:$C,3,FALSE),"")="Sí",B271=""),"Falta el N° de entrega",IF(N(I271)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -9168,7 +9171,7 @@
         <v/>
       </c>
       <c r="H272" s="9">
-        <f>IF(A272="","",IFERROR(VLOOKUP(A272,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A272="","",IFERROR(IF(VLOOKUP(A272,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A272,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I272" s="10">
@@ -9184,7 +9187,7 @@
         <v/>
       </c>
       <c r="L272" s="9">
-        <f>IF(AND(A272="",C272=""),"",IF(A272="","Falta el tipo",IF(C272="","Falta el código",IF(ISNA(MATCH(C272,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D272)&gt;0,N(VLOOKUP(C272,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A272,TIPOS!$A:$C,3,FALSE),"")="Sí",B272=""),"Falta el N° de entrega",IF(N(I272)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A272="",C272=""),"",IF(A272="","Falta el tipo",IF(H272="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C272="","Falta el código",IF(ISNA(MATCH(C272,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D272)&gt;0,N(VLOOKUP(C272,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A272,TIPOS!$A:$C,3,FALSE),"")="Sí",B272=""),"Falta el N° de entrega",IF(N(I272)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -9200,7 +9203,7 @@
         <v/>
       </c>
       <c r="H273" s="9">
-        <f>IF(A273="","",IFERROR(VLOOKUP(A273,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A273="","",IFERROR(IF(VLOOKUP(A273,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A273,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I273" s="10">
@@ -9216,7 +9219,7 @@
         <v/>
       </c>
       <c r="L273" s="9">
-        <f>IF(AND(A273="",C273=""),"",IF(A273="","Falta el tipo",IF(C273="","Falta el código",IF(ISNA(MATCH(C273,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D273)&gt;0,N(VLOOKUP(C273,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A273,TIPOS!$A:$C,3,FALSE),"")="Sí",B273=""),"Falta el N° de entrega",IF(N(I273)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A273="",C273=""),"",IF(A273="","Falta el tipo",IF(H273="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C273="","Falta el código",IF(ISNA(MATCH(C273,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D273)&gt;0,N(VLOOKUP(C273,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A273,TIPOS!$A:$C,3,FALSE),"")="Sí",B273=""),"Falta el N° de entrega",IF(N(I273)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -9232,7 +9235,7 @@
         <v/>
       </c>
       <c r="H274" s="9">
-        <f>IF(A274="","",IFERROR(VLOOKUP(A274,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A274="","",IFERROR(IF(VLOOKUP(A274,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A274,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I274" s="10">
@@ -9248,7 +9251,7 @@
         <v/>
       </c>
       <c r="L274" s="9">
-        <f>IF(AND(A274="",C274=""),"",IF(A274="","Falta el tipo",IF(C274="","Falta el código",IF(ISNA(MATCH(C274,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D274)&gt;0,N(VLOOKUP(C274,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A274,TIPOS!$A:$C,3,FALSE),"")="Sí",B274=""),"Falta el N° de entrega",IF(N(I274)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A274="",C274=""),"",IF(A274="","Falta el tipo",IF(H274="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C274="","Falta el código",IF(ISNA(MATCH(C274,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D274)&gt;0,N(VLOOKUP(C274,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A274,TIPOS!$A:$C,3,FALSE),"")="Sí",B274=""),"Falta el N° de entrega",IF(N(I274)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -9264,7 +9267,7 @@
         <v/>
       </c>
       <c r="H275" s="9">
-        <f>IF(A275="","",IFERROR(VLOOKUP(A275,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A275="","",IFERROR(IF(VLOOKUP(A275,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A275,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I275" s="10">
@@ -9280,7 +9283,7 @@
         <v/>
       </c>
       <c r="L275" s="9">
-        <f>IF(AND(A275="",C275=""),"",IF(A275="","Falta el tipo",IF(C275="","Falta el código",IF(ISNA(MATCH(C275,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D275)&gt;0,N(VLOOKUP(C275,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A275,TIPOS!$A:$C,3,FALSE),"")="Sí",B275=""),"Falta el N° de entrega",IF(N(I275)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A275="",C275=""),"",IF(A275="","Falta el tipo",IF(H275="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C275="","Falta el código",IF(ISNA(MATCH(C275,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D275)&gt;0,N(VLOOKUP(C275,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A275,TIPOS!$A:$C,3,FALSE),"")="Sí",B275=""),"Falta el N° de entrega",IF(N(I275)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -9296,7 +9299,7 @@
         <v/>
       </c>
       <c r="H276" s="9">
-        <f>IF(A276="","",IFERROR(VLOOKUP(A276,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A276="","",IFERROR(IF(VLOOKUP(A276,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A276,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I276" s="10">
@@ -9312,7 +9315,7 @@
         <v/>
       </c>
       <c r="L276" s="9">
-        <f>IF(AND(A276="",C276=""),"",IF(A276="","Falta el tipo",IF(C276="","Falta el código",IF(ISNA(MATCH(C276,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D276)&gt;0,N(VLOOKUP(C276,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A276,TIPOS!$A:$C,3,FALSE),"")="Sí",B276=""),"Falta el N° de entrega",IF(N(I276)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A276="",C276=""),"",IF(A276="","Falta el tipo",IF(H276="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C276="","Falta el código",IF(ISNA(MATCH(C276,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D276)&gt;0,N(VLOOKUP(C276,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A276,TIPOS!$A:$C,3,FALSE),"")="Sí",B276=""),"Falta el N° de entrega",IF(N(I276)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -9328,7 +9331,7 @@
         <v/>
       </c>
       <c r="H277" s="9">
-        <f>IF(A277="","",IFERROR(VLOOKUP(A277,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A277="","",IFERROR(IF(VLOOKUP(A277,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A277,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I277" s="10">
@@ -9344,7 +9347,7 @@
         <v/>
       </c>
       <c r="L277" s="9">
-        <f>IF(AND(A277="",C277=""),"",IF(A277="","Falta el tipo",IF(C277="","Falta el código",IF(ISNA(MATCH(C277,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D277)&gt;0,N(VLOOKUP(C277,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A277,TIPOS!$A:$C,3,FALSE),"")="Sí",B277=""),"Falta el N° de entrega",IF(N(I277)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A277="",C277=""),"",IF(A277="","Falta el tipo",IF(H277="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C277="","Falta el código",IF(ISNA(MATCH(C277,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D277)&gt;0,N(VLOOKUP(C277,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A277,TIPOS!$A:$C,3,FALSE),"")="Sí",B277=""),"Falta el N° de entrega",IF(N(I277)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -9360,7 +9363,7 @@
         <v/>
       </c>
       <c r="H278" s="9">
-        <f>IF(A278="","",IFERROR(VLOOKUP(A278,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A278="","",IFERROR(IF(VLOOKUP(A278,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A278,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I278" s="10">
@@ -9376,7 +9379,7 @@
         <v/>
       </c>
       <c r="L278" s="9">
-        <f>IF(AND(A278="",C278=""),"",IF(A278="","Falta el tipo",IF(C278="","Falta el código",IF(ISNA(MATCH(C278,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D278)&gt;0,N(VLOOKUP(C278,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A278,TIPOS!$A:$C,3,FALSE),"")="Sí",B278=""),"Falta el N° de entrega",IF(N(I278)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A278="",C278=""),"",IF(A278="","Falta el tipo",IF(H278="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C278="","Falta el código",IF(ISNA(MATCH(C278,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D278)&gt;0,N(VLOOKUP(C278,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A278,TIPOS!$A:$C,3,FALSE),"")="Sí",B278=""),"Falta el N° de entrega",IF(N(I278)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -9392,7 +9395,7 @@
         <v/>
       </c>
       <c r="H279" s="9">
-        <f>IF(A279="","",IFERROR(VLOOKUP(A279,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A279="","",IFERROR(IF(VLOOKUP(A279,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A279,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I279" s="10">
@@ -9408,7 +9411,7 @@
         <v/>
       </c>
       <c r="L279" s="9">
-        <f>IF(AND(A279="",C279=""),"",IF(A279="","Falta el tipo",IF(C279="","Falta el código",IF(ISNA(MATCH(C279,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D279)&gt;0,N(VLOOKUP(C279,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A279,TIPOS!$A:$C,3,FALSE),"")="Sí",B279=""),"Falta el N° de entrega",IF(N(I279)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A279="",C279=""),"",IF(A279="","Falta el tipo",IF(H279="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C279="","Falta el código",IF(ISNA(MATCH(C279,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D279)&gt;0,N(VLOOKUP(C279,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A279,TIPOS!$A:$C,3,FALSE),"")="Sí",B279=""),"Falta el N° de entrega",IF(N(I279)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -9424,7 +9427,7 @@
         <v/>
       </c>
       <c r="H280" s="9">
-        <f>IF(A280="","",IFERROR(VLOOKUP(A280,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A280="","",IFERROR(IF(VLOOKUP(A280,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A280,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I280" s="10">
@@ -9440,7 +9443,7 @@
         <v/>
       </c>
       <c r="L280" s="9">
-        <f>IF(AND(A280="",C280=""),"",IF(A280="","Falta el tipo",IF(C280="","Falta el código",IF(ISNA(MATCH(C280,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D280)&gt;0,N(VLOOKUP(C280,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A280,TIPOS!$A:$C,3,FALSE),"")="Sí",B280=""),"Falta el N° de entrega",IF(N(I280)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A280="",C280=""),"",IF(A280="","Falta el tipo",IF(H280="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C280="","Falta el código",IF(ISNA(MATCH(C280,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D280)&gt;0,N(VLOOKUP(C280,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A280,TIPOS!$A:$C,3,FALSE),"")="Sí",B280=""),"Falta el N° de entrega",IF(N(I280)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -9456,7 +9459,7 @@
         <v/>
       </c>
       <c r="H281" s="9">
-        <f>IF(A281="","",IFERROR(VLOOKUP(A281,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A281="","",IFERROR(IF(VLOOKUP(A281,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A281,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I281" s="10">
@@ -9472,7 +9475,7 @@
         <v/>
       </c>
       <c r="L281" s="9">
-        <f>IF(AND(A281="",C281=""),"",IF(A281="","Falta el tipo",IF(C281="","Falta el código",IF(ISNA(MATCH(C281,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D281)&gt;0,N(VLOOKUP(C281,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A281,TIPOS!$A:$C,3,FALSE),"")="Sí",B281=""),"Falta el N° de entrega",IF(N(I281)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A281="",C281=""),"",IF(A281="","Falta el tipo",IF(H281="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C281="","Falta el código",IF(ISNA(MATCH(C281,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D281)&gt;0,N(VLOOKUP(C281,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A281,TIPOS!$A:$C,3,FALSE),"")="Sí",B281=""),"Falta el N° de entrega",IF(N(I281)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -9488,7 +9491,7 @@
         <v/>
       </c>
       <c r="H282" s="9">
-        <f>IF(A282="","",IFERROR(VLOOKUP(A282,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A282="","",IFERROR(IF(VLOOKUP(A282,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A282,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I282" s="10">
@@ -9504,7 +9507,7 @@
         <v/>
       </c>
       <c r="L282" s="9">
-        <f>IF(AND(A282="",C282=""),"",IF(A282="","Falta el tipo",IF(C282="","Falta el código",IF(ISNA(MATCH(C282,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D282)&gt;0,N(VLOOKUP(C282,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A282,TIPOS!$A:$C,3,FALSE),"")="Sí",B282=""),"Falta el N° de entrega",IF(N(I282)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A282="",C282=""),"",IF(A282="","Falta el tipo",IF(H282="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C282="","Falta el código",IF(ISNA(MATCH(C282,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D282)&gt;0,N(VLOOKUP(C282,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A282,TIPOS!$A:$C,3,FALSE),"")="Sí",B282=""),"Falta el N° de entrega",IF(N(I282)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -9520,7 +9523,7 @@
         <v/>
       </c>
       <c r="H283" s="9">
-        <f>IF(A283="","",IFERROR(VLOOKUP(A283,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A283="","",IFERROR(IF(VLOOKUP(A283,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A283,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I283" s="10">
@@ -9536,7 +9539,7 @@
         <v/>
       </c>
       <c r="L283" s="9">
-        <f>IF(AND(A283="",C283=""),"",IF(A283="","Falta el tipo",IF(C283="","Falta el código",IF(ISNA(MATCH(C283,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D283)&gt;0,N(VLOOKUP(C283,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A283,TIPOS!$A:$C,3,FALSE),"")="Sí",B283=""),"Falta el N° de entrega",IF(N(I283)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A283="",C283=""),"",IF(A283="","Falta el tipo",IF(H283="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C283="","Falta el código",IF(ISNA(MATCH(C283,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D283)&gt;0,N(VLOOKUP(C283,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A283,TIPOS!$A:$C,3,FALSE),"")="Sí",B283=""),"Falta el N° de entrega",IF(N(I283)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -9552,7 +9555,7 @@
         <v/>
       </c>
       <c r="H284" s="9">
-        <f>IF(A284="","",IFERROR(VLOOKUP(A284,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A284="","",IFERROR(IF(VLOOKUP(A284,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A284,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I284" s="10">
@@ -9568,7 +9571,7 @@
         <v/>
       </c>
       <c r="L284" s="9">
-        <f>IF(AND(A284="",C284=""),"",IF(A284="","Falta el tipo",IF(C284="","Falta el código",IF(ISNA(MATCH(C284,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D284)&gt;0,N(VLOOKUP(C284,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A284,TIPOS!$A:$C,3,FALSE),"")="Sí",B284=""),"Falta el N° de entrega",IF(N(I284)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A284="",C284=""),"",IF(A284="","Falta el tipo",IF(H284="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C284="","Falta el código",IF(ISNA(MATCH(C284,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D284)&gt;0,N(VLOOKUP(C284,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A284,TIPOS!$A:$C,3,FALSE),"")="Sí",B284=""),"Falta el N° de entrega",IF(N(I284)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -9584,7 +9587,7 @@
         <v/>
       </c>
       <c r="H285" s="9">
-        <f>IF(A285="","",IFERROR(VLOOKUP(A285,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A285="","",IFERROR(IF(VLOOKUP(A285,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A285,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I285" s="10">
@@ -9600,7 +9603,7 @@
         <v/>
       </c>
       <c r="L285" s="9">
-        <f>IF(AND(A285="",C285=""),"",IF(A285="","Falta el tipo",IF(C285="","Falta el código",IF(ISNA(MATCH(C285,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D285)&gt;0,N(VLOOKUP(C285,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A285,TIPOS!$A:$C,3,FALSE),"")="Sí",B285=""),"Falta el N° de entrega",IF(N(I285)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A285="",C285=""),"",IF(A285="","Falta el tipo",IF(H285="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C285="","Falta el código",IF(ISNA(MATCH(C285,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D285)&gt;0,N(VLOOKUP(C285,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A285,TIPOS!$A:$C,3,FALSE),"")="Sí",B285=""),"Falta el N° de entrega",IF(N(I285)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -9616,7 +9619,7 @@
         <v/>
       </c>
       <c r="H286" s="9">
-        <f>IF(A286="","",IFERROR(VLOOKUP(A286,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A286="","",IFERROR(IF(VLOOKUP(A286,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A286,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I286" s="10">
@@ -9632,7 +9635,7 @@
         <v/>
       </c>
       <c r="L286" s="9">
-        <f>IF(AND(A286="",C286=""),"",IF(A286="","Falta el tipo",IF(C286="","Falta el código",IF(ISNA(MATCH(C286,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D286)&gt;0,N(VLOOKUP(C286,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A286,TIPOS!$A:$C,3,FALSE),"")="Sí",B286=""),"Falta el N° de entrega",IF(N(I286)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A286="",C286=""),"",IF(A286="","Falta el tipo",IF(H286="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C286="","Falta el código",IF(ISNA(MATCH(C286,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D286)&gt;0,N(VLOOKUP(C286,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A286,TIPOS!$A:$C,3,FALSE),"")="Sí",B286=""),"Falta el N° de entrega",IF(N(I286)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -9648,7 +9651,7 @@
         <v/>
       </c>
       <c r="H287" s="9">
-        <f>IF(A287="","",IFERROR(VLOOKUP(A287,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A287="","",IFERROR(IF(VLOOKUP(A287,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A287,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I287" s="10">
@@ -9664,7 +9667,7 @@
         <v/>
       </c>
       <c r="L287" s="9">
-        <f>IF(AND(A287="",C287=""),"",IF(A287="","Falta el tipo",IF(C287="","Falta el código",IF(ISNA(MATCH(C287,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D287)&gt;0,N(VLOOKUP(C287,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A287,TIPOS!$A:$C,3,FALSE),"")="Sí",B287=""),"Falta el N° de entrega",IF(N(I287)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A287="",C287=""),"",IF(A287="","Falta el tipo",IF(H287="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C287="","Falta el código",IF(ISNA(MATCH(C287,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D287)&gt;0,N(VLOOKUP(C287,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A287,TIPOS!$A:$C,3,FALSE),"")="Sí",B287=""),"Falta el N° de entrega",IF(N(I287)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -9680,7 +9683,7 @@
         <v/>
       </c>
       <c r="H288" s="9">
-        <f>IF(A288="","",IFERROR(VLOOKUP(A288,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A288="","",IFERROR(IF(VLOOKUP(A288,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A288,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I288" s="10">
@@ -9696,7 +9699,7 @@
         <v/>
       </c>
       <c r="L288" s="9">
-        <f>IF(AND(A288="",C288=""),"",IF(A288="","Falta el tipo",IF(C288="","Falta el código",IF(ISNA(MATCH(C288,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D288)&gt;0,N(VLOOKUP(C288,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A288,TIPOS!$A:$C,3,FALSE),"")="Sí",B288=""),"Falta el N° de entrega",IF(N(I288)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A288="",C288=""),"",IF(A288="","Falta el tipo",IF(H288="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C288="","Falta el código",IF(ISNA(MATCH(C288,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D288)&gt;0,N(VLOOKUP(C288,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A288,TIPOS!$A:$C,3,FALSE),"")="Sí",B288=""),"Falta el N° de entrega",IF(N(I288)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -9712,7 +9715,7 @@
         <v/>
       </c>
       <c r="H289" s="9">
-        <f>IF(A289="","",IFERROR(VLOOKUP(A289,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A289="","",IFERROR(IF(VLOOKUP(A289,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A289,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I289" s="10">
@@ -9728,7 +9731,7 @@
         <v/>
       </c>
       <c r="L289" s="9">
-        <f>IF(AND(A289="",C289=""),"",IF(A289="","Falta el tipo",IF(C289="","Falta el código",IF(ISNA(MATCH(C289,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D289)&gt;0,N(VLOOKUP(C289,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A289,TIPOS!$A:$C,3,FALSE),"")="Sí",B289=""),"Falta el N° de entrega",IF(N(I289)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A289="",C289=""),"",IF(A289="","Falta el tipo",IF(H289="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C289="","Falta el código",IF(ISNA(MATCH(C289,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D289)&gt;0,N(VLOOKUP(C289,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A289,TIPOS!$A:$C,3,FALSE),"")="Sí",B289=""),"Falta el N° de entrega",IF(N(I289)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -9744,7 +9747,7 @@
         <v/>
       </c>
       <c r="H290" s="9">
-        <f>IF(A290="","",IFERROR(VLOOKUP(A290,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A290="","",IFERROR(IF(VLOOKUP(A290,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A290,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I290" s="10">
@@ -9760,7 +9763,7 @@
         <v/>
       </c>
       <c r="L290" s="9">
-        <f>IF(AND(A290="",C290=""),"",IF(A290="","Falta el tipo",IF(C290="","Falta el código",IF(ISNA(MATCH(C290,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D290)&gt;0,N(VLOOKUP(C290,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A290,TIPOS!$A:$C,3,FALSE),"")="Sí",B290=""),"Falta el N° de entrega",IF(N(I290)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A290="",C290=""),"",IF(A290="","Falta el tipo",IF(H290="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C290="","Falta el código",IF(ISNA(MATCH(C290,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D290)&gt;0,N(VLOOKUP(C290,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A290,TIPOS!$A:$C,3,FALSE),"")="Sí",B290=""),"Falta el N° de entrega",IF(N(I290)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -9776,7 +9779,7 @@
         <v/>
       </c>
       <c r="H291" s="9">
-        <f>IF(A291="","",IFERROR(VLOOKUP(A291,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A291="","",IFERROR(IF(VLOOKUP(A291,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A291,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I291" s="10">
@@ -9792,7 +9795,7 @@
         <v/>
       </c>
       <c r="L291" s="9">
-        <f>IF(AND(A291="",C291=""),"",IF(A291="","Falta el tipo",IF(C291="","Falta el código",IF(ISNA(MATCH(C291,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D291)&gt;0,N(VLOOKUP(C291,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A291,TIPOS!$A:$C,3,FALSE),"")="Sí",B291=""),"Falta el N° de entrega",IF(N(I291)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A291="",C291=""),"",IF(A291="","Falta el tipo",IF(H291="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C291="","Falta el código",IF(ISNA(MATCH(C291,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D291)&gt;0,N(VLOOKUP(C291,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A291,TIPOS!$A:$C,3,FALSE),"")="Sí",B291=""),"Falta el N° de entrega",IF(N(I291)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -9808,7 +9811,7 @@
         <v/>
       </c>
       <c r="H292" s="9">
-        <f>IF(A292="","",IFERROR(VLOOKUP(A292,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A292="","",IFERROR(IF(VLOOKUP(A292,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A292,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I292" s="10">
@@ -9824,7 +9827,7 @@
         <v/>
       </c>
       <c r="L292" s="9">
-        <f>IF(AND(A292="",C292=""),"",IF(A292="","Falta el tipo",IF(C292="","Falta el código",IF(ISNA(MATCH(C292,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D292)&gt;0,N(VLOOKUP(C292,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A292,TIPOS!$A:$C,3,FALSE),"")="Sí",B292=""),"Falta el N° de entrega",IF(N(I292)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A292="",C292=""),"",IF(A292="","Falta el tipo",IF(H292="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C292="","Falta el código",IF(ISNA(MATCH(C292,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D292)&gt;0,N(VLOOKUP(C292,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A292,TIPOS!$A:$C,3,FALSE),"")="Sí",B292=""),"Falta el N° de entrega",IF(N(I292)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -9840,7 +9843,7 @@
         <v/>
       </c>
       <c r="H293" s="9">
-        <f>IF(A293="","",IFERROR(VLOOKUP(A293,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A293="","",IFERROR(IF(VLOOKUP(A293,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A293,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I293" s="10">
@@ -9856,7 +9859,7 @@
         <v/>
       </c>
       <c r="L293" s="9">
-        <f>IF(AND(A293="",C293=""),"",IF(A293="","Falta el tipo",IF(C293="","Falta el código",IF(ISNA(MATCH(C293,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D293)&gt;0,N(VLOOKUP(C293,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A293,TIPOS!$A:$C,3,FALSE),"")="Sí",B293=""),"Falta el N° de entrega",IF(N(I293)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A293="",C293=""),"",IF(A293="","Falta el tipo",IF(H293="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C293="","Falta el código",IF(ISNA(MATCH(C293,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D293)&gt;0,N(VLOOKUP(C293,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A293,TIPOS!$A:$C,3,FALSE),"")="Sí",B293=""),"Falta el N° de entrega",IF(N(I293)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -9872,7 +9875,7 @@
         <v/>
       </c>
       <c r="H294" s="9">
-        <f>IF(A294="","",IFERROR(VLOOKUP(A294,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A294="","",IFERROR(IF(VLOOKUP(A294,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A294,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I294" s="10">
@@ -9888,7 +9891,7 @@
         <v/>
       </c>
       <c r="L294" s="9">
-        <f>IF(AND(A294="",C294=""),"",IF(A294="","Falta el tipo",IF(C294="","Falta el código",IF(ISNA(MATCH(C294,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D294)&gt;0,N(VLOOKUP(C294,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A294,TIPOS!$A:$C,3,FALSE),"")="Sí",B294=""),"Falta el N° de entrega",IF(N(I294)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A294="",C294=""),"",IF(A294="","Falta el tipo",IF(H294="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C294="","Falta el código",IF(ISNA(MATCH(C294,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D294)&gt;0,N(VLOOKUP(C294,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A294,TIPOS!$A:$C,3,FALSE),"")="Sí",B294=""),"Falta el N° de entrega",IF(N(I294)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -9904,7 +9907,7 @@
         <v/>
       </c>
       <c r="H295" s="9">
-        <f>IF(A295="","",IFERROR(VLOOKUP(A295,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A295="","",IFERROR(IF(VLOOKUP(A295,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A295,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I295" s="10">
@@ -9920,7 +9923,7 @@
         <v/>
       </c>
       <c r="L295" s="9">
-        <f>IF(AND(A295="",C295=""),"",IF(A295="","Falta el tipo",IF(C295="","Falta el código",IF(ISNA(MATCH(C295,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D295)&gt;0,N(VLOOKUP(C295,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A295,TIPOS!$A:$C,3,FALSE),"")="Sí",B295=""),"Falta el N° de entrega",IF(N(I295)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A295="",C295=""),"",IF(A295="","Falta el tipo",IF(H295="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C295="","Falta el código",IF(ISNA(MATCH(C295,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D295)&gt;0,N(VLOOKUP(C295,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A295,TIPOS!$A:$C,3,FALSE),"")="Sí",B295=""),"Falta el N° de entrega",IF(N(I295)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -9936,7 +9939,7 @@
         <v/>
       </c>
       <c r="H296" s="9">
-        <f>IF(A296="","",IFERROR(VLOOKUP(A296,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A296="","",IFERROR(IF(VLOOKUP(A296,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A296,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I296" s="10">
@@ -9952,7 +9955,7 @@
         <v/>
       </c>
       <c r="L296" s="9">
-        <f>IF(AND(A296="",C296=""),"",IF(A296="","Falta el tipo",IF(C296="","Falta el código",IF(ISNA(MATCH(C296,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D296)&gt;0,N(VLOOKUP(C296,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A296,TIPOS!$A:$C,3,FALSE),"")="Sí",B296=""),"Falta el N° de entrega",IF(N(I296)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A296="",C296=""),"",IF(A296="","Falta el tipo",IF(H296="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C296="","Falta el código",IF(ISNA(MATCH(C296,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D296)&gt;0,N(VLOOKUP(C296,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A296,TIPOS!$A:$C,3,FALSE),"")="Sí",B296=""),"Falta el N° de entrega",IF(N(I296)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -9968,7 +9971,7 @@
         <v/>
       </c>
       <c r="H297" s="9">
-        <f>IF(A297="","",IFERROR(VLOOKUP(A297,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A297="","",IFERROR(IF(VLOOKUP(A297,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A297,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I297" s="10">
@@ -9984,7 +9987,7 @@
         <v/>
       </c>
       <c r="L297" s="9">
-        <f>IF(AND(A297="",C297=""),"",IF(A297="","Falta el tipo",IF(C297="","Falta el código",IF(ISNA(MATCH(C297,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D297)&gt;0,N(VLOOKUP(C297,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A297,TIPOS!$A:$C,3,FALSE),"")="Sí",B297=""),"Falta el N° de entrega",IF(N(I297)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A297="",C297=""),"",IF(A297="","Falta el tipo",IF(H297="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C297="","Falta el código",IF(ISNA(MATCH(C297,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D297)&gt;0,N(VLOOKUP(C297,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A297,TIPOS!$A:$C,3,FALSE),"")="Sí",B297=""),"Falta el N° de entrega",IF(N(I297)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -10000,7 +10003,7 @@
         <v/>
       </c>
       <c r="H298" s="9">
-        <f>IF(A298="","",IFERROR(VLOOKUP(A298,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A298="","",IFERROR(IF(VLOOKUP(A298,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A298,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I298" s="10">
@@ -10016,7 +10019,7 @@
         <v/>
       </c>
       <c r="L298" s="9">
-        <f>IF(AND(A298="",C298=""),"",IF(A298="","Falta el tipo",IF(C298="","Falta el código",IF(ISNA(MATCH(C298,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D298)&gt;0,N(VLOOKUP(C298,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A298,TIPOS!$A:$C,3,FALSE),"")="Sí",B298=""),"Falta el N° de entrega",IF(N(I298)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A298="",C298=""),"",IF(A298="","Falta el tipo",IF(H298="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C298="","Falta el código",IF(ISNA(MATCH(C298,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D298)&gt;0,N(VLOOKUP(C298,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A298,TIPOS!$A:$C,3,FALSE),"")="Sí",B298=""),"Falta el N° de entrega",IF(N(I298)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -10032,7 +10035,7 @@
         <v/>
       </c>
       <c r="H299" s="9">
-        <f>IF(A299="","",IFERROR(VLOOKUP(A299,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A299="","",IFERROR(IF(VLOOKUP(A299,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A299,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I299" s="10">
@@ -10048,7 +10051,7 @@
         <v/>
       </c>
       <c r="L299" s="9">
-        <f>IF(AND(A299="",C299=""),"",IF(A299="","Falta el tipo",IF(C299="","Falta el código",IF(ISNA(MATCH(C299,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D299)&gt;0,N(VLOOKUP(C299,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A299,TIPOS!$A:$C,3,FALSE),"")="Sí",B299=""),"Falta el N° de entrega",IF(N(I299)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A299="",C299=""),"",IF(A299="","Falta el tipo",IF(H299="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C299="","Falta el código",IF(ISNA(MATCH(C299,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D299)&gt;0,N(VLOOKUP(C299,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A299,TIPOS!$A:$C,3,FALSE),"")="Sí",B299=""),"Falta el N° de entrega",IF(N(I299)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -10064,7 +10067,7 @@
         <v/>
       </c>
       <c r="H300" s="9">
-        <f>IF(A300="","",IFERROR(VLOOKUP(A300,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A300="","",IFERROR(IF(VLOOKUP(A300,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A300,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I300" s="10">
@@ -10080,7 +10083,7 @@
         <v/>
       </c>
       <c r="L300" s="9">
-        <f>IF(AND(A300="",C300=""),"",IF(A300="","Falta el tipo",IF(C300="","Falta el código",IF(ISNA(MATCH(C300,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D300)&gt;0,N(VLOOKUP(C300,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A300,TIPOS!$A:$C,3,FALSE),"")="Sí",B300=""),"Falta el N° de entrega",IF(N(I300)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A300="",C300=""),"",IF(A300="","Falta el tipo",IF(H300="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C300="","Falta el código",IF(ISNA(MATCH(C300,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D300)&gt;0,N(VLOOKUP(C300,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A300,TIPOS!$A:$C,3,FALSE),"")="Sí",B300=""),"Falta el N° de entrega",IF(N(I300)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -10096,7 +10099,7 @@
         <v/>
       </c>
       <c r="H301" s="9">
-        <f>IF(A301="","",IFERROR(VLOOKUP(A301,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A301="","",IFERROR(IF(VLOOKUP(A301,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A301,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I301" s="10">
@@ -10112,7 +10115,7 @@
         <v/>
       </c>
       <c r="L301" s="9">
-        <f>IF(AND(A301="",C301=""),"",IF(A301="","Falta el tipo",IF(C301="","Falta el código",IF(ISNA(MATCH(C301,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D301)&gt;0,N(VLOOKUP(C301,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A301,TIPOS!$A:$C,3,FALSE),"")="Sí",B301=""),"Falta el N° de entrega",IF(N(I301)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A301="",C301=""),"",IF(A301="","Falta el tipo",IF(H301="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C301="","Falta el código",IF(ISNA(MATCH(C301,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D301)&gt;0,N(VLOOKUP(C301,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A301,TIPOS!$A:$C,3,FALSE),"")="Sí",B301=""),"Falta el N° de entrega",IF(N(I301)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -10128,7 +10131,7 @@
         <v/>
       </c>
       <c r="H302" s="9">
-        <f>IF(A302="","",IFERROR(VLOOKUP(A302,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A302="","",IFERROR(IF(VLOOKUP(A302,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A302,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I302" s="10">
@@ -10144,7 +10147,7 @@
         <v/>
       </c>
       <c r="L302" s="9">
-        <f>IF(AND(A302="",C302=""),"",IF(A302="","Falta el tipo",IF(C302="","Falta el código",IF(ISNA(MATCH(C302,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D302)&gt;0,N(VLOOKUP(C302,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A302,TIPOS!$A:$C,3,FALSE),"")="Sí",B302=""),"Falta el N° de entrega",IF(N(I302)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A302="",C302=""),"",IF(A302="","Falta el tipo",IF(H302="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C302="","Falta el código",IF(ISNA(MATCH(C302,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D302)&gt;0,N(VLOOKUP(C302,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A302,TIPOS!$A:$C,3,FALSE),"")="Sí",B302=""),"Falta el N° de entrega",IF(N(I302)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -10160,7 +10163,7 @@
         <v/>
       </c>
       <c r="H303" s="9">
-        <f>IF(A303="","",IFERROR(VLOOKUP(A303,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A303="","",IFERROR(IF(VLOOKUP(A303,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A303,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I303" s="10">
@@ -10176,7 +10179,7 @@
         <v/>
       </c>
       <c r="L303" s="9">
-        <f>IF(AND(A303="",C303=""),"",IF(A303="","Falta el tipo",IF(C303="","Falta el código",IF(ISNA(MATCH(C303,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D303)&gt;0,N(VLOOKUP(C303,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A303,TIPOS!$A:$C,3,FALSE),"")="Sí",B303=""),"Falta el N° de entrega",IF(N(I303)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A303="",C303=""),"",IF(A303="","Falta el tipo",IF(H303="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C303="","Falta el código",IF(ISNA(MATCH(C303,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D303)&gt;0,N(VLOOKUP(C303,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A303,TIPOS!$A:$C,3,FALSE),"")="Sí",B303=""),"Falta el N° de entrega",IF(N(I303)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -10192,7 +10195,7 @@
         <v/>
       </c>
       <c r="H304" s="9">
-        <f>IF(A304="","",IFERROR(VLOOKUP(A304,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A304="","",IFERROR(IF(VLOOKUP(A304,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A304,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I304" s="10">
@@ -10208,7 +10211,7 @@
         <v/>
       </c>
       <c r="L304" s="9">
-        <f>IF(AND(A304="",C304=""),"",IF(A304="","Falta el tipo",IF(C304="","Falta el código",IF(ISNA(MATCH(C304,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D304)&gt;0,N(VLOOKUP(C304,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A304,TIPOS!$A:$C,3,FALSE),"")="Sí",B304=""),"Falta el N° de entrega",IF(N(I304)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A304="",C304=""),"",IF(A304="","Falta el tipo",IF(H304="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C304="","Falta el código",IF(ISNA(MATCH(C304,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D304)&gt;0,N(VLOOKUP(C304,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A304,TIPOS!$A:$C,3,FALSE),"")="Sí",B304=""),"Falta el N° de entrega",IF(N(I304)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -10224,7 +10227,7 @@
         <v/>
       </c>
       <c r="H305" s="9">
-        <f>IF(A305="","",IFERROR(VLOOKUP(A305,TIPOS!$A:$B,2,FALSE),""))</f>
+        <f>IF(A305="","",IFERROR(IF(VLOOKUP(A305,TIPOS!$A:$B,2,FALSE)=0,"",VLOOKUP(A305,TIPOS!$A:$B,2,FALSE)),""))</f>
         <v/>
       </c>
       <c r="I305" s="10">
@@ -10240,7 +10243,7 @@
         <v/>
       </c>
       <c r="L305" s="9">
-        <f>IF(AND(A305="",C305=""),"",IF(A305="","Falta el tipo",IF(C305="","Falta el código",IF(ISNA(MATCH(C305,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D305)&gt;0,N(VLOOKUP(C305,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A305,TIPOS!$A:$C,3,FALSE),"")="Sí",B305=""),"Falta el N° de entrega",IF(N(I305)&lt;=0,"Falta la cantidad","OK")))))))</f>
+        <f>IF(AND(A305="",C305=""),"",IF(A305="","Falta el tipo",IF(H305="","A ese tipo le falta «SUMA EN» en la hoja TIPOS",IF(C305="","Falta el código",IF(ISNA(MATCH(C305,MAESTRO!$A:$A,0)),"El código no está en el maestro",IF(AND(N(D305)&gt;0,N(VLOOKUP(C305,MAESTRO!$A:$D,4,FALSE))=0),"Ese código no tiene cajas por estiba: escribe cajas",IF(AND(IFERROR(VLOOKUP(A305,TIPOS!$A:$C,3,FALSE),"")="Sí",B305=""),"Falta el N° de entrega",IF(N(I305)&lt;=0,"Falta la cantidad","OK"))))))))</f>
         <v/>
       </c>
     </row>
@@ -10258,14 +10261,14 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation sqref="A6:A305" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="Escoge un tipo de la lista." type="list">
-      <formula1>=TIPOS!$A$2:$A$8</formula1>
-    </dataValidation>
     <dataValidation sqref="C6:C305" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=MAESTRO!$A$2:$A$28</formula1>
     </dataValidation>
     <dataValidation sqref="D6:F305" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="Solo números (0 o más)." type="decimal" operator="greaterThanOrEqual">
       <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="A6:A305" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="Escoge un tipo de la lista (o agrégalo en la hoja TIPOS)." type="list">
+      <formula1>=TIPOS!$A$2:$A$40</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11041,7 +11044,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -11049,6 +11052,7 @@
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="48" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11077,6 +11081,11 @@
           <t>¿SUMA SU CAJA PLÁSTICA?</t>
         </is>
       </c>
+      <c r="G1" s="17" t="inlineStr">
+        <is>
+          <t>¿Una partida nueva? Escríbela en una fila amarilla: nombre, en qué lado suma (CONTEO, SAP o NO SUMA), si pide N° de entrega y si suma su caja plástica. Sale sola en la lista de NOVEDADES.</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="15" t="inlineStr">
@@ -11267,7 +11276,239 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="7" t="n"/>
+      <c r="B9" s="7" t="n"/>
+      <c r="C9" s="7" t="n"/>
+      <c r="D9" s="7" t="n"/>
+      <c r="E9" s="7" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="n"/>
+      <c r="B10" s="7" t="n"/>
+      <c r="C10" s="7" t="n"/>
+      <c r="D10" s="7" t="n"/>
+      <c r="E10" s="7" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="n"/>
+      <c r="B11" s="7" t="n"/>
+      <c r="C11" s="7" t="n"/>
+      <c r="D11" s="7" t="n"/>
+      <c r="E11" s="7" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="n"/>
+      <c r="B12" s="7" t="n"/>
+      <c r="C12" s="7" t="n"/>
+      <c r="D12" s="7" t="n"/>
+      <c r="E12" s="7" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="n"/>
+      <c r="B13" s="7" t="n"/>
+      <c r="C13" s="7" t="n"/>
+      <c r="D13" s="7" t="n"/>
+      <c r="E13" s="7" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="n"/>
+      <c r="B14" s="7" t="n"/>
+      <c r="C14" s="7" t="n"/>
+      <c r="D14" s="7" t="n"/>
+      <c r="E14" s="7" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="n"/>
+      <c r="B15" s="7" t="n"/>
+      <c r="C15" s="7" t="n"/>
+      <c r="D15" s="7" t="n"/>
+      <c r="E15" s="7" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="n"/>
+      <c r="B16" s="7" t="n"/>
+      <c r="C16" s="7" t="n"/>
+      <c r="D16" s="7" t="n"/>
+      <c r="E16" s="7" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="n"/>
+      <c r="B17" s="7" t="n"/>
+      <c r="C17" s="7" t="n"/>
+      <c r="D17" s="7" t="n"/>
+      <c r="E17" s="7" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="n"/>
+      <c r="B18" s="7" t="n"/>
+      <c r="C18" s="7" t="n"/>
+      <c r="D18" s="7" t="n"/>
+      <c r="E18" s="7" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="n"/>
+      <c r="B19" s="7" t="n"/>
+      <c r="C19" s="7" t="n"/>
+      <c r="D19" s="7" t="n"/>
+      <c r="E19" s="7" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="n"/>
+      <c r="B20" s="7" t="n"/>
+      <c r="C20" s="7" t="n"/>
+      <c r="D20" s="7" t="n"/>
+      <c r="E20" s="7" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="n"/>
+      <c r="B21" s="7" t="n"/>
+      <c r="C21" s="7" t="n"/>
+      <c r="D21" s="7" t="n"/>
+      <c r="E21" s="7" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="n"/>
+      <c r="B22" s="7" t="n"/>
+      <c r="C22" s="7" t="n"/>
+      <c r="D22" s="7" t="n"/>
+      <c r="E22" s="7" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="n"/>
+      <c r="B23" s="7" t="n"/>
+      <c r="C23" s="7" t="n"/>
+      <c r="D23" s="7" t="n"/>
+      <c r="E23" s="7" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="n"/>
+      <c r="B24" s="7" t="n"/>
+      <c r="C24" s="7" t="n"/>
+      <c r="D24" s="7" t="n"/>
+      <c r="E24" s="7" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="n"/>
+      <c r="B25" s="7" t="n"/>
+      <c r="C25" s="7" t="n"/>
+      <c r="D25" s="7" t="n"/>
+      <c r="E25" s="7" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="n"/>
+      <c r="B26" s="7" t="n"/>
+      <c r="C26" s="7" t="n"/>
+      <c r="D26" s="7" t="n"/>
+      <c r="E26" s="7" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="n"/>
+      <c r="B27" s="7" t="n"/>
+      <c r="C27" s="7" t="n"/>
+      <c r="D27" s="7" t="n"/>
+      <c r="E27" s="7" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="n"/>
+      <c r="B28" s="7" t="n"/>
+      <c r="C28" s="7" t="n"/>
+      <c r="D28" s="7" t="n"/>
+      <c r="E28" s="7" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="n"/>
+      <c r="B29" s="7" t="n"/>
+      <c r="C29" s="7" t="n"/>
+      <c r="D29" s="7" t="n"/>
+      <c r="E29" s="7" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="n"/>
+      <c r="B30" s="7" t="n"/>
+      <c r="C30" s="7" t="n"/>
+      <c r="D30" s="7" t="n"/>
+      <c r="E30" s="7" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="n"/>
+      <c r="B31" s="7" t="n"/>
+      <c r="C31" s="7" t="n"/>
+      <c r="D31" s="7" t="n"/>
+      <c r="E31" s="7" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="n"/>
+      <c r="B32" s="7" t="n"/>
+      <c r="C32" s="7" t="n"/>
+      <c r="D32" s="7" t="n"/>
+      <c r="E32" s="7" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="n"/>
+      <c r="B33" s="7" t="n"/>
+      <c r="C33" s="7" t="n"/>
+      <c r="D33" s="7" t="n"/>
+      <c r="E33" s="7" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="n"/>
+      <c r="B34" s="7" t="n"/>
+      <c r="C34" s="7" t="n"/>
+      <c r="D34" s="7" t="n"/>
+      <c r="E34" s="7" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="n"/>
+      <c r="B35" s="7" t="n"/>
+      <c r="C35" s="7" t="n"/>
+      <c r="D35" s="7" t="n"/>
+      <c r="E35" s="7" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="n"/>
+      <c r="B36" s="7" t="n"/>
+      <c r="C36" s="7" t="n"/>
+      <c r="D36" s="7" t="n"/>
+      <c r="E36" s="7" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="n"/>
+      <c r="B37" s="7" t="n"/>
+      <c r="C37" s="7" t="n"/>
+      <c r="D37" s="7" t="n"/>
+      <c r="E37" s="7" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="n"/>
+      <c r="B38" s="7" t="n"/>
+      <c r="C38" s="7" t="n"/>
+      <c r="D38" s="7" t="n"/>
+      <c r="E38" s="7" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="n"/>
+      <c r="B39" s="7" t="n"/>
+      <c r="C39" s="7" t="n"/>
+      <c r="D39" s="7" t="n"/>
+      <c r="E39" s="7" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="n"/>
+      <c r="B40" s="7" t="n"/>
+      <c r="C40" s="7" t="n"/>
+      <c r="D40" s="7" t="n"/>
+      <c r="E40" s="7" t="n"/>
+    </row>
   </sheetData>
+  <dataValidations count="2">
+    <dataValidation sqref="B2:B40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"CONTEO,SAP,NO SUMA"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C2:C40 E2:E40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Sí,No"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/public/plantillas/analisis-diferencia-novedades.xlsx
+++ b/public/plantillas/analisis-diferencia-novedades.xlsx
@@ -11277,18 +11277,58 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="n"/>
-      <c r="B9" s="7" t="n"/>
-      <c r="C9" s="7" t="n"/>
-      <c r="D9" s="7" t="n"/>
-      <c r="E9" s="7" t="n"/>
+      <c r="A9" s="15" t="inlineStr">
+        <is>
+          <t>NOTIFICACION</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>CONTEO</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D9" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente notificación de envase: existe, suma al conteo.</t>
+        </is>
+      </c>
+      <c r="E9" s="15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="n"/>
-      <c r="B10" s="7" t="n"/>
-      <c r="C10" s="7" t="n"/>
-      <c r="D10" s="7" t="n"/>
-      <c r="E10" s="7" t="n"/>
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>MERMA</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>CONTEO</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D10" s="15" t="inlineStr">
+        <is>
+          <t>Merma de envase: suma al conteo.</t>
+        </is>
+      </c>
+      <c r="E10" s="15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n"/>

--- a/public/plantillas/analisis-diferencia-novedades.xlsx
+++ b/public/plantillas/analisis-diferencia-novedades.xlsx
@@ -581,7 +581,7 @@
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Llena solo lo amarillo: el tipo, el código y la cantidad (en estibas, cajas o unidades: la que tengas). N° de entrega solo en PEND NOVEDADES CD. La ZEXI de las 6 va aquí también (tipo ZEXI 6 AM, en UNIDADES SUELTAS). Lo gris sale solo; VALIDACIÓN debe decir OK.</t>
+          <t>Llena solo lo amarillo: el tipo, el código y la cantidad (en estibas, cajas o unidades: la que tengas). N° de entrega solo en PEND NOVEDADES CD. La ZEXI de las 6 va aquí también (tipo ZEXI 6 AM, en UNIDADES SUELTAS). La DEPA de cada línea (tipo DEPA L1, DEPA L2, DEPA L4, DEPA L6, en UNIDADES SUELTAS o estibas/cajas) también va aquí cuando no hay corte inicial ese día. Lo gris sale solo; VALIDACIÓN debe decir OK.</t>
         </is>
       </c>
     </row>
@@ -10281,7 +10281,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -10508,7 +10508,33 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>DEPA L1</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="n"/>
+      <c r="C10" s="11" t="n">
+        <v>3500005</v>
+      </c>
+      <c r="D10" s="11" t="n"/>
+      <c r="E10" s="11" t="n"/>
+      <c r="F10" s="11" t="n">
+        <v>330714</v>
+      </c>
+      <c r="G10" s="11" t="inlineStr">
+        <is>
+          <t>330.714 u</t>
+        </is>
+      </c>
+      <c r="H10" s="11" t="inlineStr">
+        <is>
+          <t>3500231 · 8.703</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>Las cajas plásticas NO se escriben aparte: salen solas del envase (2052/38, 39780/30… como en tu Excel).</t>
         </is>
@@ -11331,32 +11357,112 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="n"/>
-      <c r="B11" s="7" t="n"/>
-      <c r="C11" s="7" t="n"/>
-      <c r="D11" s="7" t="n"/>
-      <c r="E11" s="7" t="n"/>
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>DEPA L1</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>CONTEO</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D11" s="15" t="inlineStr">
+        <is>
+          <t>Depaletizadora de la línea L1: lo que marca la depa. Solo si NO hay corte inicial ese día (si lo hay, la app usa el corte). La caja plástica sale sola del envase.</t>
+        </is>
+      </c>
+      <c r="E11" s="15" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="n"/>
-      <c r="B12" s="7" t="n"/>
-      <c r="C12" s="7" t="n"/>
-      <c r="D12" s="7" t="n"/>
-      <c r="E12" s="7" t="n"/>
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>DEPA L2</t>
+        </is>
+      </c>
+      <c r="B12" s="15" t="inlineStr">
+        <is>
+          <t>CONTEO</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D12" s="15" t="inlineStr">
+        <is>
+          <t>Depaletizadora de la línea L2: lo que marca la depa. Solo si NO hay corte inicial ese día (si lo hay, la app usa el corte). La caja plástica sale sola del envase.</t>
+        </is>
+      </c>
+      <c r="E12" s="15" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="n"/>
-      <c r="B13" s="7" t="n"/>
-      <c r="C13" s="7" t="n"/>
-      <c r="D13" s="7" t="n"/>
-      <c r="E13" s="7" t="n"/>
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>DEPA L4</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t>CONTEO</t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D13" s="15" t="inlineStr">
+        <is>
+          <t>Depaletizadora de la línea L4: lo que marca la depa. Solo si NO hay corte inicial ese día (si lo hay, la app usa el corte). La caja plástica sale sola del envase.</t>
+        </is>
+      </c>
+      <c r="E13" s="15" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="n"/>
-      <c r="B14" s="7" t="n"/>
-      <c r="C14" s="7" t="n"/>
-      <c r="D14" s="7" t="n"/>
-      <c r="E14" s="7" t="n"/>
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>DEPA L6</t>
+        </is>
+      </c>
+      <c r="B14" s="15" t="inlineStr">
+        <is>
+          <t>CONTEO</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D14" s="15" t="inlineStr">
+        <is>
+          <t>Depaletizadora de la línea L6: lo que marca la depa. Solo si NO hay corte inicial ese día (si lo hay, la app usa el corte). La caja plástica sale sola del envase.</t>
+        </is>
+      </c>
+      <c r="E14" s="15" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n"/>
